--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E17" s="73" t="inlineStr">
         <is>
-          <t>AI는 처리 권한이 확인된 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행하며, 작품 설정이 자동이면 회차 발행마다 실행합니다.</t>
+          <t>AI는 처리 권한이 확인된 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행하며, 작품 설정이 자동이면 작가나 자율 연재가 새 회차를 발행할 때마다 실행합니다. 피드백 수정안 반영에 따른 재발행은 실행 대상이 아닙니다.</t>
         </is>
       </c>
       <c r="F17" s="99" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="F58" s="96" t="inlineStr">
         <is>
-          <t>AI 분석 크레딧은 제보자 부담(확정). 등록 시 독자가 본 발행본 버전을 고정합니다. 외부 플랫폼 댓글 수집 제외. 비회원 범위·공개 수준 미정.</t>
+          <t>제보(질문·오류 제보·제안)의 AI 분석 크레딧은 제보자 부담이며, 크레딧이 없으면 제보는 못 하고 댓글만 등록 가능(확정). 댓글은 AI 분석 없이 무료. 등록 시 독자가 본 발행본 버전을 고정. 외부 플랫폼 댓글 수집 제외.</t>
         </is>
       </c>
       <c r="G58" s="73" t="inlineStr">
@@ -4233,7 +4233,11 @@
           <t>AI는 질문·표기 오류 제보·설정 충돌 의심·개인적 해석·전개 선호 등 유형과 의도를 구분해야 합니다. 한 피드백에 섞인 요구를 단일 유형으로 강제하지 않아야 합니다.</t>
         </is>
       </c>
-      <c r="F59" s="96" t="n"/>
+      <c r="F59" s="96" t="inlineStr">
+        <is>
+          <t>피드백 분석은 공개 근거를 대조하는 검증이며 세계관·설정을 바꾸지 않습니다.</t>
+        </is>
+      </c>
       <c r="G59" s="73" t="inlineStr">
         <is>
           <t>UC-15</t>
@@ -5850,7 +5854,7 @@
       </c>
       <c r="E87" s="73" t="inlineStr">
         <is>
-          <t>다른 플랫폼에서 가져온 2차 창작물은 작품 유형으로 구분하고 무료 공개만 허용해야 합니다. 등록자에게 권리 책임과 즉시 비공개·소명 절차를 고지하고 동의를 받아야 합니다.</t>
+          <t>다른 플랫폼에서 가져온 2차 창작물은 작품 유형으로 구분하고 무료 공개만 허용해야 합니다. 등록자에게 권리 책임과 권리 문제 시 운영자 조치·소명 절차를 고지하고 동의를 받아야 합니다. 외부 2차 창작물도 Fork 원작이 될 수 있으며 AI 기능 크레딧은 별도로 청구합니다.</t>
         </is>
       </c>
       <c r="F87" s="96" t="inlineStr">
@@ -5976,7 +5980,7 @@
       </c>
       <c r="E89" s="73" t="inlineStr">
         <is>
-          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 분석은 제보자, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담하며 Fork 생성·직접 집필은 무료입니다.</t>
+          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 제보 분석은 제보자, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담하며 Fork 생성·직접 집필·댓글은 무료입니다.</t>
         </is>
       </c>
       <c r="F89" s="96" t="inlineStr">
@@ -6220,12 +6224,12 @@
       </c>
       <c r="E93" s="73" t="inlineStr">
         <is>
-          <t>접수된 신고 대상은 즉시 비공개하고 관련 AI·Fork 기능을 멈춘 뒤 작품 소유자에게 소명 절차를 안내해야 합니다. 운영자가 소명을 검토해 재공개 또는 비공개 유지를 결정합니다.</t>
+          <t>권리 신고가 접수되면 운영자에게 바로 알리고, 운영자가 빠르게 검토해 비공개·관련 AI·Fork 기능 중지 등 필요한 조치를 한 뒤 작품 소유자에게 소명 절차를 안내해야 합니다. 운영자가 소명을 검토해 재공개 또는 비공개 유지를 결정합니다.</t>
         </is>
       </c>
       <c r="F93" s="96" t="inlineStr">
         <is>
-          <t>허위 신고 대응·소명 기한·기존 Fork 영향 미정. 신고만으로 원고를 삭제하지 않습니다.</t>
+          <t>조치 기준(즉시 비공개 여부 포함)은 상세 검토 예정. 허위 신고 대응·소명 기한·기존 Fork 영향 미정. 신고만으로 원고를 삭제하지 않습니다.</t>
         </is>
       </c>
       <c r="G93" s="73" t="inlineStr">
@@ -13858,7 +13862,7 @@
       </c>
       <c r="D18" s="73" t="inlineStr">
         <is>
-          <t>신고 접수 시 즉시 비공개·소명 절차 확정. 증빙·소명 기한·허위 신고 대응·기존 Fork 영향은 미정.</t>
+          <t>신고 접수 시 운영자가 빠르게 검토·조치(비공개 등)하고 소명 절차를 엶. 즉시 비공개 여부 등 상세 절차는 검토 예정. 증빙·소명 기한·허위 신고 대응·기존 Fork 영향은 미정.</t>
         </is>
       </c>
       <c r="E18" s="73" t="inlineStr">

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1536,7 +1536,11 @@
           <t>사용자는 작품과 별도로 새 세계관을 만들고 설명을 입력하거나 기존 세계관 정보를 수정·조회할 수 있어야 합니다.</t>
         </is>
       </c>
-      <c r="F12" s="96" t="n"/>
+      <c r="F12" s="96" t="inlineStr">
+        <is>
+          <t>필수 항목은 세계관 이름만(확정). 연결 작품이 없을 때만 삭제 가능, 연결 작품 수 제한 없음.</t>
+        </is>
+      </c>
       <c r="G12" s="73" t="inlineStr">
         <is>
           <t>UC-02</t>
@@ -1647,12 +1651,12 @@
       </c>
       <c r="E14" s="77" t="inlineStr">
         <is>
-          <t>사용자는 작품을 생성할 때 자신이 소유하거나 이용이 허용된 세계관을 반드시 연결해야 합니다. 세계관 없이 작품을 만들 수 없으며, 공개 세계관 이용이 해당 세계관 정본의 수정 권한을 부여하지는 않습니다.</t>
+          <t>사용자는 작품을 생성할 때 자신이 소유하거나 이용이 허용된 세계관을 1~5개 연결해야 합니다. 세계관 없이 작품을 만들 수 없으며, 공개 세계관 이용이 해당 세계관 정본의 수정 권한을 부여하지는 않습니다.</t>
         </is>
       </c>
       <c r="F14" s="98" t="inlineStr">
         <is>
-          <t>세계관·작품 관계와 공유 세계관 업데이트 수용 방식 미정. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
+          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
         </is>
       </c>
       <c r="G14" s="73" t="inlineStr">
@@ -1941,7 +1945,11 @@
           <t>공유 세계관을 바탕으로 창작하더라도 작품에서 발생한 사건과 설정 변경은 해당 작품에 독립적으로 저장되어야 합니다.</t>
         </is>
       </c>
-      <c r="F19" s="68" t="n"/>
+      <c r="F19" s="68" t="inlineStr">
+        <is>
+          <t>공개 세계관 이용 작품은 고치지 않은 항목만 원작 최신 공개본을 자동 반영하고 고친 항목은 유지(확정). 이용 허가 철회 시 기존 연결은 철회 시점 상태로 고정.</t>
+        </is>
+      </c>
       <c r="G19" s="73" t="inlineStr">
         <is>
           <t>UC-24, UC-05</t>
@@ -2114,7 +2122,11 @@
           <t>회차·사건 시점별 인물의 감정·관계·보유 정보 변화를 기록해야 합니다. 시뮬레이션의 임시 상태는 사용자 채택 없이 정본 상태에 반영하지 않아야 합니다.</t>
         </is>
       </c>
-      <c r="F22" s="98" t="n"/>
+      <c r="F22" s="98" t="inlineStr">
+        <is>
+          <t>인물 기본 정보·작품별 시점 상태·인지는 세계관과 함께 Gitea에 저장(확정).</t>
+        </is>
+      </c>
       <c r="G22" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1947,7 +1947,7 @@
       </c>
       <c r="F19" s="68" t="inlineStr">
         <is>
-          <t>공개 세계관 이용 작품은 고치지 않은 항목만 원작 최신 공개본을 자동 반영하고 고친 항목은 유지(확정). 이용 허가 철회 시 기존 연결은 철회 시점 상태로 고정.</t>
+          <t>공개 세계관 항목은 고치지 않으면 원본 참조(최신 공개본 자동 반영), 고치려면 작가 세계관으로 편입해 수정(확정). 새 추출 설정도 작가 세계관에 저장. 이용 허가 철회 시 철회 시점 상태로 고정.</t>
         </is>
       </c>
       <c r="G19" s="73" t="inlineStr">
@@ -5177,7 +5177,11 @@
           <t>현재 원고와 세계관 정보, 기존 회차에 기록된 설정을 대조해 충돌 여부를 검토해야 합니다.</t>
         </is>
       </c>
-      <c r="F75" s="96" t="n"/>
+      <c r="F75" s="96" t="inlineStr">
+        <is>
+          <t>검토는 선택 기능이며 발행 전 필수 단계가 아님(확정). 모든 AI 기능은 작가가 골라 쓰는 도구.</t>
+        </is>
+      </c>
       <c r="G75" s="73" t="inlineStr">
         <is>
           <t>UC-12</t>
@@ -5812,7 +5816,7 @@
       </c>
       <c r="F86" s="96" t="inlineStr">
         <is>
-          <t>기존 Fork에는 반영하지 않습니다.</t>
+          <t>독자 공개 회차는 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G86" s="73" t="inlineStr">

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F12" s="96" t="inlineStr">
         <is>
-          <t>필수 항목은 세계관 이름만(확정). 연결 작품이 없을 때만 삭제 가능, 연결 작품 수 제한 없음.</t>
+          <t>필수 항목은 세계관 이름만(확정). 기존 세계관 여러 개에서 항목을 골라 새 세계관을 조합할 수 있음. 연결 작품이 없을 때만 삭제 가능.</t>
         </is>
       </c>
       <c r="G12" s="73" t="inlineStr">
@@ -2067,7 +2067,11 @@
           <t>등장인물 간 관계를 정의하고 작품 진행에 따른 관계 정보를 확인할 수 있어야 합니다.</t>
         </is>
       </c>
-      <c r="F21" s="100" t="n"/>
+      <c r="F21" s="100" t="inlineStr">
+        <is>
+          <t>인물관계도는 세계관과 따로 만들어 작품에 추가할 수 있고, Fork에서도 인물관계도만 새로 정리 가능(확정).</t>
+        </is>
+      </c>
       <c r="G21" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -2647,7 +2651,7 @@
       </c>
       <c r="F31" s="101" t="inlineStr">
         <is>
-          <t>권리 확인 절차 및 증빙 기준 정의 필요</t>
+          <t>원작에서만 Fork 가능, 한 독자는 한 원작에서 1번만, Fork 작품의 Fork 불가(확정, 관리 단순화). 권리 확인 절차·증빙 기준 정의 필요</t>
         </is>
       </c>
       <c r="G31" s="73" t="inlineStr">
@@ -2761,7 +2765,7 @@
       </c>
       <c r="F33" s="101" t="inlineStr">
         <is>
-          <t>고정 방식(복사·불변 참조·Gitea 브랜치) 미정. 원작의 후속 변경·공개 전환은 기존 Fork에 반영하지 않습니다. 분기 이후는 Fork 소유자가 수정 가능.</t>
+          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 고정 방식(복사·불변 참조·Gitea 브랜치) 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G33" s="73" t="inlineStr">
@@ -5875,7 +5879,7 @@
       </c>
       <c r="F87" s="96" t="inlineStr">
         <is>
-          <t>플랫폼 면책 범위는 이용약관·법률 검토 필요.</t>
+          <t>같은 외부 IP는 먼저 올린 작품을 원본으로 인정하고 다른 작품도 허용(확정). 외부 IP의 2차 창작 허용 범위는 등록자가 따르며 플랫폼은 직접 확인하지 않음. 면책 범위는 이용약관·법률 검토 필요.</t>
         </is>
       </c>
       <c r="G87" s="73" t="inlineStr">
@@ -6245,7 +6249,7 @@
       </c>
       <c r="F93" s="96" t="inlineStr">
         <is>
-          <t>조치 기준(즉시 비공개 여부 포함)은 상세 검토 예정. 허위 신고 대응·소명 기한·기존 Fork 영향 미정. 신고만으로 원고를 삭제하지 않습니다.</t>
+          <t>원작 작가임이 확인된 신고는 즉시 비공개(확정), 그 밖의 조치 기준은 상세 검토 예정. 원작 작가 확인 방법·허위 신고 대응·소명 기한 미정. 신고만으로 원고를 삭제하지 않습니다.</t>
         </is>
       </c>
       <c r="G93" s="73" t="inlineStr">

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -939,7 +939,7 @@
     <row r="2" ht="30" customHeight="1" s="109">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>기획서 v1.4 · 유스케이스 v3·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 92개 미구현 · 미정 정책 유지 · 상세: 정리 기준 시트</t>
+          <t>기획서 v1.4 · 유스케이스 v5·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 92개 미구현 · 미정 정책 유지 · 상세: 정리 기준 시트</t>
         </is>
       </c>
       <c r="B2" s="110" t="n"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F12" s="96" t="inlineStr">
         <is>
-          <t>필수 항목은 세계관 이름만(확정). 기존 세계관 여러 개에서 항목을 골라 새 세계관을 조합할 수 있음. 연결 작품이 없을 때만 삭제 가능.</t>
+          <t>필수 항목은 세계관 이름만(확정). 플랫폼이 제공하는 장르 기본 세계관에서 복사해 시작 가능(원본 관계 없음, 운영자 관리, 장르 목록 미정). 기존 세계관 여러 개에서 항목을 골라 새 세계관을 조합할 수 있으며, 다른 사용자 세계관이 섞이면 세계관 Fork로 출처 기록. 연결 작품이 없을 때만 삭제 가능하며, Fork 등이 참조하는 버전은 보관하고 참조자에게 자기 세계관으로 옮기도록 안내. 인물관계도는 세계관의 일부.</t>
         </is>
       </c>
       <c r="G12" s="73" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F14" s="98" t="inlineStr">
         <is>
-          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
+          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 단, 연결한 다른 사용자 세계관을 자기 세계관 Fork로 교체하는 것은 발행 후에도 허용(연결 수 유지). 세계관 Fork를 허용하지 않은 세계관만 연결하면 작가 소유 세계관도 함께 연결하도록 안내. 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
         </is>
       </c>
       <c r="G14" s="73" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E17" s="73" t="inlineStr">
         <is>
-          <t>AI는 처리 권한이 확인된 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행하며, 작품 설정이 자동이면 작가나 자율 연재가 새 회차를 발행할 때마다 실행합니다. 피드백 수정안 반영에 따른 재발행은 실행 대상이 아닙니다.</t>
+          <t>AI는 처리 권한이 확인된 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행합니다. 작품 설정이 자동이면 새 회차 발행 때 자동 반영하고, 이미 발행한 회차를 작가가 다시 발행하면 추출 후 작가가 확인한 항목만 반영합니다. 피드백 수정안 반영에 따른 재발행은 실행 대상이 아닙니다.</t>
         </is>
       </c>
       <c r="F17" s="99" t="inlineStr">
@@ -1890,7 +1890,11 @@
           <t>수동 모드에서 사용자는 AI 추출 후보를 검토·수정하고 채택·제외할 항목을 선택하며, 확인한 설정만 저장해야 합니다. 자동 모드에서는 결과를 반영하되 변경 이력에 남기고, 기존 값과 충돌하는 항목은 덮어쓰지 않아야 합니다.</t>
         </is>
       </c>
-      <c r="F18" s="69" t="n"/>
+      <c r="F18" s="69" t="inlineStr">
+        <is>
+          <t>설정을 지우는 변경은 자동 삭제하지 않고 삭제 후보로 알림. 저장할 작가 소유 세계관이 없으면 자동으로 세계관 Fork를 만들지 않고 처음 한 번 작가 확인을 받음.</t>
+        </is>
+      </c>
       <c r="G18" s="73" t="inlineStr">
         <is>
           <t>UC-04</t>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="F19" s="68" t="inlineStr">
         <is>
-          <t>공개 세계관 항목은 고치지 않으면 원본 참조(최신 공개본 자동 반영), 고치려면 작가 세계관으로 편입해 수정(확정). 새 추출 설정도 작가 세계관에 저장. 이용 허가 철회 시 철회 시점 상태로 고정.</t>
+          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 공개 항목만, 비공개 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경 알림·골라 가져오기는 미확정. 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
         </is>
       </c>
       <c r="G19" s="73" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="F21" s="100" t="inlineStr">
         <is>
-          <t>인물관계도는 세계관과 따로 만들어 작품에 추가할 수 있고, Fork에서도 인물관계도만 새로 정리 가능(확정).</t>
+          <t>인물관계도는 세계관의 일부(확정). 인물관계도만 바꾸려면 인물관계도만 담은 세계관을 만들어 연결하며, Fork에서도 같은 방식으로 정리.</t>
         </is>
       </c>
       <c r="G21" s="73" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="F22" s="98" t="inlineStr">
         <is>
-          <t>인물 기본 정보·작품별 시점 상태·인지는 세계관과 함께 Gitea에 저장(확정).</t>
+          <t>인물 기본 정보는 세계관과 함께 Gitea에 저장(확정). 회차 시점(설정 유효·독자 공개·인물별 인지 회차)은 세계관이 아니라 작품별로 기록(확정).</t>
         </is>
       </c>
       <c r="G22" s="73" t="inlineStr">
@@ -2765,7 +2769,7 @@
       </c>
       <c r="F33" s="101" t="inlineStr">
         <is>
-          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 고정 방식(복사·불변 참조·Gitea 브랜치) 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
+          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 분기 시점 버전을 참조하는 원칙은 확정, Gitea 브랜치·커밋 참조 등 구현 수단은 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G33" s="73" t="inlineStr">
@@ -2877,7 +2881,11 @@
           <t>분기 이후 사건·인물 상태는 Fork에 독립 저장되어 원작에 영향을 주지 않아야 합니다. 원작의 후속 수정·새 회차가 기존 Fork의 고정 기준에 자동 유입되지 않아야 합니다.</t>
         </is>
       </c>
-      <c r="F35" s="69" t="n"/>
+      <c r="F35" s="69" t="inlineStr">
+        <is>
+          <t>작품 운영 설정(세계관 업데이트·표기 오류 처리·자율 연재)과 공개 조건은 Fork에 넘기지 않음(확정). 분기 이후 설정 수정은 Fork 작품 전용 세계관에 저장하며 다른 작품에 연결·공개 불가. 원작이 빌려 쓴 다른 작가 세계관 항목은 그 작가가 세계관 Fork를 허용했을 때만 수정 가능하고 그 작가의 제한이 Fork에도 적용.</t>
+        </is>
+      </c>
       <c r="G35" s="73" t="inlineStr">
         <is>
           <t>UC-08</t>
@@ -3559,7 +3567,7 @@
       </c>
       <c r="F47" s="105" t="inlineStr">
         <is>
-          <t>Fork 생성·직접 집필은 무료 기획 방향. 편집 형식·자동 저장·동시 편집 정책 미정.</t>
+          <t>Fork 생성·직접 집필은 무료 기획 방향. 편집 형식·자동 저장·동시 편집·원고 내보내기(TXT 등) 정책 미정.</t>
         </is>
       </c>
       <c r="G47" s="73" t="inlineStr">
@@ -3950,7 +3958,11 @@
           <t>허용된 이용 조건 안에서 원작과 동일한 집필 방식을 Fork 작품에도 적용할 수 있어야 합니다.</t>
         </is>
       </c>
-      <c r="F54" s="105" t="n"/>
+      <c r="F54" s="105" t="inlineStr">
+        <is>
+          <t>원작의 설정값은 물려받지 않고 기본값(수동·작가 검토·끔)으로 시작하며, Fork 소유자가 직접 설정하고 비용을 부담(확정).</t>
+        </is>
+      </c>
       <c r="G54" s="73" t="inlineStr">
         <is>
           <t>UC-08, UC-10, UC-11, UC-18</t>
@@ -4883,10 +4895,14 @@
       </c>
       <c r="E70" s="73" t="inlineStr">
         <is>
-          <t>소유자는 세계관을 비공개·일부 공개·전체 공개 등 이용 가능한 범위로 설정할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F70" s="96" t="n"/>
+          <t>소유자는 세계관을 비공개 또는 공개로 설정하고, 이용·세계관 Fork·AI 처리·이 세계관을 쓴 작품의 유료 공개 허용을 각각 정할 수 있어야 합니다. 세계관 이용과 세계관 Fork는 따로 허용합니다.</t>
+        </is>
+      </c>
+      <c r="F70" s="96" t="inlineStr">
+        <is>
+          <t>'일부 공개'는 삭제(확정). 세계관 자체의 판매는 범위 밖. 공개 세계관을 비공개로 바꾸면 이용 허가 철회와 같이 처리.</t>
+        </is>
+      </c>
       <c r="G70" s="73" t="inlineStr">
         <is>
           <t>UC-02, UC-07</t>
@@ -4997,7 +5013,7 @@
       </c>
       <c r="E72" s="73" t="inlineStr">
         <is>
-          <t>작품별 열람·세계관 이용·AI 처리·Fork·공개·유료 공개 권한을 구분하고 Core API에서 허용 여부를 확인해야 합니다. 공개된 콘텐츠나 원고 보유만으로 모든 이용을 허용하지 않아야 합니다.</t>
+          <t>작품 권한(AI 처리·작품 Fork 생성·Fork 작품 공개·유료 공개)과 세계관 권한(이용·세계관 Fork·AI 처리·작품 유료 공개 허용)을 구분하고, 독자 열람은 공개 범위로 판단하며, Core API에서 허용 여부를 확인해야 합니다. 공개된 콘텐츠나 원고 보유만으로 모든 이용을 허용하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F72" s="96" t="inlineStr">
@@ -5756,12 +5772,12 @@
       </c>
       <c r="E85" s="73" t="inlineStr">
         <is>
-          <t>세계관·인물관계도의 모든 변경을 이력으로 저장하고 이전 상태를 조회·되돌릴 수 있어야 합니다. 자동 반영 결과도 이력에 남겨야 합니다.</t>
+          <t>세계관·인물관계도의 모든 변경을 현재 HEAD 위에 새 버전으로 쌓아 저장하고(덮어쓰기·삭제·머지 없음) 이전 상태를 조회·되돌릴 수 있어야 합니다. 자동 반영 결과도 이력에 남겨야 합니다. 자기 세계관을 고칠 때 함께 반영될 자기 작품 목록을 저장 전에 안내합니다.</t>
         </is>
       </c>
       <c r="F85" s="96" t="inlineStr">
         <is>
-          <t>저장소는 Gitea(확정). 보관 기간 미정.</t>
+          <t>저장소는 Gitea(확정). 변경 이력은 무기한 보관(확정). 영향 작품 안내는 조회만 하며 AI를 쓰지 않음.</t>
         </is>
       </c>
       <c r="G85" s="73" t="inlineStr">
@@ -5820,7 +5836,7 @@
       </c>
       <c r="F86" s="96" t="inlineStr">
         <is>
-          <t>독자 공개 회차는 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
+          <t>세계관에서는 항목의 공개·비공개만 정하고, 공개 전환 회차는 연결된 작품에서 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G86" s="73" t="inlineStr">
@@ -5946,7 +5962,7 @@
       </c>
       <c r="F88" s="96" t="inlineStr">
         <is>
-          <t>가격·무료 제공량·차감 시점 미정.</t>
+          <t>가격·무료 제공량·차감 시점 미정. 비용 확인 단계 취소는 '취소됨'으로 기록하고 차감하지 않음(확정). 실행 중 중단 기능 제공 여부는 미정.</t>
         </is>
       </c>
       <c r="G88" s="73" t="inlineStr">
@@ -6000,7 +6016,7 @@
       </c>
       <c r="E89" s="73" t="inlineStr">
         <is>
-          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 제보 분석은 제보자, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담하며 Fork 생성·직접 집필·댓글은 무료입니다.</t>
+          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 제보 분석은 제보자, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담하며 작품 Fork·세계관 Fork 생성, 직접 집필, 댓글은 무료입니다.</t>
         </is>
       </c>
       <c r="F89" s="96" t="inlineStr">
@@ -6249,7 +6265,7 @@
       </c>
       <c r="F93" s="96" t="inlineStr">
         <is>
-          <t>원작 작가임이 확인된 신고는 즉시 비공개(확정), 그 밖의 조치 기준은 상세 검토 예정. 원작 작가 확인 방법·허위 신고 대응·소명 기한 미정. 신고만으로 원고를 삭제하지 않습니다.</t>
+          <t>원작 작가임이 확인된 신고는 즉시 비공개(확정), 그 밖의 조치 기준은 상세 검토 예정. 원작 작가 확인 방법·허위 신고 대응·소명 기한 미정. 신고만으로 원고를 삭제하지 않습니다. 신고 대상이 세계관이면 관련 작품·세계관 Fork 목록을 운영자에게 보여 주고 자동 일괄 조치 없이 건별 판단하며, 관련 소유자에게 경고(신고자 정보 미노출).</t>
         </is>
       </c>
       <c r="G93" s="73" t="inlineStr">
@@ -13427,7 +13443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="19" customWidth="1" style="109" min="1" max="1"/>
@@ -13666,7 +13682,7 @@
       </c>
       <c r="D10" s="73" t="inlineStr">
         <is>
-          <t>기준 회차의 정확한 버전과 당시 허용된 공개 정보만 고정. 비공개·이후 내용 제외. 원작 후속 변경 자동 유입 금지. 복사/참조 방식과 철회 영향은 미정.</t>
+          <t>기준 회차의 정확한 버전과 당시 허용된 공개 정보만 고정. 비공개·이후 내용 제외. 원작 후속 변경 자동 유입 금지. 분기 시점 버전 참조 원칙은 확정(구현 수단 미정). 작품 운영 설정·공개 조건은 넘기지 않음. 철회 영향은 미정.</t>
         </is>
       </c>
       <c r="E10" s="73" t="inlineStr">
@@ -13931,12 +13947,12 @@
       </c>
       <c r="C20" s="73" t="inlineStr">
         <is>
-          <t>별도 정정 필요</t>
+          <t>정정 완료</t>
         </is>
       </c>
       <c r="D20" s="73" t="inlineStr">
         <is>
-          <t>usecase.md의 요구사항 정의서 관련 표현은 정정 완료. README의 기획서 버전 v1.3 표기는 여전히 정정 필요.</t>
+          <t>README의 기획서 버전 표기는 v1.4로 정정 완료.</t>
         </is>
       </c>
       <c r="E20" s="73" t="inlineStr">
@@ -14023,6 +14039,114 @@
       <c r="E23" s="73" t="inlineStr">
         <is>
           <t>usecase.md §3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1" s="109">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="inlineStr">
+        <is>
+          <t>세계관 버전·회차 기록</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="inlineStr">
+        <is>
+          <t>확정 / F-SET-02·03, F-CHR-03</t>
+        </is>
+      </c>
+      <c r="D24" s="73" t="inlineStr">
+        <is>
+          <t>세계관 변경은 HEAD 위에 새 버전으로 쌓고 덮어쓰기·머지 없음. 회차 시점은 작품별로 기록. 자동 업데이트는 새 회차 자동 반영, 재발행은 작가 확인 후 반영, 수정안 재발행 제외.</t>
+        </is>
+      </c>
+      <c r="E24" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-10·BR-11; UC-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1" s="109">
+      <c r="A25" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B25" s="73" t="inlineStr">
+        <is>
+          <t>세계관 Fork·기본 세계관</t>
+        </is>
+      </c>
+      <c r="C25" s="73" t="inlineStr">
+        <is>
+          <t>확정 / F-WLD-01·08, F-RGT-01</t>
+        </is>
+      </c>
+      <c r="D25" s="73" t="inlineStr">
+        <is>
+          <t>다른 사용자 세계관 수정 시 공개 항목만 세계관 Fork로 복사·연결 교체·원본 업데이트 없음·출처 기록. 플랫폼 장르 기본 세계관 복사는 원본 관계 없음. 이용과 세계관 Fork는 따로 허용.</t>
+        </is>
+      </c>
+      <c r="E25" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-12; UC-02, UC-05, UC-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1" s="109">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B26" s="73" t="inlineStr">
+        <is>
+          <t>작품 Fork 승계 범위</t>
+        </is>
+      </c>
+      <c r="C26" s="73" t="inlineStr">
+        <is>
+          <t>확정 / F-FRK-04·06, F-WRT-08</t>
+        </is>
+      </c>
+      <c r="D26" s="73" t="inlineStr">
+        <is>
+          <t>회차·세계관·인물관계도만 승계. 작품 운영 설정·공개 조건은 승계하지 않음. 분기 이후 수정은 Fork 작품 전용 세계관.</t>
+        </is>
+      </c>
+      <c r="E26" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-04; UC-08, UC-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1" s="109">
+      <c r="A27" s="73" t="inlineStr">
+        <is>
+          <t>추적 규칙</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="inlineStr">
+        <is>
+          <t>UC-25 후보</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="inlineStr">
+        <is>
+          <t>기능 ID 미부여</t>
+        </is>
+      </c>
+      <c r="D27" s="73" t="inlineStr">
+        <is>
+          <t>UI 프로토타입에서 제안된 캐릭터 챗을 후보 유스케이스로 추가. 채택 시 기능 ID 부여.</t>
+        </is>
+      </c>
+      <c r="E27" s="73" t="inlineStr">
+        <is>
+          <t>usecase.md §3.1; usecase-spec/UC-25.md; prototype-alignment.md</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="시트1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정리 기준" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정리 기준" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'정리 기준'!$A$3:$E$20</definedName>
@@ -939,7 +939,7 @@
     <row r="2" ht="30" customHeight="1" s="109">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>기획서 v1.4 · 유스케이스 v5·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 92개 미구현 · 미정 정책 유지 · 상세: 정리 기준 시트</t>
+          <t>기획서 v1.4 · 유스케이스 v6·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 116개 미구현 · 미정 정책 유지 · 상세: 정리 기준 시트</t>
         </is>
       </c>
       <c r="B2" s="110" t="n"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F4" s="68" t="inlineStr">
         <is>
-          <t>필수 입력 항목과 본인 확인 방식 정의 필요</t>
+          <t>필수 항목은 이메일·비밀번호·닉네임, 이메일 인증 후 계정 생성(확정). 약관·선택 동의 항목은 미정.</t>
         </is>
       </c>
       <c r="G4" s="73" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H4" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I4" s="73" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F5" s="96" t="inlineStr">
         <is>
-          <t>이메일·비밀번호 로그인과 JWT 토큰 인증 확정. 소셜 로그인은 추후 연동. 토큰 만료·갱신 정책 정의 필요</t>
+          <t>이메일·비밀번호 로그인과 JWT 접근 토큰(30분)·갱신 토큰(14일, 갱신 시 재발급, 폐기 토큰 재사용 시 전체 폐기) 확정. 소셜 로그인은 추후 연동. 기준 값은 보안 검토 후 조정.</t>
         </is>
       </c>
       <c r="G5" s="73" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H5" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I5" s="73" t="inlineStr">
@@ -1178,7 +1178,11 @@
           <t>사용자는 현재 로그인 세션을 종료하고 서비스에서 로그아웃할 수 있어야 합니다.</t>
         </is>
       </c>
-      <c r="F6" s="96" t="n"/>
+      <c r="F6" s="96" t="inlineStr">
+        <is>
+          <t>로그아웃 시 그 기기의 갱신 토큰 폐기(확정). 접근 토큰은 짧은 만료로 종료.</t>
+        </is>
+      </c>
       <c r="G6" s="73" t="inlineStr">
         <is>
           <t>UC-22</t>
@@ -1186,7 +1190,7 @@
       </c>
       <c r="H6" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I6" s="73" t="inlineStr">
@@ -1235,7 +1239,7 @@
       </c>
       <c r="F7" s="96" t="inlineStr">
         <is>
-          <t>JWT 토큰 만료·갱신(리프레시) 및 다중 기기 정책 정의 필요</t>
+          <t>다중 기기 로그인 허용(확정). 갱신 토큰은 서버에서 폐기 가능하게 관리.</t>
         </is>
       </c>
       <c r="G7" s="73" t="inlineStr">
@@ -1245,7 +1249,7 @@
       </c>
       <c r="H7" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I7" s="73" t="inlineStr">
@@ -1304,7 +1308,7 @@
       </c>
       <c r="H8" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I8" s="73" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="H9" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I9" s="73" t="inlineStr">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="F10" s="96" t="inlineStr">
         <is>
-          <t>인증 방식에 따른 복구 절차 정의 필요</t>
+          <t>가입 이메일로 재설정 링크 발송, 재설정 시 모든 갱신 토큰 폐기(확정).</t>
         </is>
       </c>
       <c r="G10" s="73" t="inlineStr">
@@ -1422,7 +1426,7 @@
       </c>
       <c r="H10" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I10" s="73" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="F11" s="96" t="inlineStr">
         <is>
-          <t>데이터 삭제·보존 기준 정의 필요</t>
+          <t>30일 유예 후 작품·세계관·Fork 삭제, 다른 회원의 Fork가 참조하는 고정본은 유지('탈퇴한 회원' 표시), 댓글·피드백은 익명화(확정). 남은 크레딧 처리는 미정.</t>
         </is>
       </c>
       <c r="G11" s="73" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="H11" s="73" t="inlineStr">
         <is>
-          <t>지원 기획 / 인증 방식 확정·세부 정책 미정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I11" s="73" t="inlineStr">
@@ -1510,45 +1514,37 @@
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="n"/>
     </row>
-    <row r="12" ht="64" customHeight="1" s="109">
-      <c r="A12" s="60" t="inlineStr">
-        <is>
-          <t>REQ02</t>
-        </is>
-      </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>세계관·작품 관리</t>
-        </is>
-      </c>
+    <row r="12" ht="80" customHeight="1" s="109">
+      <c r="A12" s="112" t="n"/>
+      <c r="B12" s="112" t="n"/>
       <c r="C12" s="64" t="inlineStr">
         <is>
-          <t>F-WLD-01</t>
+          <t>F-ACT-09</t>
         </is>
       </c>
       <c r="D12" s="73" t="inlineStr">
         <is>
-          <t>세계관 생성·수정</t>
+          <t>기기 관리·전체 로그아웃</t>
         </is>
       </c>
       <c r="E12" s="73" t="inlineStr">
         <is>
-          <t>사용자는 작품과 별도로 새 세계관을 만들고 설명을 입력하거나 기존 세계관 정보를 수정·조회할 수 있어야 합니다.</t>
+          <t>회원은 로그인한 기기 목록을 확인하고 특정 기기 또는 모든 기기에서 로그아웃할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F12" s="96" t="inlineStr">
         <is>
-          <t>필수 항목은 세계관 이름만(확정). 플랫폼이 제공하는 장르 기본 세계관에서 복사해 시작 가능(원본 관계 없음, 운영자 관리, 장르 목록 미정). 기존 세계관 여러 개에서 항목을 골라 새 세계관을 조합할 수 있으며, 다른 사용자 세계관이 섞이면 세계관 Fork로 출처 기록. 연결 작품이 없을 때만 삭제 가능하며, Fork 등이 참조하는 버전은 보관하고 참조자에게 자기 세계관으로 옮기도록 안내. 인물관계도는 세계관의 일부.</t>
+          <t>해당 갱신 토큰 폐기(확정).</t>
         </is>
       </c>
       <c r="G12" s="73" t="inlineStr">
         <is>
-          <t>UC-02</t>
+          <t>UC-22</t>
         </is>
       </c>
       <c r="H12" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>지원 기획 / 인증 정책 확정·약관 미정</t>
         </is>
       </c>
       <c r="I12" s="73" t="inlineStr">
@@ -1558,7 +1554,7 @@
       </c>
       <c r="J12" s="73" t="inlineStr">
         <is>
-          <t>2.5·2.6 (저장 기반) / 구현 작업 미분해</t>
+          <t>5.7 관련 / 세부 작업 미분해</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1578,26 +1574,34 @@
       <c r="Y12" s="2" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1" s="109">
-      <c r="A13" s="112" t="n"/>
-      <c r="B13" s="112" t="n"/>
-      <c r="C13" s="65" t="inlineStr">
-        <is>
-          <t>F-WLD-02</t>
-        </is>
-      </c>
-      <c r="D13" s="75" t="inlineStr">
-        <is>
-          <t>세계관 요소 관리</t>
-        </is>
-      </c>
-      <c r="E13" s="75" t="inlineStr">
-        <is>
-          <t>장소·시대·규칙·주요 사건·세력·참고 자료를 세계관 항목으로 등록하고 관리할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F13" s="97" t="inlineStr">
-        <is>
-          <t>세계관·인물관계도는 Gitea로 변경 이력 관리(확정)</t>
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>REQ02</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>세계관·작품 관리</t>
+        </is>
+      </c>
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>F-WLD-01</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>세계관 생성·수정</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>사용자는 작품과 별도로 새 세계관을 만들고 설명을 입력하거나 기존 세계관 정보를 수정·조회할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F13" s="68" t="inlineStr">
+        <is>
+          <t>필수 항목은 세계관 이름만(확정). 플랫폼이 제공하는 장르 기본 세계관에서 복사해 시작 가능(원본 관계 없음, 운영자 관리, 장르 목록 미정). 기존 세계관 여러 개에서 항목을 골라 새 세계관을 조합할 수 있으며, 다른 사용자 세계관이 섞이면 세계관 Fork로 출처 기록. 연결 작품이 없을 때만 삭제 가능하며, Fork 등이 참조하는 버전은 보관하고 참조자에게 자기 세계관으로 옮기도록 안내. 인물관계도는 세계관의 일부.</t>
         </is>
       </c>
       <c r="G13" s="73" t="inlineStr">
@@ -1636,32 +1640,32 @@
       <c r="X13" s="2" t="n"/>
       <c r="Y13" s="2" t="n"/>
     </row>
-    <row r="14" ht="97" customHeight="1" s="109">
+    <row r="14" ht="64" customHeight="1" s="109">
       <c r="A14" s="112" t="n"/>
       <c r="B14" s="112" t="n"/>
-      <c r="C14" s="66" t="inlineStr">
-        <is>
-          <t>F-WLD-03</t>
-        </is>
-      </c>
-      <c r="D14" s="77" t="inlineStr">
-        <is>
-          <t>작품 생성 및 세계관 연결</t>
-        </is>
-      </c>
-      <c r="E14" s="77" t="inlineStr">
-        <is>
-          <t>사용자는 작품을 생성할 때 자신이 소유하거나 이용이 허용된 세계관을 1~5개 연결해야 합니다. 세계관 없이 작품을 만들 수 없으며, 공개 세계관 이용이 해당 세계관 정본의 수정 권한을 부여하지는 않습니다.</t>
-        </is>
-      </c>
-      <c r="F14" s="98" t="inlineStr">
-        <is>
-          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 단, 연결한 다른 사용자 세계관을 자기 세계관 Fork로 교체하는 것은 발행 후에도 허용(연결 수 유지). 세계관 Fork를 허용하지 않은 세계관만 연결하면 작가 소유 세계관도 함께 연결하도록 안내. 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>F-WLD-02</t>
+        </is>
+      </c>
+      <c r="D14" s="73" t="inlineStr">
+        <is>
+          <t>세계관 요소 관리</t>
+        </is>
+      </c>
+      <c r="E14" s="73" t="inlineStr">
+        <is>
+          <t>장소·시대·규칙·주요 사건·세력·참고 자료를 세계관 항목으로 등록하고 관리할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F14" s="96" t="inlineStr">
+        <is>
+          <t>세계관·인물관계도는 Gitea로 변경 이력 관리(확정)</t>
         </is>
       </c>
       <c r="G14" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-05</t>
+          <t>UC-02</t>
         </is>
       </c>
       <c r="H14" s="73" t="inlineStr">
@@ -1695,32 +1699,32 @@
       <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="n"/>
     </row>
-    <row r="15" ht="64" customHeight="1" s="109">
+    <row r="15" ht="97" customHeight="1" s="109">
       <c r="A15" s="112" t="n"/>
       <c r="B15" s="112" t="n"/>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>F-WLD-04</t>
+          <t>F-WLD-03</t>
         </is>
       </c>
       <c r="D15" s="73" t="inlineStr">
         <is>
-          <t>회차 구성 및 관리</t>
+          <t>작품 생성 및 세계관 연결</t>
         </is>
       </c>
       <c r="E15" s="73" t="inlineStr">
         <is>
-          <t>작품을 회차별로 구성하고 각 회차의 원고와 관련 인물·장소·사건을 등록·수정할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F15" s="99" t="inlineStr">
-        <is>
-          <t>회차(에피소드) 원고는 DB에 저장(확정)</t>
+          <t>사용자는 작품을 생성할 때 자신이 소유하거나 이용이 허용된 세계관을 1~5개 연결해야 합니다. 세계관 없이 작품을 만들 수 없으며, 공개 세계관 이용이 해당 세계관 정본의 수정 권한을 부여하지는 않습니다.</t>
+        </is>
+      </c>
+      <c r="F15" s="96" t="inlineStr">
+        <is>
+          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 단, 연결한 다른 사용자 세계관을 자기 세계관 Fork로 교체하는 것은 발행 후에도 허용(연결 수 유지). 세계관 Fork를 허용하지 않은 세계관만 연결하면 작가 소유 세계관도 함께 연결하도록 안내. 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
         </is>
       </c>
       <c r="G15" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-10, UC-13</t>
+          <t>UC-24, UC-05</t>
         </is>
       </c>
       <c r="H15" s="73" t="inlineStr">
@@ -1754,32 +1758,32 @@
       <c r="X15" s="2" t="n"/>
       <c r="Y15" s="2" t="n"/>
     </row>
-    <row r="16" ht="114" customHeight="1" s="109">
+    <row r="16" ht="64" customHeight="1" s="109">
       <c r="A16" s="112" t="n"/>
       <c r="B16" s="112" t="n"/>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>F-WLD-05</t>
+          <t>F-WLD-04</t>
         </is>
       </c>
       <c r="D16" s="73" t="inlineStr">
         <is>
-          <t>기존 원고 등록</t>
+          <t>회차 구성 및 관리</t>
         </is>
       </c>
       <c r="E16" s="73" t="inlineStr">
         <is>
-          <t>원고를 보유한 창작자는 기존 원고를 제공하고 읽힌 내용과 회차 구분·순서를 확인한 뒤 등록 범위를 확정할 수 있어야 합니다. 등록 성공과 실패 항목을 구분해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F16" s="99" t="inlineStr">
-        <is>
-          <t>외부 연재 원고 보유자 포함. 입력은 .txt 업로드 또는 STORYFORK 에디터 입력·붙여넣기만 지원(확정). 크기·회차 구분·중복 정책 미정. 등록은 공개·학습 동의·외부 동기화가 아닙니다.</t>
+          <t>작품을 회차별로 구성하고 각 회차의 원고와 관련 인물·장소·사건을 등록·수정할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F16" s="96" t="inlineStr">
+        <is>
+          <t>회차(에피소드) 원고는 DB에 저장(확정)</t>
         </is>
       </c>
       <c r="G16" s="73" t="inlineStr">
         <is>
-          <t>UC-03</t>
+          <t>UC-24, UC-10, UC-13</t>
         </is>
       </c>
       <c r="H16" s="73" t="inlineStr">
@@ -1813,32 +1817,32 @@
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="n"/>
     </row>
-    <row r="17" ht="97" customHeight="1" s="109">
+    <row r="17" ht="114" customHeight="1" s="109">
       <c r="A17" s="112" t="n"/>
       <c r="B17" s="112" t="n"/>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>F-WLD-06</t>
+          <t>F-WLD-05</t>
         </is>
       </c>
       <c r="D17" s="73" t="inlineStr">
         <is>
-          <t>원고 기반 설정 추출</t>
+          <t>기존 원고 등록</t>
         </is>
       </c>
       <c r="E17" s="73" t="inlineStr">
         <is>
-          <t>AI는 처리 권한이 확인된 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행합니다. 작품 설정이 자동이면 새 회차 발행 때 자동 반영하고, 이미 발행한 회차를 작가가 다시 발행하면 추출 후 작가가 확인한 항목만 반영합니다. 피드백 수정안 반영에 따른 재발행은 실행 대상이 아닙니다.</t>
-        </is>
-      </c>
-      <c r="F17" s="99" t="inlineStr">
-        <is>
-          <t>자동 모드 크레딧은 작품 소유자 부담. AI 실패와 등록 실패를 구분하며 기존 원고·확정 설정을 덮어쓰지 않습니다.</t>
+          <t>원고를 보유한 창작자는 기존 원고를 제공하고 읽힌 내용과 회차 구분·순서를 확인한 뒤 등록 범위를 확정할 수 있어야 합니다. 등록 성공과 실패 항목을 구분해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F17" s="96" t="inlineStr">
+        <is>
+          <t>외부 연재 원고 보유자 포함. 입력은 .txt·.epub(DRM 없는 파일, 이미지 포함) 업로드 또는 STORYFORK 에디터 입력·붙여넣기(확정). 회차 자동 구분(epub 챕터·txt 제목 줄), UTF-8·EUC-KR 판별, 재등록은 새 초안 버전, 한도 기준 txt 10MB·epub 50MB·300회차(확정, 구현 시 조정). 등록은 공개·학습 동의·외부 동기화가 아닙니다.</t>
         </is>
       </c>
       <c r="G17" s="73" t="inlineStr">
         <is>
-          <t>UC-04</t>
+          <t>UC-03</t>
         </is>
       </c>
       <c r="H17" s="73" t="inlineStr">
@@ -1872,27 +1876,27 @@
       <c r="X17" s="2" t="n"/>
       <c r="Y17" s="2" t="n"/>
     </row>
-    <row r="18" ht="64" customHeight="1" s="109">
+    <row r="18" ht="97" customHeight="1" s="109">
       <c r="A18" s="112" t="n"/>
       <c r="B18" s="112" t="n"/>
-      <c r="C18" s="65" t="inlineStr">
-        <is>
-          <t>F-WLD-07</t>
+      <c r="C18" s="64" t="inlineStr">
+        <is>
+          <t>F-WLD-06</t>
         </is>
       </c>
       <c r="D18" s="73" t="inlineStr">
         <is>
-          <t>추출 설정 검토·확정</t>
+          <t>원고 기반 설정 추출</t>
         </is>
       </c>
       <c r="E18" s="73" t="inlineStr">
         <is>
-          <t>수동 모드에서 사용자는 AI 추출 후보를 검토·수정하고 채택·제외할 항목을 선택하며, 확인한 설정만 저장해야 합니다. 자동 모드에서는 결과를 반영하되 변경 이력에 남기고, 기존 값과 충돌하는 항목은 덮어쓰지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F18" s="69" t="inlineStr">
-        <is>
-          <t>설정을 지우는 변경은 자동 삭제하지 않고 삭제 후보로 알림. 저장할 작가 소유 세계관이 없으면 자동으로 세계관 Fork를 만들지 않고 처음 한 번 작가 확인을 받음.</t>
+          <t>AI는 권리 제한이 없는 회차 원고에서 세계관·장소·인물·관계·사건·규칙 후보와 근거, 공개 전환 후보를 제시하고 불명확하거나 충돌하는 항목을 구분해야 합니다. 작가 요청 시(수동, 기본값) 실행합니다. 작품 설정이 자동이면 새 회차 발행 때 자동 반영하고, 이미 발행한 회차를 작가가 다시 발행하면 추출 후 작가가 확인한 항목만 반영합니다. 피드백 수정안 반영에 따른 재발행은 실행 대상이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="F18" s="96" t="inlineStr">
+        <is>
+          <t>자동 모드 크레딧은 작품 소유자 부담. AI 실패와 등록 실패를 구분하며 기존 원고·확정 설정을 덮어쓰지 않습니다.</t>
         </is>
       </c>
       <c r="G18" s="73" t="inlineStr">
@@ -1934,29 +1938,29 @@
     <row r="19" ht="64" customHeight="1" s="109">
       <c r="A19" s="112" t="n"/>
       <c r="B19" s="112" t="n"/>
-      <c r="C19" s="66" t="inlineStr">
-        <is>
-          <t>F-WLD-08</t>
-        </is>
-      </c>
-      <c r="D19" s="77" t="inlineStr">
-        <is>
-          <t>작품별 설정 변경 분리</t>
-        </is>
-      </c>
-      <c r="E19" s="77" t="inlineStr">
-        <is>
-          <t>공유 세계관을 바탕으로 창작하더라도 작품에서 발생한 사건과 설정 변경은 해당 작품에 독립적으로 저장되어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F19" s="68" t="inlineStr">
-        <is>
-          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 공개 항목만, 비공개 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경 알림·골라 가져오기는 미확정. 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>F-WLD-07</t>
+        </is>
+      </c>
+      <c r="D19" s="73" t="inlineStr">
+        <is>
+          <t>추출 설정 검토·확정</t>
+        </is>
+      </c>
+      <c r="E19" s="73" t="inlineStr">
+        <is>
+          <t>수동 모드에서 사용자는 AI 추출 후보를 검토·수정하고 채택·제외할 항목을 선택하며, 확인한 설정만 저장해야 합니다. 자동 모드에서는 결과를 반영하되 변경 이력에 남기고, 기존 값과 충돌하는 항목은 덮어쓰지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F19" s="96" t="inlineStr">
+        <is>
+          <t>설정을 지우는 변경은 자동 삭제하지 않고 삭제 후보로 알림. 저장할 작가 소유 세계관이 없으면 자동으로 세계관 Fork를 만들지 않고 처음 한 번 작가 확인을 받음.</t>
         </is>
       </c>
       <c r="G19" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-05</t>
+          <t>UC-04</t>
         </is>
       </c>
       <c r="H19" s="73" t="inlineStr">
@@ -1991,35 +1995,31 @@
       <c r="Y19" s="2" t="n"/>
     </row>
     <row r="20" ht="64" customHeight="1" s="109">
-      <c r="A20" s="60" t="inlineStr">
-        <is>
-          <t>REQ03</t>
-        </is>
-      </c>
-      <c r="B20" s="60" t="inlineStr">
-        <is>
-          <t>캐릭터·관계 관리</t>
-        </is>
-      </c>
+      <c r="A20" s="112" t="n"/>
+      <c r="B20" s="112" t="n"/>
       <c r="C20" s="64" t="inlineStr">
         <is>
-          <t>F-CHR-01</t>
+          <t>F-WLD-08</t>
         </is>
       </c>
       <c r="D20" s="73" t="inlineStr">
         <is>
-          <t>캐릭터 프로필 관리</t>
+          <t>작품별 설정 변경 분리</t>
         </is>
       </c>
       <c r="E20" s="73" t="inlineStr">
         <is>
-          <t>등장인물별 성격·목표·기억·능력·역할 등 프로필 정보를 등록·수정·조회할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F20" s="99" t="n"/>
+          <t>공유 세계관을 바탕으로 창작하더라도 작품에서 발생한 사건과 설정 변경은 해당 작품에 독립적으로 저장되어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F20" s="96" t="inlineStr">
+        <is>
+          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 공개 항목만, 비공개 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경 알림·골라 가져오기는 미확정. 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
+        </is>
+      </c>
       <c r="G20" s="73" t="inlineStr">
         <is>
-          <t>UC-06</t>
+          <t>UC-24, UC-05</t>
         </is>
       </c>
       <c r="H20" s="73" t="inlineStr">
@@ -2053,37 +2053,37 @@
       <c r="X20" s="2" t="n"/>
       <c r="Y20" s="2" t="n"/>
     </row>
-    <row r="21" ht="64" customHeight="1" s="109">
+    <row r="21" ht="80" customHeight="1" s="109">
       <c r="A21" s="112" t="n"/>
       <c r="B21" s="112" t="n"/>
       <c r="C21" s="64" t="inlineStr">
         <is>
-          <t>F-CHR-02</t>
+          <t>F-WLD-09</t>
         </is>
       </c>
       <c r="D21" s="73" t="inlineStr">
         <is>
-          <t>인물 간 관계 관리</t>
+          <t>.epub 원고 가져오기</t>
         </is>
       </c>
       <c r="E21" s="73" t="inlineStr">
         <is>
-          <t>등장인물 간 관계를 정의하고 작품 진행에 따른 관계 정보를 확인할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F21" s="100" t="inlineStr">
-        <is>
-          <t>인물관계도는 세계관의 일부(확정). 인물관계도만 바꾸려면 인물관계도만 담은 세계관을 만들어 연결하며, Fork에서도 같은 방식으로 정리.</t>
+          <t>창작자는 DRM이 없는 .epub 파일을 올려 챕터를 회차로 나누고 본문 이미지 위치를 유지한 채 등록할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F21" s="96" t="inlineStr">
+        <is>
+          <t>DRM 파일·지원하지 않는 이미지는 실패로 구분(확정). 이미지 저장 위치 미정.</t>
         </is>
       </c>
       <c r="G21" s="73" t="inlineStr">
         <is>
-          <t>UC-06</t>
+          <t>UC-03</t>
         </is>
       </c>
       <c r="H21" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I21" s="73" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J21" s="73" t="inlineStr">
         <is>
-          <t>2.5·2.6 (저장 기반) / 구현 작업 미분해</t>
+          <t>작업 미분해 (개발현황 GAP-09)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n"/>
@@ -2113,28 +2113,32 @@
       <c r="Y21" s="2" t="n"/>
     </row>
     <row r="22" ht="64" customHeight="1" s="109">
-      <c r="A22" s="112" t="n"/>
-      <c r="B22" s="112" t="n"/>
-      <c r="C22" s="66" t="inlineStr">
-        <is>
-          <t>F-CHR-03</t>
-        </is>
-      </c>
-      <c r="D22" s="77" t="inlineStr">
-        <is>
-          <t>회차별 상태 변화 기록</t>
-        </is>
-      </c>
-      <c r="E22" s="77" t="inlineStr">
-        <is>
-          <t>회차·사건 시점별 인물의 감정·관계·보유 정보 변화를 기록해야 합니다. 시뮬레이션의 임시 상태는 사용자 채택 없이 정본 상태에 반영하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F22" s="98" t="inlineStr">
-        <is>
-          <t>인물 기본 정보는 세계관과 함께 Gitea에 저장(확정). 회차 시점(설정 유효·독자 공개·인물별 인지 회차)은 세계관이 아니라 작품별로 기록(확정).</t>
-        </is>
-      </c>
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>REQ03</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>캐릭터·관계 관리</t>
+        </is>
+      </c>
+      <c r="C22" s="64" t="inlineStr">
+        <is>
+          <t>F-CHR-01</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>캐릭터 프로필 관리</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
+        <is>
+          <t>등장인물별 성격·목표·기억·능력·역할 등 프로필 정보를 등록·수정·조회할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F22" s="68" t="n"/>
       <c r="G22" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -2176,20 +2180,24 @@
       <c r="B23" s="112" t="n"/>
       <c r="C23" s="64" t="inlineStr">
         <is>
-          <t>F-CHR-04</t>
+          <t>F-CHR-02</t>
         </is>
       </c>
       <c r="D23" s="73" t="inlineStr">
         <is>
-          <t>시점별 인물 지식 관리</t>
+          <t>인물 간 관계 관리</t>
         </is>
       </c>
       <c r="E23" s="73" t="inlineStr">
         <is>
-          <t>특정 시점의 인물별 지식을 다른 인물의 지식, 작가 비공개 설정, 독자 공개 정보와 구분해야 합니다. 독자 공개 범위와 인물별 인지 여부는 별도 속성으로 관리하고 각 작업에 허용된 범위만 제공해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F23" s="99" t="n"/>
+          <t>등장인물 간 관계를 정의하고 작품 진행에 따른 관계 정보를 확인할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F23" s="96" t="inlineStr">
+        <is>
+          <t>인물관계도는 세계관의 일부(확정). 인물관계도만 바꾸려면 인물관계도만 담은 세계관을 만들어 연결하며, Fork에서도 같은 방식으로 정리.</t>
+        </is>
+      </c>
       <c r="G23" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -2231,20 +2239,24 @@
       <c r="B24" s="112" t="n"/>
       <c r="C24" s="64" t="inlineStr">
         <is>
-          <t>F-CHR-05</t>
+          <t>F-CHR-03</t>
         </is>
       </c>
       <c r="D24" s="73" t="inlineStr">
         <is>
-          <t>행동 가능 범위 관리</t>
+          <t>회차별 상태 변화 기록</t>
         </is>
       </c>
       <c r="E24" s="73" t="inlineStr">
         <is>
-          <t>인물의 지식·목표·능력에 따라 가능한 행동 범위를 관리하고 시뮬레이션에 제공해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F24" s="99" t="n"/>
+          <t>회차·사건 시점별 인물의 감정·관계·보유 정보 변화를 기록해야 합니다. 시뮬레이션의 임시 상태는 사용자 채택 없이 정본 상태에 반영하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F24" s="96" t="inlineStr">
+        <is>
+          <t>인물 기본 정보는 세계관과 함께 Gitea에 저장(확정). 회차 시점(설정 유효·독자 공개·인물별 인지 회차)은 세계관이 아니라 작품별로 기록(확정).</t>
+        </is>
+      </c>
       <c r="G24" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -2286,20 +2298,20 @@
       <c r="B25" s="112" t="n"/>
       <c r="C25" s="64" t="inlineStr">
         <is>
-          <t>F-CHR-06</t>
+          <t>F-CHR-04</t>
         </is>
       </c>
       <c r="D25" s="73" t="inlineStr">
         <is>
-          <t>인물 상태 이력 조회</t>
+          <t>시점별 인물 지식 관리</t>
         </is>
       </c>
       <c r="E25" s="73" t="inlineStr">
         <is>
-          <t>사용자는 회차 또는 특정 시점을 기준으로 인물의 프로필·관계·상태 이력을 조회할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F25" s="99" t="n"/>
+          <t>특정 시점의 인물별 지식을 다른 인물의 지식, 작가 비공개 설정, 독자 공개 정보와 구분해야 합니다. 독자 공개 범위와 인물별 인지 여부는 별도 속성으로 관리하고 각 작업에 허용된 범위만 제공해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F25" s="96" t="n"/>
       <c r="G25" s="73" t="inlineStr">
         <is>
           <t>UC-06</t>
@@ -2337,35 +2349,27 @@
       <c r="Y25" s="2" t="n"/>
     </row>
     <row r="26" ht="64" customHeight="1" s="109">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
-          <t>REQ04</t>
-        </is>
-      </c>
-      <c r="B26" s="60" t="inlineStr">
-        <is>
-          <t>작품 공개·열람</t>
-        </is>
-      </c>
+      <c r="A26" s="112" t="n"/>
+      <c r="B26" s="112" t="n"/>
       <c r="C26" s="64" t="inlineStr">
         <is>
-          <t>F-PUB-01</t>
+          <t>F-CHR-05</t>
         </is>
       </c>
       <c r="D26" s="73" t="inlineStr">
         <is>
-          <t>원작·Fork 작품 구분</t>
+          <t>행동 가능 범위 관리</t>
         </is>
       </c>
       <c r="E26" s="73" t="inlineStr">
         <is>
-          <t>작품 목록에서 원작과 사용자가 생성한 Fork 작품을 구분해 확인할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F26" s="99" t="n"/>
+          <t>인물의 지식·목표·능력에 따라 가능한 행동 범위를 관리하고 시뮬레이션에 제공해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F26" s="96" t="n"/>
       <c r="G26" s="73" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>UC-06</t>
         </is>
       </c>
       <c r="H26" s="73" t="inlineStr">
@@ -2380,7 +2384,7 @@
       </c>
       <c r="J26" s="73" t="inlineStr">
         <is>
-          <t>5.5 (열람 화면)</t>
+          <t>2.5·2.6 (저장 기반) / 구현 작업 미분해</t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2399,32 +2403,28 @@
       <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="n"/>
     </row>
-    <row r="27" ht="97" customHeight="1" s="109">
+    <row r="27" ht="64" customHeight="1" s="109">
       <c r="A27" s="112" t="n"/>
       <c r="B27" s="112" t="n"/>
       <c r="C27" s="64" t="inlineStr">
         <is>
-          <t>F-PUB-02</t>
+          <t>F-CHR-06</t>
         </is>
       </c>
       <c r="D27" s="73" t="inlineStr">
         <is>
-          <t>회차 공개 상태 관리</t>
+          <t>인물 상태 이력 조회</t>
         </is>
       </c>
       <c r="E27" s="73" t="inlineStr">
         <is>
-          <t>작품 소유자는 편집 중 초안과 독자에게 공개된 발행본을 구분하고, 공개 권한을 확인한 뒤 발행 절차를 수행할 수 있어야 합니다. 저장·AI 생성만으로 공개하지 않으며, 소유자가 켠 자동 처리(표기 오류 자동 승인·발행, 자율 연재)는 사전 승인으로 보고 같은 발행 확인을 거칩니다. 외부 2차 창작물은 유료 공개할 수 없습니다.</t>
-        </is>
-      </c>
-      <c r="F27" s="99" t="inlineStr">
-        <is>
-          <t>발행 후 수정·공개 철회·버전 노출·유료 열람 정책 미정. 등록 원고의 공개를 강제하지 않습니다.</t>
-        </is>
-      </c>
+          <t>사용자는 회차 또는 특정 시점을 기준으로 인물의 프로필·관계·상태 이력을 조회할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F27" s="96" t="n"/>
       <c r="G27" s="73" t="inlineStr">
         <is>
-          <t>UC-13</t>
+          <t>UC-06</t>
         </is>
       </c>
       <c r="H27" s="73" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="J27" s="73" t="inlineStr">
         <is>
-          <t>발행 API·화면 작업 미분해</t>
+          <t>2.5·2.6 (저장 기반) / 구현 작업 미분해</t>
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2459,24 +2459,32 @@
       <c r="Y27" s="2" t="n"/>
     </row>
     <row r="28" ht="64" customHeight="1" s="109">
-      <c r="A28" s="112" t="n"/>
-      <c r="B28" s="112" t="n"/>
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>REQ04</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>작품 공개·열람</t>
+        </is>
+      </c>
       <c r="C28" s="64" t="inlineStr">
         <is>
-          <t>F-PUB-03</t>
-        </is>
-      </c>
-      <c r="D28" s="73" t="inlineStr">
-        <is>
-          <t>공개 작품 열람</t>
-        </is>
-      </c>
-      <c r="E28" s="73" t="inlineStr">
-        <is>
-          <t>독자는 공개로 설정된 작품과 회차의 내용을 열람할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F28" s="99" t="n"/>
+          <t>F-PUB-01</t>
+        </is>
+      </c>
+      <c r="D28" s="70" t="inlineStr">
+        <is>
+          <t>원작·Fork 작품 구분</t>
+        </is>
+      </c>
+      <c r="E28" s="70" t="inlineStr">
+        <is>
+          <t>작품 목록에서 원작과 사용자가 생성한 Fork 작품을 구분해 확인할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F28" s="68" t="n"/>
       <c r="G28" s="73" t="inlineStr">
         <is>
           <t>UC-01</t>
@@ -2513,28 +2521,32 @@
       <c r="X28" s="2" t="n"/>
       <c r="Y28" s="2" t="n"/>
     </row>
-    <row r="29" ht="64" customHeight="1" s="109">
+    <row r="29" ht="97" customHeight="1" s="109">
       <c r="A29" s="112" t="n"/>
       <c r="B29" s="112" t="n"/>
-      <c r="C29" s="67" t="inlineStr">
-        <is>
-          <t>F-PUB-04</t>
-        </is>
-      </c>
-      <c r="D29" s="79" t="inlineStr">
-        <is>
-          <t>회차 순서 탐색</t>
-        </is>
-      </c>
-      <c r="E29" s="79" t="inlineStr">
-        <is>
-          <t>독자는 회차의 순서와 공개 여부를 확인하며 작품의 회차를 탐색할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F29" s="101" t="n"/>
+      <c r="C29" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-02</t>
+        </is>
+      </c>
+      <c r="D29" s="73" t="inlineStr">
+        <is>
+          <t>회차 공개 상태 관리</t>
+        </is>
+      </c>
+      <c r="E29" s="73" t="inlineStr">
+        <is>
+          <t>작품 소유자는 편집 중 초안과 독자에게 공개된 발행본을 구분하고, 공개 권한을 확인한 뒤 발행 절차를 수행할 수 있어야 합니다. 저장·AI 생성만으로 공개하지 않으며, 소유자가 켠 자동 처리(표기 오류 자동 승인·발행, 자율 연재)는 사전 승인으로 보고 같은 발행 확인을 거칩니다. 외부 2차 창작물은 유료 공개할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F29" s="96" t="inlineStr">
+        <is>
+          <t>발행 후 수정·공개 철회·버전 노출·유료 열람 정책 미정. 등록 원고의 공개를 강제하지 않습니다.</t>
+        </is>
+      </c>
       <c r="G29" s="73" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>UC-13</t>
         </is>
       </c>
       <c r="H29" s="73" t="inlineStr">
@@ -2549,7 +2561,7 @@
       </c>
       <c r="J29" s="73" t="inlineStr">
         <is>
-          <t>5.5 (열람 화면)</t>
+          <t>발행 API·화면 작업 미분해</t>
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2569,39 +2581,27 @@
       <c r="Y29" s="2" t="n"/>
     </row>
     <row r="30" ht="64" customHeight="1" s="109">
-      <c r="A30" s="60" t="inlineStr">
-        <is>
-          <t>REQ05</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="inlineStr">
-        <is>
-          <t>Fork 분기·창작</t>
-        </is>
-      </c>
-      <c r="C30" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-01</t>
-        </is>
-      </c>
-      <c r="D30" s="79" t="inlineStr">
-        <is>
-          <t>Fork 가능 작품 표시</t>
-        </is>
-      </c>
-      <c r="E30" s="79" t="inlineStr">
-        <is>
-          <t>Fork가 허용된 원작과 회차만 분기 후보로 사용자에게 보여야 합니다.</t>
-        </is>
-      </c>
-      <c r="F30" s="101" t="inlineStr">
-        <is>
-          <t>원작별 권리·허용 범위 확인 필요</t>
-        </is>
-      </c>
+      <c r="A30" s="112" t="n"/>
+      <c r="B30" s="112" t="n"/>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-03</t>
+        </is>
+      </c>
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>공개 작품 열람</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
+        <is>
+          <t>독자는 공개로 설정된 작품과 회차의 내용을 열람할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F30" s="96" t="n"/>
       <c r="G30" s="73" t="inlineStr">
         <is>
-          <t>UC-07, UC-08</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="H30" s="73" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="J30" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.8 (Fork 화면·API)</t>
+          <t>5.5 (열람 화면)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2638,29 +2638,25 @@
     <row r="31" ht="64" customHeight="1" s="109">
       <c r="A31" s="112" t="n"/>
       <c r="B31" s="112" t="n"/>
-      <c r="C31" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-02</t>
-        </is>
-      </c>
-      <c r="D31" s="79" t="inlineStr">
-        <is>
-          <t>Fork 권한 확인</t>
-        </is>
-      </c>
-      <c r="E31" s="79" t="inlineStr">
-        <is>
-          <t>Core API는 Fork 생성 전에 요청자의 접근 권한, 원작의 이용 조건, 원작 세계관의 공개 상태와 선택 회차의 Fork 허용 여부를 확인해야 합니다. 등록·허용 설정만으로 외부 IP의 적법한 이용권을 가정하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F31" s="101" t="inlineStr">
-        <is>
-          <t>원작에서만 Fork 가능, 한 독자는 한 원작에서 1번만, Fork 작품의 Fork 불가(확정, 관리 단순화). 권리 확인 절차·증빙 기준 정의 필요</t>
-        </is>
-      </c>
+      <c r="C31" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-04</t>
+        </is>
+      </c>
+      <c r="D31" s="73" t="inlineStr">
+        <is>
+          <t>회차 순서 탐색</t>
+        </is>
+      </c>
+      <c r="E31" s="73" t="inlineStr">
+        <is>
+          <t>독자는 회차의 순서와 공개 여부를 확인하며 작품의 회차를 탐색할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F31" s="96" t="n"/>
       <c r="G31" s="73" t="inlineStr">
         <is>
-          <t>UC-07, UC-08</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="H31" s="73" t="inlineStr">
@@ -2675,7 +2671,7 @@
       </c>
       <c r="J31" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.8 (Fork 화면·API)</t>
+          <t>5.5 (열람 화면)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2694,33 +2690,37 @@
       <c r="X31" s="2" t="n"/>
       <c r="Y31" s="2" t="n"/>
     </row>
-    <row r="32" ht="64" customHeight="1" s="109">
+    <row r="32" ht="80" customHeight="1" s="109">
       <c r="A32" s="112" t="n"/>
       <c r="B32" s="112" t="n"/>
-      <c r="C32" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-03</t>
-        </is>
-      </c>
-      <c r="D32" s="79" t="inlineStr">
-        <is>
-          <t>분기 시점 선택</t>
-        </is>
-      </c>
-      <c r="E32" s="79" t="inlineStr">
-        <is>
-          <t>독자는 허용된 범위에서 특정 회차의 종료 시점을 Fork 분기점으로 선택할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F32" s="101" t="n"/>
+      <c r="C32" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-05</t>
+        </is>
+      </c>
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>작품 검색·정렬</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>독자는 작품 제목·작가 닉네임·해시태그·장르로 작품을 검색하고 최신 발행순(기본)·좋아요순·조회순으로 정렬할 수 있어야 합니다. 열람 가능한 공개 작품만 결과에 표시합니다.</t>
+        </is>
+      </c>
+      <c r="F32" s="96" t="inlineStr">
+        <is>
+          <t>Elasticsearch 예정, 공개 정보만 색인, 본문 검색 제외(확정). 한국어 분석 방식은 구현 시 결정.</t>
+        </is>
+      </c>
       <c r="G32" s="73" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="H32" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I32" s="73" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="J32" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.8 (Fork 화면·API)</t>
+          <t>WBS 없음 (개발현황 GAP-08)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2749,37 +2749,37 @@
       <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="n"/>
     </row>
-    <row r="33" ht="97" customHeight="1" s="109">
+    <row r="33" ht="80" customHeight="1" s="109">
       <c r="A33" s="112" t="n"/>
       <c r="B33" s="112" t="n"/>
-      <c r="C33" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-04</t>
-        </is>
-      </c>
-      <c r="D33" s="79" t="inlineStr">
-        <is>
-          <t>분기 시점 설정 복제</t>
-        </is>
-      </c>
-      <c r="E33" s="79" t="inlineStr">
-        <is>
-          <t>Fork 생성 시 기준 회차까지의 회차 원고와 분기 시점의 세계관·인물관계도를 불변으로 고정해야 합니다. 분기 시점에 독자에게 공개된 항목만 포함하고 비공개 항목은 제외합니다.</t>
-        </is>
-      </c>
-      <c r="F33" s="101" t="inlineStr">
-        <is>
-          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 분기 시점 버전을 참조하는 원칙은 확정, Gitea 브랜치·커밋 참조 등 구현 수단은 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
+      <c r="C33" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-06</t>
+        </is>
+      </c>
+      <c r="D33" s="73" t="inlineStr">
+        <is>
+          <t>좋아요·관심 소설·이어 읽기</t>
+        </is>
+      </c>
+      <c r="E33" s="73" t="inlineStr">
+        <is>
+          <t>로그인한 독자는 작품 좋아요, 관심 소설 담기, 작품별 이어 읽기(마지막 회차·위치)를 이용할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F33" s="96" t="inlineStr">
+        <is>
+          <t>좋아요 수 공개·누른 사람 비공개, 관심 소설·이어 읽기는 본인만, 탈퇴 시 이어 읽기 삭제, 조회수는 사용자·회차별 하루 1회 집계, 감정 반응 없음(확정).</t>
         </is>
       </c>
       <c r="G33" s="73" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-01</t>
         </is>
       </c>
       <c r="H33" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I33" s="73" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J33" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.8 (Fork 화면·API)</t>
+          <t>5.5 관련 / 세부 작업 미분해</t>
         </is>
       </c>
       <c r="K33" s="2" t="n"/>
@@ -2808,33 +2808,37 @@
       <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="n"/>
     </row>
-    <row r="34" ht="64" customHeight="1" s="109">
+    <row r="34" ht="80" customHeight="1" s="109">
       <c r="A34" s="112" t="n"/>
       <c r="B34" s="112" t="n"/>
-      <c r="C34" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-05</t>
-        </is>
-      </c>
-      <c r="D34" s="79" t="inlineStr">
-        <is>
-          <t>독립 Fork 작품 생성</t>
-        </is>
-      </c>
-      <c r="E34" s="79" t="inlineStr">
-        <is>
-          <t>선택한 원작·기준 회차와 연결된 독립 Fork 작품을 생성할 수 있어야 합니다. 생성자는 자신의 Fork에서 창작자 권한을 가지며 원작 수정 권한은 얻지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F34" s="101" t="n"/>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>F-PUB-07</t>
+        </is>
+      </c>
+      <c r="D34" s="73" t="inlineStr">
+        <is>
+          <t>캐릭터 챗</t>
+        </is>
+      </c>
+      <c r="E34" s="73" t="inlineStr">
+        <is>
+          <t>독자는 열람한 회차까지 등장한 인물과 그 시점의 공개 정보 범위에서 대화할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F34" s="96" t="inlineStr">
+        <is>
+          <t>채택·MVP 제외(확정). 기준 회차·비용·기록 보관은 MVP 이후 확정.</t>
+        </is>
+      </c>
       <c r="G34" s="73" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-25</t>
         </is>
       </c>
       <c r="H34" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>채택·MVP 제외</t>
         </is>
       </c>
       <c r="I34" s="73" t="inlineStr">
@@ -2844,7 +2848,7 @@
       </c>
       <c r="J34" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.8 (Fork 화면·API)</t>
+          <t>MVP 범위 밖</t>
         </is>
       </c>
       <c r="K34" s="2" t="n"/>
@@ -2864,31 +2868,39 @@
       <c r="Y34" s="2" t="n"/>
     </row>
     <row r="35" ht="64" customHeight="1" s="109">
-      <c r="A35" s="112" t="n"/>
-      <c r="B35" s="112" t="n"/>
-      <c r="C35" s="67" t="inlineStr">
-        <is>
-          <t>F-FRK-06</t>
-        </is>
-      </c>
-      <c r="D35" s="79" t="inlineStr">
-        <is>
-          <t>원작과 Fork 상태 분리</t>
-        </is>
-      </c>
-      <c r="E35" s="79" t="inlineStr">
-        <is>
-          <t>분기 이후 사건·인물 상태는 Fork에 독립 저장되어 원작에 영향을 주지 않아야 합니다. 원작의 후속 수정·새 회차가 기존 Fork의 고정 기준에 자동 유입되지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F35" s="69" t="inlineStr">
-        <is>
-          <t>작품 운영 설정(세계관 업데이트·표기 오류 처리·자율 연재)과 공개 조건은 Fork에 넘기지 않음(확정). 분기 이후 설정 수정은 Fork 작품 전용 세계관에 저장하며 다른 작품에 연결·공개 불가. 원작이 빌려 쓴 다른 작가 세계관 항목은 그 작가가 세계관 Fork를 허용했을 때만 수정 가능하고 그 작가의 제한이 Fork에도 적용.</t>
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>REQ05</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="inlineStr">
+        <is>
+          <t>Fork 분기·창작</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>F-FRK-01</t>
+        </is>
+      </c>
+      <c r="D35" s="70" t="inlineStr">
+        <is>
+          <t>Fork 가능 작품 표시</t>
+        </is>
+      </c>
+      <c r="E35" s="70" t="inlineStr">
+        <is>
+          <t>Fork가 허용된 원작과 회차만 분기 후보로 사용자에게 보여야 합니다.</t>
+        </is>
+      </c>
+      <c r="F35" s="68" t="inlineStr">
+        <is>
+          <t>원작별 권리·허용 범위 확인 필요</t>
         </is>
       </c>
       <c r="G35" s="73" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-07, UC-08</t>
         </is>
       </c>
       <c r="H35" s="73" t="inlineStr">
@@ -2925,25 +2937,29 @@
     <row r="36" ht="64" customHeight="1" s="109">
       <c r="A36" s="112" t="n"/>
       <c r="B36" s="112" t="n"/>
-      <c r="C36" s="66" t="inlineStr">
-        <is>
-          <t>F-FRK-07</t>
-        </is>
-      </c>
-      <c r="D36" s="77" t="inlineStr">
-        <is>
-          <t>후속 전개 설정</t>
-        </is>
-      </c>
-      <c r="E36" s="77" t="inlineStr">
-        <is>
-          <t>사용자는 새로운 전개를 직접 입력하거나 시뮬레이션 결과를 선택해 Fork의 후속 이야기를 정할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F36" s="91" t="n"/>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>F-FRK-02</t>
+        </is>
+      </c>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>Fork 권한 확인</t>
+        </is>
+      </c>
+      <c r="E36" s="73" t="inlineStr">
+        <is>
+          <t>Core API는 Fork 생성 전에 요청자의 접근 권한, 원작의 이용 조건, 원작 세계관의 공개 상태와 선택 회차의 Fork 허용 여부를 확인해야 합니다. 등록·허용 설정만으로 외부 IP의 적법한 이용권을 가정하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F36" s="96" t="inlineStr">
+        <is>
+          <t>원작에서만 Fork 가능, 한 독자는 한 원작에서 1번만, Fork 작품의 Fork 불가(확정, 관리 단순화). 권리 확인 절차·증빙 기준 정의 필요</t>
+        </is>
+      </c>
       <c r="G36" s="73" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-07, UC-08</t>
         </is>
       </c>
       <c r="H36" s="73" t="inlineStr">
@@ -2978,35 +2994,27 @@
       <c r="Y36" s="2" t="n"/>
     </row>
     <row r="37" ht="64" customHeight="1" s="109">
-      <c r="A37" s="61" t="inlineStr">
-        <is>
-          <t>REQ06</t>
-        </is>
-      </c>
-      <c r="B37" s="63" t="inlineStr">
-        <is>
-          <t>다중 AI 시뮬레이션</t>
-        </is>
-      </c>
+      <c r="A37" s="112" t="n"/>
+      <c r="B37" s="112" t="n"/>
       <c r="C37" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-01</t>
+          <t>F-FRK-03</t>
         </is>
       </c>
       <c r="D37" s="73" t="inlineStr">
         <is>
-          <t>상황·사건 입력</t>
+          <t>분기 시점 선택</t>
         </is>
       </c>
       <c r="E37" s="73" t="inlineStr">
         <is>
-          <t>사용자는 시뮬레이션에서 발생시킬 사건과 상황을 입력할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F37" s="102" t="n"/>
+          <t>독자는 허용된 범위에서 특정 회차의 종료 시점을 Fork 분기점으로 선택할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F37" s="96" t="n"/>
       <c r="G37" s="73" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="H37" s="73" t="inlineStr">
@@ -3021,7 +3029,7 @@
       </c>
       <c r="J37" s="73" t="inlineStr">
         <is>
-          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
+          <t>5.5·5.8 (Fork 화면·API)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3040,28 +3048,32 @@
       <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="n"/>
     </row>
-    <row r="38" ht="64" customHeight="1" s="109">
+    <row r="38" ht="97" customHeight="1" s="109">
       <c r="A38" s="112" t="n"/>
-      <c r="B38" s="113" t="n"/>
+      <c r="B38" s="112" t="n"/>
       <c r="C38" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-02</t>
+          <t>F-FRK-04</t>
         </is>
       </c>
       <c r="D38" s="73" t="inlineStr">
         <is>
-          <t>시뮬레이션 조건 설정</t>
+          <t>분기 시점 설정 복제</t>
         </is>
       </c>
       <c r="E38" s="73" t="inlineStr">
         <is>
-          <t>사용자는 시뮬레이션 장소·참여 인물·원하는 전개 방향을 지정할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F38" s="102" t="n"/>
+          <t>Fork 생성 시 기준 회차까지의 회차 원고와 분기 시점의 세계관·인물관계도를 불변으로 고정해야 합니다. 분기 시점에 독자에게 공개된 항목만 포함하고 비공개 항목은 제외합니다.</t>
+        </is>
+      </c>
+      <c r="F38" s="96" t="inlineStr">
+        <is>
+          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 분기 시점 버전을 참조하는 원칙은 확정, Gitea 브랜치·커밋 참조 등 구현 수단은 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
+        </is>
+      </c>
       <c r="G38" s="73" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="H38" s="73" t="inlineStr">
@@ -3076,7 +3088,7 @@
       </c>
       <c r="J38" s="73" t="inlineStr">
         <is>
-          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
+          <t>5.5·5.8 (Fork 화면·API)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3097,26 +3109,26 @@
     </row>
     <row r="39" ht="64" customHeight="1" s="109">
       <c r="A39" s="112" t="n"/>
-      <c r="B39" s="113" t="n"/>
+      <c r="B39" s="112" t="n"/>
       <c r="C39" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-03</t>
+          <t>F-FRK-05</t>
         </is>
       </c>
       <c r="D39" s="73" t="inlineStr">
         <is>
-          <t>스토리 계획 에이전트 구성</t>
+          <t>독립 Fork 작품 생성</t>
         </is>
       </c>
       <c r="E39" s="73" t="inlineStr">
         <is>
-          <t>스토리 계획 에이전트는 역할·목표·환경을 구성하고 사건과 전체 진행 흐름을 관리해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F39" s="102" t="n"/>
+          <t>선택한 원작·기준 회차와 연결된 독립 Fork 작품을 생성할 수 있어야 합니다. 생성자는 자신의 Fork에서 창작자 권한을 가지며 원작 수정 권한은 얻지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F39" s="96" t="n"/>
       <c r="G39" s="73" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="H39" s="73" t="inlineStr">
@@ -3131,7 +3143,7 @@
       </c>
       <c r="J39" s="73" t="inlineStr">
         <is>
-          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
+          <t>5.5·5.8 (Fork 화면·API)</t>
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3152,26 +3164,30 @@
     </row>
     <row r="40" ht="64" customHeight="1" s="109">
       <c r="A40" s="112" t="n"/>
-      <c r="B40" s="113" t="n"/>
+      <c r="B40" s="112" t="n"/>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-04</t>
+          <t>F-FRK-06</t>
         </is>
       </c>
       <c r="D40" s="73" t="inlineStr">
         <is>
-          <t>캐릭터별 에이전트 구성</t>
+          <t>원작과 Fork 상태 분리</t>
         </is>
       </c>
       <c r="E40" s="73" t="inlineStr">
         <is>
-          <t>캐릭터별 AI 역할은 해당 인물의 성격·목표·기억과 기준 시점에 알고 있는 사실만으로 구성해야 합니다. 다른 인물의 비밀이나 미래 사건을 전달하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F40" s="102" t="n"/>
+          <t>분기 이후 사건·인물 상태는 Fork에 독립 저장되어 원작에 영향을 주지 않아야 합니다. 원작의 후속 수정·새 회차가 기존 Fork의 고정 기준에 자동 유입되지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F40" s="96" t="inlineStr">
+        <is>
+          <t>작품 운영 설정(세계관 업데이트·표기 오류 처리·자율 연재)과 공개 조건은 Fork에 넘기지 않음(확정). 분기 이후 설정 수정은 Fork 작품 전용 세계관에 저장하며 다른 작품에 연결·공개 불가. 원작이 빌려 쓴 다른 작가 세계관 항목은 그 작가가 세계관 Fork를 허용했을 때만 수정 가능하고 그 작가의 제한이 Fork에도 적용.</t>
+        </is>
+      </c>
       <c r="G40" s="73" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="H40" s="73" t="inlineStr">
@@ -3186,7 +3202,7 @@
       </c>
       <c r="J40" s="73" t="inlineStr">
         <is>
-          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
+          <t>5.5·5.8 (Fork 화면·API)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n"/>
@@ -3207,26 +3223,26 @@
     </row>
     <row r="41" ht="64" customHeight="1" s="109">
       <c r="A41" s="112" t="n"/>
-      <c r="B41" s="113" t="n"/>
+      <c r="B41" s="112" t="n"/>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-05</t>
+          <t>F-FRK-07</t>
         </is>
       </c>
       <c r="D41" s="73" t="inlineStr">
         <is>
-          <t>인물 자율 행동·대화</t>
+          <t>후속 전개 설정</t>
         </is>
       </c>
       <c r="E41" s="73" t="inlineStr">
         <is>
-          <t>캐릭터 에이전트는 보유 설정을 바탕으로 자율 판단하고 대화하며 다른 인물과 상호작용해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F41" s="102" t="n"/>
+          <t>사용자는 새로운 전개를 직접 입력하거나 시뮬레이션 결과를 선택해 Fork의 후속 이야기를 정할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F41" s="96" t="n"/>
       <c r="G41" s="73" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-08</t>
         </is>
       </c>
       <c r="H41" s="73" t="inlineStr">
@@ -3241,7 +3257,7 @@
       </c>
       <c r="J41" s="73" t="inlineStr">
         <is>
-          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
+          <t>5.5·5.8 (Fork 화면·API)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -3261,24 +3277,32 @@
       <c r="Y41" s="2" t="n"/>
     </row>
     <row r="42" ht="64" customHeight="1" s="109">
-      <c r="A42" s="112" t="n"/>
-      <c r="B42" s="113" t="n"/>
+      <c r="A42" s="50" t="inlineStr">
+        <is>
+          <t>REQ06</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="inlineStr">
+        <is>
+          <t>다중 AI 시뮬레이션</t>
+        </is>
+      </c>
       <c r="C42" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-06</t>
-        </is>
-      </c>
-      <c r="D42" s="73" t="inlineStr">
-        <is>
-          <t>시뮬레이션 진행 기록</t>
-        </is>
-      </c>
-      <c r="E42" s="73" t="inlineStr">
-        <is>
-          <t>사용자는 시뮬레이션에서 발생한 인물 행동·대화와 사건 진행 기록을 결과에서 확인할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F42" s="102" t="n"/>
+          <t>F-SIM-01</t>
+        </is>
+      </c>
+      <c r="D42" s="70" t="inlineStr">
+        <is>
+          <t>상황·사건 입력</t>
+        </is>
+      </c>
+      <c r="E42" s="70" t="inlineStr">
+        <is>
+          <t>사용자는 시뮬레이션에서 발생시킬 사건과 상황을 입력할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F42" s="68" t="n"/>
       <c r="G42" s="73" t="inlineStr">
         <is>
           <t>UC-09</t>
@@ -3317,23 +3341,23 @@
     </row>
     <row r="43" ht="64" customHeight="1" s="109">
       <c r="A43" s="112" t="n"/>
-      <c r="B43" s="113" t="n"/>
+      <c r="B43" s="112" t="n"/>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-07</t>
+          <t>F-SIM-02</t>
         </is>
       </c>
       <c r="D43" s="73" t="inlineStr">
         <is>
-          <t>대안 전개 후보 생성</t>
+          <t>시뮬레이션 조건 설정</t>
         </is>
       </c>
       <c r="E43" s="73" t="inlineStr">
         <is>
-          <t>같은 상황을 바탕으로 서로 다른 이야기 전개 후보를 여러 개 생성해 비교할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F43" s="102" t="n"/>
+          <t>사용자는 시뮬레이션 장소·참여 인물·원하는 전개 방향을 지정할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F43" s="96" t="n"/>
       <c r="G43" s="73" t="inlineStr">
         <is>
           <t>UC-09</t>
@@ -3372,23 +3396,23 @@
     </row>
     <row r="44" ht="64" customHeight="1" s="109">
       <c r="A44" s="112" t="n"/>
-      <c r="B44" s="113" t="n"/>
-      <c r="C44" s="65" t="inlineStr">
-        <is>
-          <t>F-SIM-08</t>
-        </is>
-      </c>
-      <c r="D44" s="75" t="inlineStr">
-        <is>
-          <t>사건 인과관계 확인</t>
-        </is>
-      </c>
-      <c r="E44" s="75" t="inlineStr">
-        <is>
-          <t>사용자는 시뮬레이션 결과에서 사건 간 원인과 결과, 인물 행동의 연결을 확인할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F44" s="103" t="n"/>
+      <c r="B44" s="112" t="n"/>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-03</t>
+        </is>
+      </c>
+      <c r="D44" s="73" t="inlineStr">
+        <is>
+          <t>스토리 계획 에이전트 구성</t>
+        </is>
+      </c>
+      <c r="E44" s="73" t="inlineStr">
+        <is>
+          <t>스토리 계획 에이전트는 역할·목표·환경을 구성하고 사건과 전체 진행 흐름을 관리해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F44" s="96" t="n"/>
       <c r="G44" s="73" t="inlineStr">
         <is>
           <t>UC-09</t>
@@ -3427,26 +3451,26 @@
     </row>
     <row r="45" ht="64" customHeight="1" s="109">
       <c r="A45" s="112" t="n"/>
-      <c r="B45" s="113" t="n"/>
-      <c r="C45" s="66" t="inlineStr">
-        <is>
-          <t>F-SIM-09</t>
-        </is>
-      </c>
-      <c r="D45" s="77" t="inlineStr">
-        <is>
-          <t>설정 일관성 검토</t>
-        </is>
-      </c>
-      <c r="E45" s="77" t="inlineStr">
-        <is>
-          <t>시뮬레이션 결과를 기존 세계관·캐릭터 설정과 대조해 일관성 및 충돌 여부를 검토해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F45" s="104" t="n"/>
+      <c r="B45" s="112" t="n"/>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-04</t>
+        </is>
+      </c>
+      <c r="D45" s="73" t="inlineStr">
+        <is>
+          <t>캐릭터별 에이전트 구성</t>
+        </is>
+      </c>
+      <c r="E45" s="73" t="inlineStr">
+        <is>
+          <t>캐릭터별 AI 역할은 해당 인물의 성격·목표·기억과 기준 시점에 알고 있는 사실만으로 구성해야 합니다. 다른 인물의 비밀이나 미래 사건을 전달하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F45" s="96" t="n"/>
       <c r="G45" s="73" t="inlineStr">
         <is>
-          <t>UC-09, UC-12</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="H45" s="73" t="inlineStr">
@@ -3461,7 +3485,7 @@
       </c>
       <c r="J45" s="73" t="inlineStr">
         <is>
-          <t>4.7 (설정 검토) / 화면·API 미분해</t>
+          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K45" s="2" t="n"/>
@@ -3480,32 +3504,28 @@
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="n"/>
     </row>
-    <row r="46" ht="80" customHeight="1" s="109">
-      <c r="A46" s="114" t="n"/>
-      <c r="B46" s="115" t="n"/>
+    <row r="46" ht="64" customHeight="1" s="109">
+      <c r="A46" s="112" t="n"/>
+      <c r="B46" s="112" t="n"/>
       <c r="C46" s="64" t="inlineStr">
         <is>
-          <t>F-SIM-10</t>
+          <t>F-SIM-05</t>
         </is>
       </c>
       <c r="D46" s="73" t="inlineStr">
         <is>
-          <t>선택 결과 집필 전달</t>
+          <t>인물 자율 행동·대화</t>
         </is>
       </c>
       <c r="E46" s="73" t="inlineStr">
         <is>
-          <t>사용자는 검토한 전개 후보를 선택·수정·폐기하고 채택한 결과만 집필 재료로 전달할 수 있어야 합니다. 임시 사건·기억·관계 변화는 정본에 자동 반영하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F46" s="96" t="inlineStr">
-        <is>
-          <t>실패·시간 초과·미완료와 완료를 구분합니다. 취소·부분 결과 보관·실행 한도는 미정입니다.</t>
-        </is>
-      </c>
+          <t>캐릭터 에이전트는 보유 설정을 바탕으로 자율 판단하고 대화하며 다른 인물과 상호작용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F46" s="96" t="n"/>
       <c r="G46" s="73" t="inlineStr">
         <is>
-          <t>UC-09, UC-10, UC-11</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="H46" s="73" t="inlineStr">
@@ -3539,40 +3559,28 @@
       <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="n"/>
     </row>
-    <row r="47" ht="80" customHeight="1" s="109">
-      <c r="A47" s="54" t="inlineStr">
-        <is>
-          <t>REQ07</t>
-        </is>
-      </c>
-      <c r="B47" s="55" t="inlineStr">
-        <is>
-          <t>원고 작성·편집</t>
-        </is>
-      </c>
-      <c r="C47" s="66" t="inlineStr">
-        <is>
-          <t>F-WRT-01</t>
-        </is>
-      </c>
-      <c r="D47" s="77" t="inlineStr">
-        <is>
-          <t>직접 집필</t>
-        </is>
-      </c>
-      <c r="E47" s="77" t="inlineStr">
-        <is>
-          <t>편집 권한이 있는 사용자는 AI 없이 원작 또는 자신의 Fork 원고를 직접 작성·수정·저장할 수 있어야 합니다. 저장 실패와 미저장을 표시하며 기존 저장본을 보존해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F47" s="105" t="inlineStr">
-        <is>
-          <t>Fork 생성·직접 집필은 무료 기획 방향. 편집 형식·자동 저장·동시 편집·원고 내보내기(TXT 등) 정책 미정.</t>
-        </is>
-      </c>
+    <row r="47" ht="64" customHeight="1" s="109">
+      <c r="A47" s="112" t="n"/>
+      <c r="B47" s="112" t="n"/>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-06</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr">
+        <is>
+          <t>시뮬레이션 진행 기록</t>
+        </is>
+      </c>
+      <c r="E47" s="73" t="inlineStr">
+        <is>
+          <t>사용자는 시뮬레이션에서 발생한 인물 행동·대화와 사건 진행 기록을 결과에서 확인할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F47" s="96" t="n"/>
       <c r="G47" s="73" t="inlineStr">
         <is>
-          <t>UC-10</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="H47" s="73" t="inlineStr">
@@ -3587,7 +3595,7 @@
       </c>
       <c r="J47" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3611,23 +3619,23 @@
       <c r="B48" s="112" t="n"/>
       <c r="C48" s="64" t="inlineStr">
         <is>
-          <t>F-WRT-02</t>
+          <t>F-SIM-07</t>
         </is>
       </c>
       <c r="D48" s="73" t="inlineStr">
         <is>
-          <t>AI 협업 집필 방향 설정</t>
-        </is>
-      </c>
-      <c r="E48" s="77" t="inlineStr">
-        <is>
-          <t>AI 협업 집필에서 사용자는 원하는 이야기 방향을 결정하고 AI에게 작성 지원을 요청할 수 있어야 합니다.</t>
+          <t>대안 전개 후보 생성</t>
+        </is>
+      </c>
+      <c r="E48" s="73" t="inlineStr">
+        <is>
+          <t>같은 상황을 바탕으로 서로 다른 이야기 전개 후보를 여러 개 생성해 비교할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F48" s="96" t="n"/>
       <c r="G48" s="73" t="inlineStr">
         <is>
-          <t>UC-11</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="H48" s="73" t="inlineStr">
@@ -3642,7 +3650,7 @@
       </c>
       <c r="J48" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K48" s="2" t="n"/>
@@ -3666,23 +3674,23 @@
       <c r="B49" s="112" t="n"/>
       <c r="C49" s="64" t="inlineStr">
         <is>
-          <t>F-WRT-03</t>
+          <t>F-SIM-08</t>
         </is>
       </c>
       <c r="D49" s="73" t="inlineStr">
         <is>
-          <t>장면·대화·원고 생성</t>
+          <t>사건 인과관계 확인</t>
         </is>
       </c>
       <c r="E49" s="73" t="inlineStr">
         <is>
-          <t>AI는 사용자의 집필 요청과 작품 정보를 바탕으로 장면·대화·원고 초안을 생성할 수 있어야 합니다.</t>
+          <t>사용자는 시뮬레이션 결과에서 사건 간 원인과 결과, 인물 행동의 연결을 확인할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F49" s="96" t="n"/>
       <c r="G49" s="73" t="inlineStr">
         <is>
-          <t>UC-11</t>
+          <t>UC-09</t>
         </is>
       </c>
       <c r="H49" s="73" t="inlineStr">
@@ -3697,7 +3705,7 @@
       </c>
       <c r="J49" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K49" s="2" t="n"/>
@@ -3719,25 +3727,25 @@
     <row r="50" ht="64" customHeight="1" s="109">
       <c r="A50" s="112" t="n"/>
       <c r="B50" s="112" t="n"/>
-      <c r="C50" s="65" t="inlineStr">
-        <is>
-          <t>F-WRT-04</t>
-        </is>
-      </c>
-      <c r="D50" s="75" t="inlineStr">
-        <is>
-          <t>AI 원고 수정 지원</t>
-        </is>
-      </c>
-      <c r="E50" s="75" t="inlineStr">
-        <is>
-          <t>사용자는 AI 원고 제안을 검토·수정·거절하고 선택한 부분만 편집 초안에 반영할 수 있어야 합니다. 생성 완료와 실제 저장·승인·발행 완료를 구분해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F50" s="97" t="n"/>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-09</t>
+        </is>
+      </c>
+      <c r="D50" s="73" t="inlineStr">
+        <is>
+          <t>설정 일관성 검토</t>
+        </is>
+      </c>
+      <c r="E50" s="73" t="inlineStr">
+        <is>
+          <t>시뮬레이션 결과를 기존 세계관·캐릭터 설정과 대조해 일관성 및 충돌 여부를 검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F50" s="96" t="n"/>
       <c r="G50" s="73" t="inlineStr">
         <is>
-          <t>UC-11</t>
+          <t>UC-09, UC-12</t>
         </is>
       </c>
       <c r="H50" s="73" t="inlineStr">
@@ -3752,7 +3760,7 @@
       </c>
       <c r="J50" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.7 (설정 검토) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3771,25 +3779,29 @@
       <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="n"/>
     </row>
-    <row r="51" ht="64" customHeight="1" s="109">
+    <row r="51" ht="80" customHeight="1" s="109">
       <c r="A51" s="112" t="n"/>
       <c r="B51" s="112" t="n"/>
-      <c r="C51" s="66" t="inlineStr">
-        <is>
-          <t>F-WRT-05</t>
-        </is>
-      </c>
-      <c r="D51" s="77" t="inlineStr">
-        <is>
-          <t>시뮬레이션 결과 활용</t>
-        </is>
-      </c>
-      <c r="E51" s="106" t="inlineStr">
-        <is>
-          <t>사용자는 선택한 시뮬레이션 결과를 원고의 사건·장면·대화 작성에 활용할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F51" s="105" t="n"/>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-10</t>
+        </is>
+      </c>
+      <c r="D51" s="73" t="inlineStr">
+        <is>
+          <t>선택 결과 집필 전달</t>
+        </is>
+      </c>
+      <c r="E51" s="73" t="inlineStr">
+        <is>
+          <t>사용자는 검토한 전개 후보를 선택·수정·폐기하고 채택한 결과만 집필 재료로 전달할 수 있어야 합니다. 임시 사건·기억·관계 변화는 정본에 자동 반영하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F51" s="96" t="inlineStr">
+        <is>
+          <t>실패·시간 초과·미완료와 완료를 구분합니다. 취소·부분 결과 보관·실행 한도는 미정입니다.</t>
+        </is>
+      </c>
       <c r="G51" s="73" t="inlineStr">
         <is>
           <t>UC-09, UC-10, UC-11</t>
@@ -3807,7 +3819,7 @@
       </c>
       <c r="J51" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.8 (인물·스토리 AI) / 화면·API 미분해</t>
         </is>
       </c>
       <c r="K51" s="2" t="n"/>
@@ -3826,33 +3838,37 @@
       <c r="X51" s="2" t="n"/>
       <c r="Y51" s="2" t="n"/>
     </row>
-    <row r="52" ht="64" customHeight="1" s="109">
+    <row r="52" ht="80" customHeight="1" s="109">
       <c r="A52" s="112" t="n"/>
       <c r="B52" s="112" t="n"/>
-      <c r="C52" s="50" t="inlineStr">
-        <is>
-          <t>F-WRT-06</t>
-        </is>
-      </c>
-      <c r="D52" s="88" t="inlineStr">
-        <is>
-          <t>세계관·캐릭터 설정 활용</t>
-        </is>
-      </c>
-      <c r="E52" s="89" t="inlineStr">
-        <is>
-          <t>AI 집필 지원은 현재 작품·기준 시점에서 사용이 허용된 세계관·캐릭터·원고와 선택된 시뮬레이션 결과를 필요한 범위만 참고해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F52" s="107" t="n"/>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>F-SIM-11</t>
+        </is>
+      </c>
+      <c r="D52" s="73" t="inlineStr">
+        <is>
+          <t>독자 스토리 오류 검증 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="E52" s="73" t="inlineStr">
+        <is>
+          <t>독자는 스토리 오류를 제보하기 전에 자기 크레딧으로 검증 시뮬레이션을 실행해 오류 가능성·신뢰도·근거를 확인하고 제보 여부를 정할 수 있어야 합니다. 독자가 본 회차까지의 공개 정보만 사용합니다.</t>
+        </is>
+      </c>
+      <c r="F52" s="96" t="inlineStr">
+        <is>
+          <t>독자 부담, 크레딧 환급 없음, 결과는 제보에만 첨부(확정).</t>
+        </is>
+      </c>
       <c r="G52" s="73" t="inlineStr">
         <is>
-          <t>UC-11</t>
+          <t>UC-09, UC-14</t>
         </is>
       </c>
       <c r="H52" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I52" s="73" t="inlineStr">
@@ -3862,7 +3878,7 @@
       </c>
       <c r="J52" s="73" t="inlineStr">
         <is>
-          <t>집필·버전 작업 미분해</t>
+          <t>4.8 관련 / 세부 작업 미분해</t>
         </is>
       </c>
       <c r="K52" s="2" t="n"/>
@@ -3881,32 +3897,40 @@
       <c r="X52" s="2" t="n"/>
       <c r="Y52" s="2" t="n"/>
     </row>
-    <row r="53" ht="97" customHeight="1" s="109">
-      <c r="A53" s="112" t="n"/>
-      <c r="B53" s="112" t="n"/>
-      <c r="C53" s="65" t="inlineStr">
-        <is>
-          <t>F-WRT-07</t>
-        </is>
-      </c>
-      <c r="D53" s="75" t="inlineStr">
-        <is>
-          <t>집필 방식 선택</t>
-        </is>
-      </c>
-      <c r="E53" s="75" t="inlineStr">
-        <is>
-          <t>작품 소유자는 작품 설정에서 직접 집필, AI 협업 집필, AI 자율 연재를 선택할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F53" s="100" t="inlineStr">
-        <is>
-          <t>자율 연재는 자동 발행으로 확정, 실행 주기는 미정. 직접 집필에 AI 사용을 강제하지 않습니다.</t>
+    <row r="53" ht="80" customHeight="1" s="109">
+      <c r="A53" s="50" t="inlineStr">
+        <is>
+          <t>REQ07</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>원고 작성·편집</t>
+        </is>
+      </c>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>F-WRT-01</t>
+        </is>
+      </c>
+      <c r="D53" s="70" t="inlineStr">
+        <is>
+          <t>직접 집필</t>
+        </is>
+      </c>
+      <c r="E53" s="70" t="inlineStr">
+        <is>
+          <t>편집 권한이 있는 사용자는 AI 없이 원작 또는 자신의 Fork 원고를 직접 작성·수정·저장할 수 있어야 합니다. 저장 실패와 미저장을 표시하며 기존 저장본을 보존해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F53" s="68" t="inlineStr">
+        <is>
+          <t>Fork 생성·직접 집필은 무료. 원고는 문단 단위 일반 텍스트에 이미지 삽입, 자동 저장은 초안만 갱신(버전 미생성), 다중 탭·기기 충돌은 재확인(확정). 자동 저장 간격 미정.</t>
         </is>
       </c>
       <c r="G53" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-10, UC-11, UC-18</t>
+          <t>UC-10</t>
         </is>
       </c>
       <c r="H53" s="73" t="inlineStr">
@@ -3943,29 +3967,25 @@
     <row r="54" ht="64" customHeight="1" s="109">
       <c r="A54" s="112" t="n"/>
       <c r="B54" s="112" t="n"/>
-      <c r="C54" s="68" t="inlineStr">
-        <is>
-          <t>F-WRT-08</t>
-        </is>
-      </c>
-      <c r="D54" s="91" t="inlineStr">
-        <is>
-          <t>Fork 작품 집필 방식 적용</t>
-        </is>
-      </c>
-      <c r="E54" s="92" t="inlineStr">
-        <is>
-          <t>허용된 이용 조건 안에서 원작과 동일한 집필 방식을 Fork 작품에도 적용할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F54" s="105" t="inlineStr">
-        <is>
-          <t>원작의 설정값은 물려받지 않고 기본값(수동·작가 검토·끔)으로 시작하며, Fork 소유자가 직접 설정하고 비용을 부담(확정).</t>
-        </is>
-      </c>
+      <c r="C54" s="64" t="inlineStr">
+        <is>
+          <t>F-WRT-02</t>
+        </is>
+      </c>
+      <c r="D54" s="73" t="inlineStr">
+        <is>
+          <t>AI 협업 집필 방향 설정</t>
+        </is>
+      </c>
+      <c r="E54" s="73" t="inlineStr">
+        <is>
+          <t>AI 협업 집필에서 사용자는 원하는 이야기 방향을 결정하고 AI에게 작성 지원을 요청할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F54" s="96" t="n"/>
       <c r="G54" s="73" t="inlineStr">
         <is>
-          <t>UC-08, UC-10, UC-11, UC-18</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="H54" s="73" t="inlineStr">
@@ -3999,37 +4019,33 @@
       <c r="X54" s="2" t="n"/>
       <c r="Y54" s="2" t="n"/>
     </row>
-    <row r="55" ht="114" customHeight="1" s="109">
+    <row r="55" ht="64" customHeight="1" s="109">
       <c r="A55" s="112" t="n"/>
       <c r="B55" s="112" t="n"/>
-      <c r="C55" s="68" t="inlineStr">
-        <is>
-          <t>F-WRT-09</t>
-        </is>
-      </c>
-      <c r="D55" s="93" t="inlineStr">
-        <is>
-          <t>AI 자율 연재 회차 생성</t>
-        </is>
-      </c>
-      <c r="E55" s="94" t="inlineStr">
-        <is>
-          <t>작품 소유자(원작·Fork 모두)가 자율 연재를 켜면 AI가 설정한 조건과 허용 문맥 안에서 다음 회차를 생성하고, 발행 확인(권한·Fork 원작 조건·권리 제한)을 거쳐 자동 발행해야 합니다. 크레딧은 작품 소유자에게 청구합니다.</t>
-        </is>
-      </c>
-      <c r="F55" s="104" t="inlineStr">
-        <is>
-          <t>자동 발행 확정. 실행 주기·트리거·자동 중지 조건·스케줄러 도입 미정.</t>
-        </is>
-      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>F-WRT-03</t>
+        </is>
+      </c>
+      <c r="D55" s="73" t="inlineStr">
+        <is>
+          <t>장면·대화·원고 생성</t>
+        </is>
+      </c>
+      <c r="E55" s="73" t="inlineStr">
+        <is>
+          <t>AI는 사용자의 집필 요청과 작품 정보를 바탕으로 장면·대화·원고 초안을 생성할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F55" s="96" t="n"/>
       <c r="G55" s="73" t="inlineStr">
         <is>
-          <t>UC-18</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="H55" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 실행 주기 미정</t>
+          <t>기획 초안 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I55" s="73" t="inlineStr">
@@ -4039,7 +4055,7 @@
       </c>
       <c r="J55" s="73" t="inlineStr">
         <is>
-          <t>조건부 / 작업 미분해</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K55" s="2" t="n"/>
@@ -4058,37 +4074,33 @@
       <c r="X55" s="2" t="n"/>
       <c r="Y55" s="2" t="n"/>
     </row>
-    <row r="56" ht="114" customHeight="1" s="109">
+    <row r="56" ht="64" customHeight="1" s="109">
       <c r="A56" s="112" t="n"/>
       <c r="B56" s="112" t="n"/>
-      <c r="C56" s="69" t="inlineStr">
-        <is>
-          <t>F-WRT-10</t>
-        </is>
-      </c>
-      <c r="D56" s="75" t="inlineStr">
-        <is>
-          <t>독자 반응 기반 전개 참고</t>
-        </is>
-      </c>
-      <c r="E56" s="75" t="inlineStr">
-        <is>
-          <t>AI 자율 연재는 허용된 독자 반응을 다음 회차의 사건·전개에 참고할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F56" s="108" t="inlineStr">
-        <is>
-          <t>반영 기준 미정. 투표 기능이나 외부 댓글 수집은 확정하지 않습니다.</t>
-        </is>
-      </c>
+      <c r="C56" s="64" t="inlineStr">
+        <is>
+          <t>F-WRT-04</t>
+        </is>
+      </c>
+      <c r="D56" s="73" t="inlineStr">
+        <is>
+          <t>AI 원고 수정 지원</t>
+        </is>
+      </c>
+      <c r="E56" s="73" t="inlineStr">
+        <is>
+          <t>사용자는 AI 원고 제안을 검토·수정·거절하고 선택한 부분만 편집 초안에 반영할 수 있어야 합니다. 생성 완료와 실제 저장·승인·발행 완료를 구분해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F56" s="96" t="n"/>
       <c r="G56" s="73" t="inlineStr">
         <is>
-          <t>UC-18</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="H56" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 실행 주기 미정</t>
+          <t>기획 초안 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I56" s="73" t="inlineStr">
@@ -4098,7 +4110,7 @@
       </c>
       <c r="J56" s="73" t="inlineStr">
         <is>
-          <t>조건부 / 작업 미분해</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -4122,27 +4134,23 @@
       <c r="B57" s="112" t="n"/>
       <c r="C57" s="64" t="inlineStr">
         <is>
-          <t>F-WRT-11</t>
+          <t>F-WRT-05</t>
         </is>
       </c>
       <c r="D57" s="73" t="inlineStr">
         <is>
-          <t>원고 버전 이력 관리</t>
+          <t>시뮬레이션 결과 활용</t>
         </is>
       </c>
       <c r="E57" s="73" t="inlineStr">
         <is>
-          <t>원고의 작성 내용과 수정 버전을 저장하고 이전 작업 이력을 확인할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F57" s="96" t="inlineStr">
-        <is>
-          <t>버전 보존·복원 정책 상세 정의 필요</t>
-        </is>
-      </c>
+          <t>사용자는 선택한 시뮬레이션 결과를 원고의 사건·장면·대화 작성에 활용할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F57" s="96" t="n"/>
       <c r="G57" s="73" t="inlineStr">
         <is>
-          <t>UC-10, UC-13, UC-16</t>
+          <t>UC-09, UC-10, UC-11</t>
         </is>
       </c>
       <c r="H57" s="73" t="inlineStr">
@@ -4176,40 +4184,28 @@
       <c r="X57" s="2" t="n"/>
       <c r="Y57" s="2" t="n"/>
     </row>
-    <row r="58" ht="80" customHeight="1" s="109">
-      <c r="A58" s="60" t="inlineStr">
-        <is>
-          <t>REQ08</t>
-        </is>
-      </c>
-      <c r="B58" s="60" t="inlineStr">
-        <is>
-          <t>독자 피드백·응대</t>
-        </is>
-      </c>
+    <row r="58" ht="64" customHeight="1" s="109">
+      <c r="A58" s="112" t="n"/>
+      <c r="B58" s="112" t="n"/>
       <c r="C58" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-01</t>
+          <t>F-WRT-06</t>
         </is>
       </c>
       <c r="D58" s="73" t="inlineStr">
         <is>
-          <t>피드백·오류 제보 등록</t>
+          <t>세계관·캐릭터 설정 활용</t>
         </is>
       </c>
       <c r="E58" s="73" t="inlineStr">
         <is>
-          <t>접근·작성 조건을 충족한 독자는 STORYFORK 작품·회차에 댓글·질문·의견·오류 제보를 등록할 수 있어야 합니다. 대상 회차·제보·처리 결과를 연결해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F58" s="96" t="inlineStr">
-        <is>
-          <t>제보(질문·오류 제보·제안)의 AI 분석 크레딧은 제보자 부담이며, 크레딧이 없으면 제보는 못 하고 댓글만 등록 가능(확정). 댓글은 AI 분석 없이 무료. 등록 시 독자가 본 발행본 버전을 고정. 외부 플랫폼 댓글 수집 제외.</t>
-        </is>
-      </c>
+          <t>AI 집필 지원은 현재 작품·기준 시점에서 사용이 허용된 세계관·캐릭터·원고와 선택된 시뮬레이션 결과를 필요한 범위만 참고해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F58" s="96" t="n"/>
       <c r="G58" s="73" t="inlineStr">
         <is>
-          <t>UC-14</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="H58" s="73" t="inlineStr">
@@ -4224,7 +4220,7 @@
       </c>
       <c r="J58" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.6·5.8 (피드백 화면·API)</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4243,32 +4239,32 @@
       <c r="X58" s="2" t="n"/>
       <c r="Y58" s="2" t="n"/>
     </row>
-    <row r="59" ht="64" customHeight="1" s="109">
+    <row r="59" ht="97" customHeight="1" s="109">
       <c r="A59" s="112" t="n"/>
       <c r="B59" s="112" t="n"/>
       <c r="C59" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-02</t>
+          <t>F-WRT-07</t>
         </is>
       </c>
       <c r="D59" s="73" t="inlineStr">
         <is>
-          <t>피드백 유형 분류</t>
+          <t>집필 방식 선택</t>
         </is>
       </c>
       <c r="E59" s="73" t="inlineStr">
         <is>
-          <t>AI는 질문·표기 오류 제보·설정 충돌 의심·개인적 해석·전개 선호 등 유형과 의도를 구분해야 합니다. 한 피드백에 섞인 요구를 단일 유형으로 강제하지 않아야 합니다.</t>
+          <t>작품 소유자는 작품 설정에서 직접 집필, AI 협업 집필, AI 자율 연재를 선택할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F59" s="96" t="inlineStr">
         <is>
-          <t>피드백 분석은 공개 근거를 대조하는 검증이며 세계관·설정을 바꾸지 않습니다.</t>
+          <t>자율 연재는 자동 발행·소유자 지정 일정 실행(확정). 직접 집필에 AI 사용을 강제하지 않습니다.</t>
         </is>
       </c>
       <c r="G59" s="73" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-24, UC-10, UC-11, UC-18</t>
         </is>
       </c>
       <c r="H59" s="73" t="inlineStr">
@@ -4283,7 +4279,7 @@
       </c>
       <c r="J59" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K59" s="2" t="n"/>
@@ -4307,23 +4303,27 @@
       <c r="B60" s="112" t="n"/>
       <c r="C60" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-03</t>
+          <t>F-WRT-08</t>
         </is>
       </c>
       <c r="D60" s="73" t="inlineStr">
         <is>
-          <t>표기 오류와 전개 의견 구분</t>
+          <t>Fork 작품 집필 방식 적용</t>
         </is>
       </c>
       <c r="E60" s="73" t="inlineStr">
         <is>
-          <t>AI는 오타·맞춤법·명백한 숫자 표기 오류와 스토리 전개·인물 행동에 대한 의견을 구분해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F60" s="96" t="n"/>
+          <t>허용된 이용 조건 안에서 원작과 동일한 집필 방식을 Fork 작품에도 적용할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F60" s="96" t="inlineStr">
+        <is>
+          <t>원작의 설정값은 물려받지 않고 기본값(수동·작가 검토·끔)으로 시작하며, Fork 소유자가 직접 설정하고 비용을 부담(확정).</t>
+        </is>
+      </c>
       <c r="G60" s="73" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-08, UC-10, UC-11, UC-18</t>
         </is>
       </c>
       <c r="H60" s="73" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="J60" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K60" s="2" t="n"/>
@@ -4357,32 +4357,32 @@
       <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="n"/>
     </row>
-    <row r="61" ht="64" customHeight="1" s="109">
+    <row r="61" ht="114" customHeight="1" s="109">
       <c r="A61" s="112" t="n"/>
       <c r="B61" s="112" t="n"/>
       <c r="C61" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-04</t>
+          <t>F-WRT-09</t>
         </is>
       </c>
       <c r="D61" s="73" t="inlineStr">
         <is>
-          <t>작품 맥락 기반 검토</t>
+          <t>AI 자율 연재 회차 생성</t>
         </is>
       </c>
       <c r="E61" s="73" t="inlineStr">
         <is>
-          <t>피드백 응대는 대상 작품·회차에서 허용된 공개 원고·설정·사건·인물 정보를 근거로 수행해야 합니다. 작가 비공개 설정이나 비공개 후속 회차를 노출하지 않아야 합니다.</t>
+          <t>작품 소유자(원작·Fork 모두)가 자율 연재를 켜면 AI가 설정한 조건과 허용 문맥 안에서 다음 회차를 생성하고, 발행 확인(권한·Fork 원작 조건·권리 제한)을 거쳐 자동 발행해야 합니다. 크레딧은 작품 소유자에게 청구합니다.</t>
         </is>
       </c>
       <c r="F61" s="96" t="inlineStr">
         <is>
-          <t>공개 후속 회차의 스포일러 허용 범위와 답변 공개 수준은 미정.</t>
+          <t>자동 발행 확정. 소유자가 정한 요일·시각(주 1~7회, 하루 최대 1회)에 Core API 내장 스케줄러로 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단됨, 생성 회차도 1차 필터, 발행 전 확인 옵션(기본 꺼짐)(확정). 다중 서버 중복 실행 방지 미정.</t>
         </is>
       </c>
       <c r="G61" s="73" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-18</t>
         </is>
       </c>
       <c r="H61" s="73" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="J61" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>조건부 / 작업 미분해</t>
         </is>
       </c>
       <c r="K61" s="2" t="n"/>
@@ -4416,28 +4416,32 @@
       <c r="X61" s="2" t="n"/>
       <c r="Y61" s="2" t="n"/>
     </row>
-    <row r="62" ht="64" customHeight="1" s="109">
+    <row r="62" ht="114" customHeight="1" s="109">
       <c r="A62" s="112" t="n"/>
       <c r="B62" s="112" t="n"/>
       <c r="C62" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-05</t>
+          <t>F-WRT-10</t>
         </is>
       </c>
       <c r="D62" s="73" t="inlineStr">
         <is>
-          <t>근거 정보 제공</t>
+          <t>독자 반응 기반 전개 참고</t>
         </is>
       </c>
       <c r="E62" s="73" t="inlineStr">
         <is>
-          <t>확인에 사용한 설정·회차·사건 근거를 응답에 제시할 수 있어야 합니다. 근거 부족·문맥 한계·AI 실패를 구분하고 허구의 인용이나 정상 처리로 대체하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F62" s="96" t="n"/>
+          <t>AI 자율 연재는 허용된 독자 반응을 다음 회차의 사건·전개에 참고할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F62" s="96" t="inlineStr">
+        <is>
+          <t>소유자가 켠 경우에만 직전 회차 이후 필터 통과 공개 댓글·제안을 참고하고 작성자 정보는 보내지 않음(확정). 투표·외부 댓글 수집은 범위 밖.</t>
+        </is>
+      </c>
       <c r="G62" s="73" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-18</t>
         </is>
       </c>
       <c r="H62" s="73" t="inlineStr">
@@ -4452,7 +4456,7 @@
       </c>
       <c r="J62" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>조건부 / 작업 미분해</t>
         </is>
       </c>
       <c r="K62" s="2" t="n"/>
@@ -4476,27 +4480,27 @@
       <c r="B63" s="112" t="n"/>
       <c r="C63" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-06</t>
+          <t>F-WRT-11</t>
         </is>
       </c>
       <c r="D63" s="73" t="inlineStr">
         <is>
-          <t>표기 오류 수정안 작성</t>
+          <t>원고 버전 이력 관리</t>
         </is>
       </c>
       <c r="E63" s="73" t="inlineStr">
         <is>
-          <t>명확한 표기 오류에는 대상 원고의 기준 버전, 변경 전후와 근거가 연결된 작품 내 수정안(PR)을 제시해야 합니다. 제안 생성만으로 원고를 수정하지 않아야 합니다.</t>
+          <t>원고의 작성 내용과 수정 버전을 저장하고 이전 작업 이력을 확인할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F63" s="96" t="inlineStr">
         <is>
-          <t>PR은 작품 내 변경 제안이며 GitHub 연동이 아닙니다.</t>
+          <t>수동 저장 버전은 무기한 보관, 복원은 선택 버전을 새 초안 버전으로 쌓음(확정). 발행본은 바꾸지 않음.</t>
         </is>
       </c>
       <c r="G63" s="73" t="inlineStr">
         <is>
-          <t>UC-15, UC-16</t>
+          <t>UC-10, UC-13, UC-16</t>
         </is>
       </c>
       <c r="H63" s="73" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="J63" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7·5.8 (수정안)</t>
+          <t>집필·버전 작업 미분해</t>
         </is>
       </c>
       <c r="K63" s="2" t="n"/>
@@ -4530,37 +4534,37 @@
       <c r="X63" s="2" t="n"/>
       <c r="Y63" s="2" t="n"/>
     </row>
-    <row r="64" ht="97" customHeight="1" s="109">
+    <row r="64" ht="80" customHeight="1" s="109">
       <c r="A64" s="112" t="n"/>
       <c r="B64" s="112" t="n"/>
       <c r="C64" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-07</t>
+          <t>F-WRT-12</t>
         </is>
       </c>
       <c r="D64" s="73" t="inlineStr">
         <is>
-          <t>작품 소유자 승인 후 대상 원고 반영</t>
+          <t>원고 이미지 삽입</t>
         </is>
       </c>
       <c r="E64" s="73" t="inlineStr">
         <is>
-          <t>작품 소유자가 수정안을 검토·승인하면 권한과 기준 버전을 다시 확인해 승인 범위만 초안에 반영하고 발행 절차로 공개해야 합니다. 작품 설정이 '표기 오류 자동 승인·발행'이면 오타·맞춤법·명백한 숫자 표기 오류에 한해 시스템이 자동 승인·발행합니다.</t>
+          <t>창작자는 원고의 문단 사이에 이미지를 올려 넣을 수 있어야 하며, 이미지는 원고 버전에 포함되고 발행 시 독자 화면에 표시되어야 합니다.</t>
         </is>
       </c>
       <c r="F64" s="96" t="inlineStr">
         <is>
-          <t>Fork 소유자는 자신의 Fork만 승인. 기준 버전이 바뀌거나 자동 발행이 실패하면 자동 처리를 멈추고 작가 검토로 전환.</t>
+          <t>JPG·PNG·WebP 장당 10MB, 이용 권한 확인, 저장 사용량 포함, AI에 전달하지 않음(확정). 저장 위치·대체 텍스트 입력 방식 미정.</t>
         </is>
       </c>
       <c r="G64" s="73" t="inlineStr">
         <is>
-          <t>UC-16</t>
+          <t>UC-10</t>
         </is>
       </c>
       <c r="H64" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I64" s="73" t="inlineStr">
@@ -4570,7 +4574,7 @@
       </c>
       <c r="J64" s="73" t="inlineStr">
         <is>
-          <t>5.6·5.8 (수정안 검토·반영)</t>
+          <t>작업 미분해 (개발현황 GAP-09)</t>
         </is>
       </c>
       <c r="K64" s="2" t="n"/>
@@ -4589,33 +4593,37 @@
       <c r="X64" s="2" t="n"/>
       <c r="Y64" s="2" t="n"/>
     </row>
-    <row r="65" ht="64" customHeight="1" s="109">
+    <row r="65" ht="80" customHeight="1" s="109">
       <c r="A65" s="112" t="n"/>
       <c r="B65" s="112" t="n"/>
       <c r="C65" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-08</t>
+          <t>F-WRT-13</t>
         </is>
       </c>
       <c r="D65" s="73" t="inlineStr">
         <is>
-          <t>판단이 필요한 제보 전달</t>
+          <t>원고 내보내기</t>
         </is>
       </c>
       <c r="E65" s="73" t="inlineStr">
         <is>
-          <t>자동으로 판단하기 어려운 피드백은 해당 작품의 작가에게 전달할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F65" s="96" t="n"/>
+          <t>창작자는 회차 하나 또는 작품 전체의 초안·발행본을 .txt 또는 .epub으로 내려받을 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F65" s="96" t="inlineStr">
+        <is>
+          <t>epub은 회차를 챕터로·이미지 포함, txt는 이미지 제외, Fork는 분기 이후 자기 회차만, 메모 제외(확정).</t>
+        </is>
+      </c>
       <c r="G65" s="73" t="inlineStr">
         <is>
-          <t>UC-15, UC-16</t>
+          <t>UC-10</t>
         </is>
       </c>
       <c r="H65" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I65" s="73" t="inlineStr">
@@ -4625,7 +4633,7 @@
       </c>
       <c r="J65" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>작업 미분해 (개발현황 GAP-09)</t>
         </is>
       </c>
       <c r="K65" s="2" t="n"/>
@@ -4644,33 +4652,37 @@
       <c r="X65" s="2" t="n"/>
       <c r="Y65" s="2" t="n"/>
     </row>
-    <row r="66" ht="64" customHeight="1" s="109">
+    <row r="66" ht="80" customHeight="1" s="109">
       <c r="A66" s="112" t="n"/>
       <c r="B66" s="112" t="n"/>
       <c r="C66" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-09</t>
+          <t>F-WRT-14</t>
         </is>
       </c>
       <c r="D66" s="73" t="inlineStr">
         <is>
-          <t>설정 사실과 해석 구분</t>
+          <t>일러스트 생성</t>
         </is>
       </c>
       <c r="E66" s="73" t="inlineStr">
         <is>
-          <t>응대 시 확인 가능한 설정과 스토리 해석의 영역을 구분하고, 독자의 의견을 무조건 옳거나 그르다고 판정하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F66" s="96" t="n"/>
+          <t>창작자는 원고의 장면을 지정해 AI 일러스트를 생성하고, 채택한 이미지만 원고에 넣을 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F66" s="96" t="inlineStr">
+        <is>
+          <t>지정 장면과 작가가 정리한 인물 외형만 이미지 생성 모델에 전달, 안전 정책 거부는 실패로 고지(확정). 비용·권리 귀속·AI 생성 표시 미정. 기획서 근거 없음(팀 결정).</t>
+        </is>
+      </c>
       <c r="G66" s="73" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-11</t>
         </is>
       </c>
       <c r="H66" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I66" s="73" t="inlineStr">
@@ -4680,7 +4692,7 @@
       </c>
       <c r="J66" s="73" t="inlineStr">
         <is>
-          <t>4.6·4.7 (분석·근거 검토)</t>
+          <t>작업 미분해 (개발현황 GAP-09)</t>
         </is>
       </c>
       <c r="K66" s="2" t="n"/>
@@ -4699,32 +4711,40 @@
       <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="n"/>
     </row>
-    <row r="67" ht="64" customHeight="1" s="109">
-      <c r="A67" s="112" t="n"/>
-      <c r="B67" s="112" t="n"/>
+    <row r="67" ht="80" customHeight="1" s="109">
+      <c r="A67" s="50" t="inlineStr">
+        <is>
+          <t>REQ08</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>독자 피드백·응대</t>
+        </is>
+      </c>
       <c r="C67" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-10</t>
-        </is>
-      </c>
-      <c r="D67" s="73" t="inlineStr">
-        <is>
-          <t>피드백 처리 상태 관리</t>
-        </is>
-      </c>
-      <c r="E67" s="73" t="inlineStr">
-        <is>
-          <t>피드백 접수, AI 처리·실패, 작가 검토, 승인·거절·보류와 실제 반영 성공·실패를 구분해 기록해야 합니다. 아직 검토 중이거나 반영에 실패한 제보를 해결 완료로 표시하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F67" s="96" t="inlineStr">
-        <is>
-          <t>AI 실패·지연은 대기 없이 즉시 실패로 고지. 상태값 세부 정의 필요</t>
+          <t>F-FBK-01</t>
+        </is>
+      </c>
+      <c r="D67" s="70" t="inlineStr">
+        <is>
+          <t>피드백·오류 제보 등록</t>
+        </is>
+      </c>
+      <c r="E67" s="70" t="inlineStr">
+        <is>
+          <t>로그인한 독자는 STORYFORK 작품·회차에 피드백 유형(댓글·단순 오류·스토리 오류·질문·제안)을 골라 무료로 등록할 수 있어야 합니다. 대상 회차·발행본 버전·지정 구절·처리 결과를 연결해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F67" s="68" t="inlineStr">
+        <is>
+          <t>댓글·제보 등록 무료(확정). 댓글은 전체 공개·좋아요 수 공개, 제보와 응답은 제보자·작가만 보고 작가가 고른 응답만 공개. 댓글은 수정·삭제, 제보는 응대 시작 후 철회만 가능.</t>
         </is>
       </c>
       <c r="G67" s="73" t="inlineStr">
         <is>
-          <t>UC-14, UC-15, UC-16</t>
+          <t>UC-14</t>
         </is>
       </c>
       <c r="H67" s="73" t="inlineStr">
@@ -4763,27 +4783,27 @@
       <c r="B68" s="112" t="n"/>
       <c r="C68" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-11</t>
+          <t>F-FBK-02</t>
         </is>
       </c>
       <c r="D68" s="73" t="inlineStr">
         <is>
-          <t>처리 결과 안내</t>
+          <t>피드백 유형 선택</t>
         </is>
       </c>
       <c r="E68" s="73" t="inlineStr">
         <is>
-          <t>피드백을 등록한 독자에게 검토 결과와 처리 상태를 안내할 수 있어야 합니다.</t>
+          <t>독자가 피드백 유형(댓글·단순 오류·스토리 오류·질문·제안)을 직접 골라야 하며, 시스템은 유형을 AI로 분류하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F68" s="96" t="inlineStr">
         <is>
-          <t>안내 시점·알림 채널 정의 필요</t>
+          <t>BR-15(확정). 피드백 분석은 공개 근거를 대조하는 검증이며 세계관·설정을 바꾸지 않습니다. 자체 분류 모델(WBS 3.5)의 용도는 재검토(개발현황 CHECK-07).</t>
         </is>
       </c>
       <c r="G68" s="73" t="inlineStr">
         <is>
-          <t>UC-14, UC-15, UC-16</t>
+          <t>UC-14, UC-15</t>
         </is>
       </c>
       <c r="H68" s="73" t="inlineStr">
@@ -4798,7 +4818,7 @@
       </c>
       <c r="J68" s="73" t="inlineStr">
         <is>
-          <t>5.5·5.6·5.8 (피드백 화면·API)</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K68" s="2" t="n"/>
@@ -4822,23 +4842,23 @@
       <c r="B69" s="112" t="n"/>
       <c r="C69" s="64" t="inlineStr">
         <is>
-          <t>F-FBK-12</t>
+          <t>F-FBK-03</t>
         </is>
       </c>
       <c r="D69" s="73" t="inlineStr">
         <is>
-          <t>대안 창작 경로 안내</t>
+          <t>단순 오류와 스토리 오류 분리</t>
         </is>
       </c>
       <c r="E69" s="73" t="inlineStr">
         <is>
-          <t>다른 전개를 직접 창작하려는 의도가 있고 이용이 허용된 경우에만 Fork·시뮬레이션을 선택적으로 안내해야 합니다. 단순 비판·해석 차이에 분기 창작을 강요하지 않아야 합니다.</t>
+          <t>단순 오류(오탈자·맞춤법·명백한 숫자·표기)와 스토리 오류(설정 충돌·인물 행동·지식 모순·개연성)를 분리해야 합니다. 단순 오류만 수정안·자동 승인 경로로 처리하고, 스토리 오류는 언제나 작가가 판단합니다.</t>
         </is>
       </c>
       <c r="F69" s="96" t="n"/>
       <c r="G69" s="73" t="inlineStr">
         <is>
-          <t>UC-08, UC-09, UC-15</t>
+          <t>UC-14, UC-15, UC-16</t>
         </is>
       </c>
       <c r="H69" s="73" t="inlineStr">
@@ -4853,7 +4873,7 @@
       </c>
       <c r="J69" s="73" t="inlineStr">
         <is>
-          <t>4.6·5.5 (응대·Fork 안내)</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K69" s="2" t="n"/>
@@ -4873,39 +4893,31 @@
       <c r="Y69" s="2" t="n"/>
     </row>
     <row r="70" ht="64" customHeight="1" s="109">
-      <c r="A70" s="60" t="inlineStr">
-        <is>
-          <t>REQ09</t>
-        </is>
-      </c>
-      <c r="B70" s="60" t="inlineStr">
-        <is>
-          <t>저작권·이용 권한</t>
-        </is>
-      </c>
+      <c r="A70" s="112" t="n"/>
+      <c r="B70" s="112" t="n"/>
       <c r="C70" s="64" t="inlineStr">
         <is>
-          <t>F-RGT-01</t>
+          <t>F-FBK-04</t>
         </is>
       </c>
       <c r="D70" s="73" t="inlineStr">
         <is>
-          <t>세계관 공개 범위 설정</t>
+          <t>작품 맥락 기반 검토</t>
         </is>
       </c>
       <c r="E70" s="73" t="inlineStr">
         <is>
-          <t>소유자는 세계관을 비공개 또는 공개로 설정하고, 이용·세계관 Fork·AI 처리·이 세계관을 쓴 작품의 유료 공개 허용을 각각 정할 수 있어야 합니다. 세계관 이용과 세계관 Fork는 따로 허용합니다.</t>
+          <t>피드백 응대는 대상 작품·회차에서 허용된 공개 원고·설정·사건·인물 정보를 근거로 수행해야 합니다. 작가 비공개 설정이나 비공개 후속 회차를 노출하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F70" s="96" t="inlineStr">
         <is>
-          <t>'일부 공개'는 삭제(확정). 세계관 자체의 판매는 범위 밖. 공개 세계관을 비공개로 바꾸면 이용 허가 철회와 같이 처리.</t>
+          <t>독자가 본 회차까지만 근거로 사용하며 이후 회차는 공개됐어도 쓰지 않음(확정). 응대 시간 초과 2분.</t>
         </is>
       </c>
       <c r="G70" s="73" t="inlineStr">
         <is>
-          <t>UC-02, UC-07</t>
+          <t>UC-15</t>
         </is>
       </c>
       <c r="H70" s="73" t="inlineStr">
@@ -4920,7 +4932,7 @@
       </c>
       <c r="J70" s="73" t="inlineStr">
         <is>
-          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -4944,27 +4956,23 @@
       <c r="B71" s="112" t="n"/>
       <c r="C71" s="64" t="inlineStr">
         <is>
-          <t>F-RGT-02</t>
+          <t>F-FBK-05</t>
         </is>
       </c>
       <c r="D71" s="73" t="inlineStr">
         <is>
-          <t>Fork 허용 조건 설정</t>
+          <t>근거 정보 제공</t>
         </is>
       </c>
       <c r="E71" s="73" t="inlineStr">
         <is>
-          <t>소유자는 작품의 Fork 허용 여부와 허용 조건을 설정할 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F71" s="96" t="inlineStr">
-        <is>
-          <t>허용 조건의 세부 항목 및 문구 정의 필요</t>
-        </is>
-      </c>
+          <t>확인에 사용한 설정·회차·사건 근거를 응답에 제시할 수 있어야 합니다. 근거 부족·문맥 한계·AI 실패를 구분하고 허구의 인용이나 정상 처리로 대체하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F71" s="96" t="n"/>
       <c r="G71" s="73" t="inlineStr">
         <is>
-          <t>UC-07, UC-08</t>
+          <t>UC-15</t>
         </is>
       </c>
       <c r="H71" s="73" t="inlineStr">
@@ -4979,7 +4987,7 @@
       </c>
       <c r="J71" s="73" t="inlineStr">
         <is>
-          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K71" s="2" t="n"/>
@@ -5003,27 +5011,27 @@
       <c r="B72" s="112" t="n"/>
       <c r="C72" s="64" t="inlineStr">
         <is>
-          <t>F-RGT-03</t>
+          <t>F-FBK-06</t>
         </is>
       </c>
       <c r="D72" s="73" t="inlineStr">
         <is>
-          <t>이용 조건 기반 기능 제어</t>
+          <t>표기 오류 수정안 작성</t>
         </is>
       </c>
       <c r="E72" s="73" t="inlineStr">
         <is>
-          <t>작품 권한(AI 처리·작품 Fork 생성·Fork 작품 공개·유료 공개)과 세계관 권한(이용·세계관 Fork·AI 처리·작품 유료 공개 허용)을 구분하고, 독자 열람은 공개 범위로 판단하며, Core API에서 허용 여부를 확인해야 합니다. 공개된 콘텐츠나 원고 보유만으로 모든 이용을 허용하지 않아야 합니다.</t>
+          <t>명확한 표기 오류에는 대상 원고의 기준 버전, 변경 전후와 근거가 연결된 작품 내 수정안(PR)을 제시해야 합니다. 제안 생성만으로 원고를 수정하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F72" s="96" t="inlineStr">
         <is>
-          <t>권리 증빙·허용 철회·기존 Fork 영향·유료 공개 조건은 미정.</t>
+          <t>PR은 작품 내 변경 제안이며 GitHub 연동이 아닙니다.</t>
         </is>
       </c>
       <c r="G72" s="73" t="inlineStr">
         <is>
-          <t>UC-05, UC-07, UC-08, UC-13</t>
+          <t>UC-15, UC-16</t>
         </is>
       </c>
       <c r="H72" s="73" t="inlineStr">
@@ -5038,7 +5046,7 @@
       </c>
       <c r="J72" s="73" t="inlineStr">
         <is>
-          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
+          <t>4.6·4.7·5.8 (수정안)</t>
         </is>
       </c>
       <c r="K72" s="2" t="n"/>
@@ -5057,32 +5065,32 @@
       <c r="X72" s="2" t="n"/>
       <c r="Y72" s="2" t="n"/>
     </row>
-    <row r="73" ht="64" customHeight="1" s="109">
+    <row r="73" ht="97" customHeight="1" s="109">
       <c r="A73" s="112" t="n"/>
       <c r="B73" s="112" t="n"/>
       <c r="C73" s="64" t="inlineStr">
         <is>
-          <t>F-RGT-04</t>
+          <t>F-FBK-07</t>
         </is>
       </c>
       <c r="D73" s="73" t="inlineStr">
         <is>
-          <t>권리 확인 작품만 Fork 지원</t>
+          <t>작품 소유자 승인 후 대상 원고 반영</t>
         </is>
       </c>
       <c r="E73" s="73" t="inlineStr">
         <is>
-          <t>저작권 만료 또는 권리자의 이용 허락을 확인할 수 있는 작품을 Fork 지원 대상으로 등록해야 합니다.</t>
+          <t>작품 소유자가 수정안을 검토·승인하면 권한과 기준 버전을 다시 확인해 승인 범위만 초안에 반영하고 발행 절차로 공개해야 합니다. 작품 설정이 '표기 오류 자동 승인·발행'이면 오타·맞춤법·명백한 숫자 표기 오류에 한해 시스템이 자동 승인·발행합니다.</t>
         </is>
       </c>
       <c r="F73" s="96" t="inlineStr">
         <is>
-          <t>저작권 만료 작품 등록은 검증·테스트 전용(확정). 권리 확인 절차·증빙 기준 정의 필요</t>
+          <t>Fork 소유자는 자신의 Fork만 승인. 기준 버전이 바뀌거나 자동 발행이 실패하면 자동 처리를 멈추고 작가 검토로 전환.</t>
         </is>
       </c>
       <c r="G73" s="73" t="inlineStr">
         <is>
-          <t>UC-23(테스트 전용), UC-07, UC-08</t>
+          <t>UC-16</t>
         </is>
       </c>
       <c r="H73" s="73" t="inlineStr">
@@ -5097,7 +5105,7 @@
       </c>
       <c r="J73" s="73" t="inlineStr">
         <is>
-          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
+          <t>5.6·5.8 (수정안 검토·반영)</t>
         </is>
       </c>
       <c r="K73" s="2" t="n"/>
@@ -5121,23 +5129,23 @@
       <c r="B74" s="112" t="n"/>
       <c r="C74" s="64" t="inlineStr">
         <is>
-          <t>F-RGT-05</t>
+          <t>F-FBK-08</t>
         </is>
       </c>
       <c r="D74" s="73" t="inlineStr">
         <is>
-          <t>권리 미확인 작품 제한</t>
+          <t>판단이 필요한 제보 전달</t>
         </is>
       </c>
       <c r="E74" s="73" t="inlineStr">
         <is>
-          <t>이용 허락이 확인되지 않은 타인 작품은 공식 Fork 지원 대상으로 제공하지 않아야 합니다.</t>
+          <t>자동으로 판단하기 어려운 피드백은 해당 작품의 작가에게 전달할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F74" s="96" t="n"/>
       <c r="G74" s="73" t="inlineStr">
         <is>
-          <t>UC-23, UC-07, UC-08</t>
+          <t>UC-15, UC-16</t>
         </is>
       </c>
       <c r="H74" s="73" t="inlineStr">
@@ -5152,7 +5160,7 @@
       </c>
       <c r="J74" s="73" t="inlineStr">
         <is>
-          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K74" s="2" t="n"/>
@@ -5172,39 +5180,27 @@
       <c r="Y74" s="2" t="n"/>
     </row>
     <row r="75" ht="64" customHeight="1" s="109">
-      <c r="A75" s="60" t="inlineStr">
-        <is>
-          <t>REQ10</t>
-        </is>
-      </c>
-      <c r="B75" s="60" t="inlineStr">
-        <is>
-          <t>설정·개연성 검토</t>
-        </is>
-      </c>
+      <c r="A75" s="112" t="n"/>
+      <c r="B75" s="112" t="n"/>
       <c r="C75" s="64" t="inlineStr">
         <is>
-          <t>F-REV-01</t>
+          <t>F-FBK-09</t>
         </is>
       </c>
       <c r="D75" s="73" t="inlineStr">
         <is>
-          <t>기존 설정 대조</t>
+          <t>설정 사실과 해석 구분</t>
         </is>
       </c>
       <c r="E75" s="73" t="inlineStr">
         <is>
-          <t>현재 원고와 세계관 정보, 기존 회차에 기록된 설정을 대조해 충돌 여부를 검토해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F75" s="96" t="inlineStr">
-        <is>
-          <t>검토는 선택 기능이며 발행 전 필수 단계가 아님(확정). 모든 AI 기능은 작가가 골라 쓰는 도구.</t>
-        </is>
-      </c>
+          <t>응대 시 확인 가능한 설정과 스토리 해석의 영역을 구분하고, 독자의 의견을 무조건 옳거나 그르다고 판정하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F75" s="96" t="n"/>
       <c r="G75" s="73" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-15</t>
         </is>
       </c>
       <c r="H75" s="73" t="inlineStr">
@@ -5219,7 +5215,7 @@
       </c>
       <c r="J75" s="73" t="inlineStr">
         <is>
-          <t>4.7 (설정 검토 AI)</t>
+          <t>4.6·4.7 (분석·근거 검토)</t>
         </is>
       </c>
       <c r="K75" s="2" t="n"/>
@@ -5243,23 +5239,27 @@
       <c r="B76" s="112" t="n"/>
       <c r="C76" s="64" t="inlineStr">
         <is>
-          <t>F-REV-02</t>
+          <t>F-FBK-10</t>
         </is>
       </c>
       <c r="D76" s="73" t="inlineStr">
         <is>
-          <t>설정·수치 충돌 탐지</t>
+          <t>피드백 처리 상태 관리</t>
         </is>
       </c>
       <c r="E76" s="73" t="inlineStr">
         <is>
-          <t>과거 설정과 비교해 인물 정보·사건·수치 등 서로 일치하지 않는 내용을 식별해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F76" s="96" t="n"/>
+          <t>피드백 접수, AI 처리·실패, 작가 검토, 승인·거절·보류와 실제 반영 성공·실패를 구분해 기록해야 합니다. 아직 검토 중이거나 반영에 실패한 제보를 해결 완료로 표시하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F76" s="96" t="inlineStr">
+        <is>
+          <t>AI 실패·지연은 대기 없이 즉시 실패로 고지. 상태값 세부 정의 필요</t>
+        </is>
+      </c>
       <c r="G76" s="73" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-14, UC-15, UC-16</t>
         </is>
       </c>
       <c r="H76" s="73" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="J76" s="73" t="inlineStr">
         <is>
-          <t>4.7 (설정 검토 AI)</t>
+          <t>5.5·5.6·5.8 (피드백 화면·API)</t>
         </is>
       </c>
       <c r="K76" s="2" t="n"/>
@@ -5298,23 +5298,27 @@
       <c r="B77" s="112" t="n"/>
       <c r="C77" s="64" t="inlineStr">
         <is>
-          <t>F-REV-03</t>
+          <t>F-FBK-11</t>
         </is>
       </c>
       <c r="D77" s="73" t="inlineStr">
         <is>
-          <t>인물 행동·사건 개연성 검토</t>
+          <t>처리 결과 안내</t>
         </is>
       </c>
       <c r="E77" s="73" t="inlineStr">
         <is>
-          <t>인물의 행동과 사건 전개가 기존 설정 및 사건 인과관계와 일관되는지 검토해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F77" s="96" t="n"/>
+          <t>피드백을 등록한 독자에게 검토 결과와 처리 상태를 안내할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F77" s="96" t="inlineStr">
+        <is>
+          <t>사이트 안 알림(UC-27)으로 안내(확정). 이메일 알림은 범위 밖.</t>
+        </is>
+      </c>
       <c r="G77" s="73" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-14, UC-15, UC-16</t>
         </is>
       </c>
       <c r="H77" s="73" t="inlineStr">
@@ -5329,7 +5333,7 @@
       </c>
       <c r="J77" s="73" t="inlineStr">
         <is>
-          <t>4.7 (설정 검토 AI)</t>
+          <t>5.5·5.6·5.8 (피드백 화면·API)</t>
         </is>
       </c>
       <c r="K77" s="2" t="n"/>
@@ -5353,23 +5357,23 @@
       <c r="B78" s="112" t="n"/>
       <c r="C78" s="64" t="inlineStr">
         <is>
-          <t>F-REV-04</t>
+          <t>F-FBK-12</t>
         </is>
       </c>
       <c r="D78" s="73" t="inlineStr">
         <is>
-          <t>검토 결과 및 근거 표시</t>
+          <t>대안 창작 경로 안내</t>
         </is>
       </c>
       <c r="E78" s="73" t="inlineStr">
         <is>
-          <t>검토 결과에 관련 설정·회차 근거와 충돌 의심·창작적 해석·문맥 한계를 구분해 표시해야 합니다. AI 실패를 충돌 없음으로 바꾸거나 검토만으로 원고·설정을 수정하지 않아야 합니다.</t>
+          <t>제안 유형 제보이고 이용이 허용된 경우에만 Fork·시뮬레이션을 선택적으로 안내해야 합니다. 단순 비판·해석 차이에 분기 창작을 강요하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F78" s="96" t="n"/>
       <c r="G78" s="73" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-08, UC-09, UC-14</t>
         </is>
       </c>
       <c r="H78" s="73" t="inlineStr">
@@ -5384,7 +5388,7 @@
       </c>
       <c r="J78" s="73" t="inlineStr">
         <is>
-          <t>4.7 (설정 검토 AI)</t>
+          <t>4.6·5.5 (응대·Fork 안내)</t>
         </is>
       </c>
       <c r="K78" s="2" t="n"/>
@@ -5403,41 +5407,37 @@
       <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="n"/>
     </row>
-    <row r="79" ht="64" customHeight="1" s="109">
-      <c r="A79" s="60" t="inlineStr">
-        <is>
-          <t>REQ11</t>
-        </is>
-      </c>
-      <c r="B79" s="60" t="inlineStr">
-        <is>
-          <t>데이터·운영 기반</t>
-        </is>
-      </c>
+    <row r="79" ht="80" customHeight="1" s="109">
+      <c r="A79" s="112" t="n"/>
+      <c r="B79" s="112" t="n"/>
       <c r="C79" s="64" t="inlineStr">
         <is>
-          <t>F-OPS-01</t>
+          <t>F-FBK-13</t>
         </is>
       </c>
       <c r="D79" s="73" t="inlineStr">
         <is>
-          <t>서비스 핵심 데이터 관리</t>
+          <t>유해 콘텐츠 1차 필터</t>
         </is>
       </c>
       <c r="E79" s="73" t="inlineStr">
         <is>
-          <t>세계관·등장인물·작품·회차·Fork·원고·피드백 정보를 서로 연결해 관리해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F79" s="96" t="n"/>
+          <t>댓글·제보는 등록 전에 유해 콘텐츠 판정 모델을 거쳐 통과하면 공개하고, 판정되면 숨김 처리해 작성자에게 사유를 알려야 합니다.</t>
+        </is>
+      </c>
+      <c r="F79" s="96" t="inlineStr">
+        <is>
+          <t>OpenAI 모더레이션 모델(AI Service 경유), 호출 실패는 필터 대기(비공개)로 재검사, 다른 독자 신고 시 재검사, 숨긴 글은 삭제하지 않고 작가·운영자가 복원(확정). 재검사 주기 미정.</t>
+        </is>
+      </c>
       <c r="G79" s="73" t="inlineStr">
         <is>
-          <t>UC-02~16 (공통)</t>
+          <t>UC-14</t>
         </is>
       </c>
       <c r="H79" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I79" s="73" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="J79" s="73" t="inlineStr">
         <is>
-          <t>2.5·2.6 (저장 기반)</t>
+          <t>작업 미분해 (개발현황 GAP-10)</t>
         </is>
       </c>
       <c r="K79" s="2" t="n"/>
@@ -5466,33 +5466,37 @@
       <c r="X79" s="2" t="n"/>
       <c r="Y79" s="2" t="n"/>
     </row>
-    <row r="80" ht="64" customHeight="1" s="109">
+    <row r="80" ht="80" customHeight="1" s="109">
       <c r="A80" s="112" t="n"/>
       <c r="B80" s="112" t="n"/>
       <c r="C80" s="64" t="inlineStr">
         <is>
-          <t>F-OPS-02</t>
+          <t>F-FBK-14</t>
         </is>
       </c>
       <c r="D80" s="73" t="inlineStr">
         <is>
-          <t>시점별 데이터 연결</t>
+          <t>댓글 스포일러 가리기</t>
         </is>
       </c>
       <c r="E80" s="73" t="inlineStr">
         <is>
-          <t>설정·인물 상태·사건 기록을 작품과 회차 또는 시점에 연결해 필요한 시점의 맥락을 찾을 수 있어야 합니다.</t>
-        </is>
-      </c>
-      <c r="F80" s="96" t="n"/>
+          <t>댓글 작성자가 스포일러 가리기를 켜면 다른 독자에게는 가려져 보이고 펼쳐야 보여야 합니다.</t>
+        </is>
+      </c>
+      <c r="F80" s="96" t="inlineStr">
+        <is>
+          <t>확정.</t>
+        </is>
+      </c>
       <c r="G80" s="73" t="inlineStr">
         <is>
-          <t>UC-06, UC-08, UC-12</t>
+          <t>UC-14</t>
         </is>
       </c>
       <c r="H80" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I80" s="73" t="inlineStr">
@@ -5502,7 +5506,7 @@
       </c>
       <c r="J80" s="73" t="inlineStr">
         <is>
-          <t>2.5·2.6 (저장 기반)</t>
+          <t>5.5 관련 / 세부 작업 미분해</t>
         </is>
       </c>
       <c r="K80" s="2" t="n"/>
@@ -5521,33 +5525,37 @@
       <c r="X80" s="2" t="n"/>
       <c r="Y80" s="2" t="n"/>
     </row>
-    <row r="81" ht="64" customHeight="1" s="109">
+    <row r="81" ht="80" customHeight="1" s="109">
       <c r="A81" s="112" t="n"/>
       <c r="B81" s="112" t="n"/>
       <c r="C81" s="64" t="inlineStr">
         <is>
-          <t>F-OPS-03</t>
+          <t>F-FBK-15</t>
         </is>
       </c>
       <c r="D81" s="73" t="inlineStr">
         <is>
-          <t>AI 참조 자료 제공</t>
+          <t>스토리 오류 반영 보상</t>
         </is>
       </c>
       <c r="E81" s="73" t="inlineStr">
         <is>
-          <t>Core API가 작업별 권한과 작품·회차·Fork 기준을 확인한 최소 문맥만 AI에 제공해야 합니다. AI는 제안만 반환하며 정본·승인·발행·크레딧을 최종 확정하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F81" s="96" t="n"/>
+          <t>검증 시뮬레이션을 거쳐 제보한 스토리 오류가 작가 승인으로 원고에 반영되면 제보자에게 보상 크레딧을 지급해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F81" s="96" t="inlineStr">
+        <is>
+          <t>플랫폼 부담, 사용 크레딧 이내(기준 50%), 자기 작품·중복 제보 제외, 월 상한(확정). 상한 값·부계정 악용 탐지 미정.</t>
+        </is>
+      </c>
       <c r="G81" s="73" t="inlineStr">
         <is>
-          <t>UC-04, UC-09, UC-11, UC-12, UC-15</t>
+          <t>UC-14, UC-16, UC-17</t>
         </is>
       </c>
       <c r="H81" s="73" t="inlineStr">
         <is>
-          <t>기획 초안 / 개발 계약 미확정</t>
+          <t>팀 결정 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I81" s="73" t="inlineStr">
@@ -5557,7 +5565,7 @@
       </c>
       <c r="J81" s="73" t="inlineStr">
         <is>
-          <t>4.9·5.9 (연동)</t>
+          <t>작업 미분해 (개발현황 GAP-11)</t>
         </is>
       </c>
       <c r="K81" s="2" t="n"/>
@@ -5577,27 +5585,39 @@
       <c r="Y81" s="2" t="n"/>
     </row>
     <row r="82" ht="64" customHeight="1" s="109">
-      <c r="A82" s="112" t="n"/>
-      <c r="B82" s="112" t="n"/>
+      <c r="A82" s="50" t="inlineStr">
+        <is>
+          <t>REQ09</t>
+        </is>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>저작권·이용 권한</t>
+        </is>
+      </c>
       <c r="C82" s="64" t="inlineStr">
         <is>
-          <t>F-OPS-04</t>
-        </is>
-      </c>
-      <c r="D82" s="73" t="inlineStr">
-        <is>
-          <t>원작·분기 데이터 격리</t>
-        </is>
-      </c>
-      <c r="E82" s="73" t="inlineStr">
-        <is>
-          <t>원작·각 Fork·편집 초안·시뮬레이션의 사건·설정·인물 상태를 분리해야 합니다. 폐기한 실행이나 다른 분기의 데이터가 정본·다른 실행에 섞이지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F82" s="96" t="n"/>
+          <t>F-RGT-01</t>
+        </is>
+      </c>
+      <c r="D82" s="70" t="inlineStr">
+        <is>
+          <t>세계관 공개 범위 설정</t>
+        </is>
+      </c>
+      <c r="E82" s="70" t="inlineStr">
+        <is>
+          <t>소유자는 세계관을 비공개 또는 공개로 설정하고, 이용·세계관 Fork·이 세계관을 쓴 작품의 유료 공개 허용을 각각 정할 수 있어야 합니다. 세계관 이용과 세계관 Fork는 따로 허용합니다.</t>
+        </is>
+      </c>
+      <c r="F82" s="68" t="inlineStr">
+        <is>
+          <t>'일부 공개'는 삭제(확정). 세계관 자체의 판매는 범위 밖. 공개 세계관을 비공개로 바꾸면 이용 허가 철회와 같이 처리.</t>
+        </is>
+      </c>
       <c r="G82" s="73" t="inlineStr">
         <is>
-          <t>UC-08, UC-09</t>
+          <t>UC-02, UC-07</t>
         </is>
       </c>
       <c r="H82" s="73" t="inlineStr">
@@ -5612,7 +5632,7 @@
       </c>
       <c r="J82" s="73" t="inlineStr">
         <is>
-          <t>2.5·2.6 (저장 기반)</t>
+          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
         </is>
       </c>
       <c r="K82" s="2" t="n"/>
@@ -5631,32 +5651,32 @@
       <c r="X82" s="2" t="n"/>
       <c r="Y82" s="2" t="n"/>
     </row>
-    <row r="83" ht="97" customHeight="1" s="109">
+    <row r="83" ht="64" customHeight="1" s="109">
       <c r="A83" s="112" t="n"/>
       <c r="B83" s="112" t="n"/>
       <c r="C83" s="64" t="inlineStr">
         <is>
-          <t>F-OPS-05</t>
+          <t>F-RGT-02</t>
         </is>
       </c>
       <c r="D83" s="73" t="inlineStr">
         <is>
-          <t>사용자 유형별 운영 흐름</t>
+          <t>Fork 허용 조건 설정</t>
         </is>
       </c>
       <c r="E83" s="73" t="inlineStr">
         <is>
-          <t>독자·신입 작가·연재 작가의 이용 흐름과 운영 업무를 구분해야 합니다. 운영자는 처리 실패·지연 경고와 오류 로그 확인, 권리 신고 검토를 맡으며 개별 피드백 응대·비공개 원고 무제한 열람·임의 수정 권한을 갖지 않아야 합니다.</t>
+          <t>소유자는 작품의 Fork 허용 여부와 허용 조건을 설정할 수 있어야 합니다.</t>
         </is>
       </c>
       <c r="F83" s="96" t="inlineStr">
         <is>
-          <t>운영자 세부 권한·조회 항목·재처리 절차 미정. 외부 플랫폼 로그인·스크래핑·자동 게시·동기화는 제외.</t>
+          <t>허용 조건의 세부 항목 및 문구 정의 필요</t>
         </is>
       </c>
       <c r="G83" s="73" t="inlineStr">
         <is>
-          <t>UC-21, UC-20</t>
+          <t>UC-07, UC-08</t>
         </is>
       </c>
       <c r="H83" s="73" t="inlineStr">
@@ -5671,7 +5691,7 @@
       </c>
       <c r="J83" s="73" t="inlineStr">
         <is>
-          <t>운영 작업 미분해</t>
+          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
         </is>
       </c>
       <c r="K83" s="2" t="n"/>
@@ -5690,40 +5710,32 @@
       <c r="X83" s="2" t="n"/>
       <c r="Y83" s="2" t="n"/>
     </row>
-    <row r="84" ht="97" customHeight="1" s="109">
-      <c r="A84" s="116" t="inlineStr">
-        <is>
-          <t>REQ12</t>
-        </is>
-      </c>
-      <c r="B84" s="116" t="inlineStr">
-        <is>
-          <t>작품 설정·변경 이력</t>
-        </is>
-      </c>
+    <row r="84" ht="64" customHeight="1" s="109">
+      <c r="A84" s="112" t="n"/>
+      <c r="B84" s="112" t="n"/>
       <c r="C84" s="64" t="inlineStr">
         <is>
-          <t>F-SET-01</t>
+          <t>F-RGT-03</t>
         </is>
       </c>
       <c r="D84" s="73" t="inlineStr">
         <is>
-          <t>작품별 자동 처리 설정</t>
+          <t>이용 조건 기반 기능 제어</t>
         </is>
       </c>
       <c r="E84" s="73" t="inlineStr">
         <is>
-          <t>작품 소유자는 작품 설정에서 세계관 업데이트(수동/자동), 표기 오류 수정안(작가 검토/자동 승인·발행), AI 자율 연재(끔/켬)를 선택할 수 있어야 합니다. 기본값은 수동·작가 검토·끔입니다.</t>
+          <t>작품 권한(작품 Fork 생성·Fork 작품 공개·유료 공개)과 세계관 권한(이용·세계관 Fork·작품 유료 공개 허용)을 구분하고, 독자 열람은 공개 범위로 판단하며, Core API에서 허용 여부를 확인해야 합니다. AI 이용은 별도 허용 항목이 아니며 Fork·세계관 이용 허용 범위에 포함되고, 권리 제한만 AI 이용을 막습니다.</t>
         </is>
       </c>
       <c r="F84" s="96" t="inlineStr">
         <is>
-          <t>크레딧이 드는 자동 처리는 켤 때 예상 비용과 부담 주체(작품 소유자)를 안내하고 동의를 받습니다.</t>
+          <t>AI 처리 허용 항목 제거(확정). 허용 철회·작품 비공개 전환('비공개 원작' 표시)·회차 공개 중단은 기존 Fork와 공개 상태를 유지하고 새 행위만 차단(확정). 권리 증빙·유료 공개 조건은 미정.</t>
         </is>
       </c>
       <c r="G84" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-04, UC-16, UC-18</t>
+          <t>UC-05, UC-07, UC-08, UC-13</t>
         </is>
       </c>
       <c r="H84" s="73" t="inlineStr">
@@ -5738,7 +5750,7 @@
       </c>
       <c r="J84" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
         </is>
       </c>
       <c r="K84" s="2" t="n"/>
@@ -5757,32 +5769,32 @@
       <c r="X84" s="2" t="n"/>
       <c r="Y84" s="2" t="n"/>
     </row>
-    <row r="85" ht="97" customHeight="1" s="109">
+    <row r="85" ht="64" customHeight="1" s="109">
       <c r="A85" s="112" t="n"/>
       <c r="B85" s="112" t="n"/>
       <c r="C85" s="64" t="inlineStr">
         <is>
-          <t>F-SET-02</t>
+          <t>F-RGT-04</t>
         </is>
       </c>
       <c r="D85" s="73" t="inlineStr">
         <is>
-          <t>세계관 변경 이력</t>
+          <t>권리 확인 작품만 Fork 지원</t>
         </is>
       </c>
       <c r="E85" s="73" t="inlineStr">
         <is>
-          <t>세계관·인물관계도의 모든 변경을 현재 HEAD 위에 새 버전으로 쌓아 저장하고(덮어쓰기·삭제·머지 없음) 이전 상태를 조회·되돌릴 수 있어야 합니다. 자동 반영 결과도 이력에 남겨야 합니다. 자기 세계관을 고칠 때 함께 반영될 자기 작품 목록을 저장 전에 안내합니다.</t>
+          <t>저작권 만료 또는 권리자의 이용 허락을 확인할 수 있는 작품을 Fork 지원 대상으로 등록해야 합니다.</t>
         </is>
       </c>
       <c r="F85" s="96" t="inlineStr">
         <is>
-          <t>저장소는 Gitea(확정). 변경 이력은 무기한 보관(확정). 영향 작품 안내는 조회만 하며 AI를 쓰지 않음.</t>
+          <t>저작권 만료 작품 등록은 검증·테스트 전용(확정). 권리 확인 절차·증빙 기준 정의 필요</t>
         </is>
       </c>
       <c r="G85" s="73" t="inlineStr">
         <is>
-          <t>UC-02, UC-04, UC-06</t>
+          <t>UC-23(테스트 전용), UC-07, UC-08</t>
         </is>
       </c>
       <c r="H85" s="73" t="inlineStr">
@@ -5797,7 +5809,7 @@
       </c>
       <c r="J85" s="73" t="inlineStr">
         <is>
-          <t>Gitea 구축 작업 WBS 없음</t>
+          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
         </is>
       </c>
       <c r="K85" s="2" t="n"/>
@@ -5816,32 +5828,28 @@
       <c r="X85" s="2" t="n"/>
       <c r="Y85" s="2" t="n"/>
     </row>
-    <row r="86" ht="97" customHeight="1" s="109">
+    <row r="86" ht="64" customHeight="1" s="109">
       <c r="A86" s="112" t="n"/>
       <c r="B86" s="112" t="n"/>
       <c r="C86" s="64" t="inlineStr">
         <is>
-          <t>F-SET-03</t>
+          <t>F-RGT-05</t>
         </is>
       </c>
       <c r="D86" s="73" t="inlineStr">
         <is>
-          <t>비공개 설정 공개 전환</t>
+          <t>권리 미확인 작품 제한</t>
         </is>
       </c>
       <c r="E86" s="73" t="inlineStr">
         <is>
-          <t>비공개 설정집·인물관계도 항목을 특정 회차부터 독자 공개로 전환하고 전환 회차를 기록해야 합니다. 세계관 자동 업데이트 실행 시에도 같은 방식으로 반영합니다.</t>
-        </is>
-      </c>
-      <c r="F86" s="96" t="inlineStr">
-        <is>
-          <t>세계관에서는 항목의 공개·비공개만 정하고, 공개 전환 회차는 연결된 작품에서 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
-        </is>
-      </c>
+          <t>이용 허락이 확인되지 않은 타인 작품은 공식 Fork 지원 대상으로 제공하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F86" s="96" t="n"/>
       <c r="G86" s="73" t="inlineStr">
         <is>
-          <t>UC-02, UC-06, UC-04</t>
+          <t>UC-23, UC-07, UC-08</t>
         </is>
       </c>
       <c r="H86" s="73" t="inlineStr">
@@ -5856,7 +5864,7 @@
       </c>
       <c r="J86" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>5.8 (Fork 관련) / 세부 권한 작업 미분해</t>
         </is>
       </c>
       <c r="K86" s="2" t="n"/>
@@ -5875,32 +5883,40 @@
       <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
     </row>
-    <row r="87" ht="97" customHeight="1" s="109">
-      <c r="A87" s="112" t="n"/>
-      <c r="B87" s="112" t="n"/>
+    <row r="87" ht="64" customHeight="1" s="109">
+      <c r="A87" s="50" t="inlineStr">
+        <is>
+          <t>REQ10</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>설정·개연성 검토</t>
+        </is>
+      </c>
       <c r="C87" s="64" t="inlineStr">
         <is>
-          <t>F-SET-04</t>
-        </is>
-      </c>
-      <c r="D87" s="73" t="inlineStr">
-        <is>
-          <t>외부 2차 창작물 등록</t>
-        </is>
-      </c>
-      <c r="E87" s="73" t="inlineStr">
-        <is>
-          <t>다른 플랫폼에서 가져온 2차 창작물은 작품 유형으로 구분하고 무료 공개만 허용해야 합니다. 등록자에게 권리 책임과 권리 문제 시 운영자 조치·소명 절차를 고지하고 동의를 받아야 합니다. 외부 2차 창작물도 Fork 원작이 될 수 있으며 AI 기능 크레딧은 별도로 청구합니다.</t>
-        </is>
-      </c>
-      <c r="F87" s="96" t="inlineStr">
-        <is>
-          <t>같은 외부 IP는 먼저 올린 작품을 원본으로 인정하고 다른 작품도 허용(확정). 외부 IP의 2차 창작 허용 범위는 등록자가 따르며 플랫폼은 직접 확인하지 않음. 면책 범위는 이용약관·법률 검토 필요.</t>
+          <t>F-REV-01</t>
+        </is>
+      </c>
+      <c r="D87" s="70" t="inlineStr">
+        <is>
+          <t>기존 설정 대조</t>
+        </is>
+      </c>
+      <c r="E87" s="70" t="inlineStr">
+        <is>
+          <t>현재 원고와 세계관 정보, 기존 회차에 기록된 설정을 대조해 충돌 여부를 검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F87" s="68" t="inlineStr">
+        <is>
+          <t>검토는 선택 기능이며 발행 전 필수 단계가 아님(확정). 모든 AI 기능은 작가가 골라 쓰는 도구.</t>
         </is>
       </c>
       <c r="G87" s="73" t="inlineStr">
         <is>
-          <t>UC-24, UC-03, UC-13, UC-20</t>
+          <t>UC-12</t>
         </is>
       </c>
       <c r="H87" s="73" t="inlineStr">
@@ -5915,7 +5931,7 @@
       </c>
       <c r="J87" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>4.7 (설정 검토 AI)</t>
         </is>
       </c>
       <c r="K87" s="2" t="n"/>
@@ -5934,40 +5950,28 @@
       <c r="X87" s="2" t="n"/>
       <c r="Y87" s="2" t="n"/>
     </row>
-    <row r="88" ht="97" customHeight="1" s="109">
-      <c r="A88" s="116" t="inlineStr">
-        <is>
-          <t>REQ13</t>
-        </is>
-      </c>
-      <c r="B88" s="116" t="inlineStr">
-        <is>
-          <t>AI 크레딧·저장 관리</t>
-        </is>
-      </c>
+    <row r="88" ht="64" customHeight="1" s="109">
+      <c r="A88" s="112" t="n"/>
+      <c r="B88" s="112" t="n"/>
       <c r="C88" s="64" t="inlineStr">
         <is>
-          <t>F-CRD-01</t>
+          <t>F-REV-02</t>
         </is>
       </c>
       <c r="D88" s="73" t="inlineStr">
         <is>
-          <t>실행 전 비용 안내·동의</t>
+          <t>설정·수치 충돌 탐지</t>
         </is>
       </c>
       <c r="E88" s="73" t="inlineStr">
         <is>
-          <t>AI 작업 전에 필요한 크레딧·부담 주체·잔여량을 안내하고 동의를 받아야 하며, 동의 없이 차감하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F88" s="96" t="inlineStr">
-        <is>
-          <t>가격·무료 제공량·차감 시점 미정. 비용 확인 단계 취소는 '취소됨'으로 기록하고 차감하지 않음(확정). 실행 중 중단 기능 제공 여부는 미정.</t>
-        </is>
-      </c>
+          <t>과거 설정과 비교해 인물 정보·사건·수치 등 서로 일치하지 않는 내용을 식별해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F88" s="96" t="n"/>
       <c r="G88" s="73" t="inlineStr">
         <is>
-          <t>UC-17</t>
+          <t>UC-12</t>
         </is>
       </c>
       <c r="H88" s="73" t="inlineStr">
@@ -5982,7 +5986,7 @@
       </c>
       <c r="J88" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>4.7 (설정 검토 AI)</t>
         </is>
       </c>
       <c r="K88" s="2" t="n"/>
@@ -6001,32 +6005,28 @@
       <c r="X88" s="2" t="n"/>
       <c r="Y88" s="2" t="n"/>
     </row>
-    <row r="89" ht="97" customHeight="1" s="109">
+    <row r="89" ht="64" customHeight="1" s="109">
       <c r="A89" s="112" t="n"/>
       <c r="B89" s="112" t="n"/>
       <c r="C89" s="64" t="inlineStr">
         <is>
-          <t>F-CRD-02</t>
+          <t>F-REV-03</t>
         </is>
       </c>
       <c r="D89" s="73" t="inlineStr">
         <is>
-          <t>크레딧 부담 주체</t>
+          <t>인물 행동·사건 개연성 검토</t>
         </is>
       </c>
       <c r="E89" s="73" t="inlineStr">
         <is>
-          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 제보 분석은 제보자, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담하며 작품 Fork·세계관 Fork 생성, 직접 집필, 댓글은 무료입니다.</t>
-        </is>
-      </c>
-      <c r="F89" s="96" t="inlineStr">
-        <is>
-          <t>팀 결정으로 확정.</t>
-        </is>
-      </c>
+          <t>인물의 행동과 사건 전개가 기존 설정 및 사건 인과관계와 일관되는지 검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F89" s="96" t="n"/>
       <c r="G89" s="73" t="inlineStr">
         <is>
-          <t>UC-17, UC-14, UC-04, UC-18</t>
+          <t>UC-12</t>
         </is>
       </c>
       <c r="H89" s="73" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="J89" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>4.7 (설정 검토 AI)</t>
         </is>
       </c>
       <c r="K89" s="2" t="n"/>
@@ -6060,32 +6060,28 @@
       <c r="X89" s="2" t="n"/>
       <c r="Y89" s="2" t="n"/>
     </row>
-    <row r="90" ht="97" customHeight="1" s="109">
+    <row r="90" ht="64" customHeight="1" s="109">
       <c r="A90" s="112" t="n"/>
       <c r="B90" s="112" t="n"/>
       <c r="C90" s="64" t="inlineStr">
         <is>
-          <t>F-CRD-03</t>
+          <t>F-REV-04</t>
         </is>
       </c>
       <c r="D90" s="73" t="inlineStr">
         <is>
-          <t>사용 내역·오류 복구</t>
+          <t>검토 결과 및 근거 표시</t>
         </is>
       </c>
       <c r="E90" s="73" t="inlineStr">
         <is>
-          <t>실제 사용량과 결과 상태를 기록하고, 서비스 오류로 완료되지 않은 작업은 성공과 구분해 복구 기준에 따라 처리해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F90" s="96" t="inlineStr">
-        <is>
-          <t>복구·환급 기준 미정. 동의 없는 재차감 금지.</t>
-        </is>
-      </c>
+          <t>검토 결과에 관련 설정·회차 근거와 충돌 의심·창작적 해석·문맥 한계를 구분해 표시해야 합니다. AI 실패를 충돌 없음으로 바꾸거나 검토만으로 원고·설정을 수정하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F90" s="96" t="n"/>
       <c r="G90" s="73" t="inlineStr">
         <is>
-          <t>UC-17, UC-21</t>
+          <t>UC-12</t>
         </is>
       </c>
       <c r="H90" s="73" t="inlineStr">
@@ -6100,7 +6096,7 @@
       </c>
       <c r="J90" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해</t>
+          <t>4.7 (설정 검토 AI)</t>
         </is>
       </c>
       <c r="K90" s="2" t="n"/>
@@ -6119,37 +6115,41 @@
       <c r="X90" s="2" t="n"/>
       <c r="Y90" s="2" t="n"/>
     </row>
-    <row r="91" ht="97" customHeight="1" s="109">
-      <c r="A91" s="112" t="n"/>
-      <c r="B91" s="112" t="n"/>
+    <row r="91" ht="64" customHeight="1" s="109">
+      <c r="A91" s="50" t="inlineStr">
+        <is>
+          <t>REQ11</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>데이터·운영 기반</t>
+        </is>
+      </c>
       <c r="C91" s="64" t="inlineStr">
         <is>
-          <t>F-STO-01</t>
-        </is>
-      </c>
-      <c r="D91" s="73" t="inlineStr">
-        <is>
-          <t>저장 사용량 확인·정리</t>
-        </is>
-      </c>
-      <c r="E91" s="73" t="inlineStr">
-        <is>
-          <t>사용자는 저장 사용량을 확인하고 정리·확장을 선택할 수 있어야 하며, 한도 초과로 기존 작품을 자동 삭제하지 않아야 합니다.</t>
-        </is>
-      </c>
-      <c r="F91" s="96" t="inlineStr">
-        <is>
-          <t>용량·요금·삭제 복원 정책 미정.</t>
-        </is>
-      </c>
+          <t>F-OPS-01</t>
+        </is>
+      </c>
+      <c r="D91" s="70" t="inlineStr">
+        <is>
+          <t>서비스 핵심 데이터 관리</t>
+        </is>
+      </c>
+      <c r="E91" s="70" t="inlineStr">
+        <is>
+          <t>세계관·등장인물·작품·회차·Fork·원고·피드백 정보를 서로 연결해 관리해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F91" s="68" t="n"/>
       <c r="G91" s="73" t="inlineStr">
         <is>
-          <t>UC-19</t>
+          <t>UC-02~16 (공통)</t>
         </is>
       </c>
       <c r="H91" s="73" t="inlineStr">
         <is>
-          <t>조건부 기획 / 정책 미정</t>
+          <t>기획 초안 / 개발 계약 미확정</t>
         </is>
       </c>
       <c r="I91" s="73" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="J91" s="73" t="inlineStr">
         <is>
-          <t>조건부 / 작업 미분해</t>
+          <t>2.5·2.6 (저장 기반)</t>
         </is>
       </c>
       <c r="K91" s="2" t="n"/>
@@ -6178,40 +6178,28 @@
       <c r="X91" s="2" t="n"/>
       <c r="Y91" s="2" t="n"/>
     </row>
-    <row r="92" ht="97" customHeight="1" s="109">
-      <c r="A92" s="116" t="inlineStr">
-        <is>
-          <t>REQ14</t>
-        </is>
-      </c>
-      <c r="B92" s="116" t="inlineStr">
-        <is>
-          <t>권리 신고·운영 알림</t>
-        </is>
-      </c>
+    <row r="92" ht="64" customHeight="1" s="109">
+      <c r="A92" s="112" t="n"/>
+      <c r="B92" s="112" t="n"/>
       <c r="C92" s="64" t="inlineStr">
         <is>
-          <t>F-RPT-01</t>
+          <t>F-OPS-02</t>
         </is>
       </c>
       <c r="D92" s="73" t="inlineStr">
         <is>
-          <t>권리 침해 신고 접수</t>
+          <t>시점별 데이터 연결</t>
         </is>
       </c>
       <c r="E92" s="73" t="inlineStr">
         <is>
-          <t>신고자는 대상 작품·회차, 근거, 연락처를 제출할 수 있어야 하며, 대상·근거가 빠진 신고는 보완을 요청해야 합니다.</t>
-        </is>
-      </c>
-      <c r="F92" s="96" t="inlineStr">
-        <is>
-          <t>접수 자격·증빙 기준 미정.</t>
-        </is>
-      </c>
+          <t>설정·인물 상태·사건 기록을 작품과 회차 또는 시점에 연결해 필요한 시점의 맥락을 찾을 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F92" s="96" t="n"/>
       <c r="G92" s="73" t="inlineStr">
         <is>
-          <t>UC-20</t>
+          <t>UC-06, UC-08, UC-12</t>
         </is>
       </c>
       <c r="H92" s="73" t="inlineStr">
@@ -6226,7 +6214,7 @@
       </c>
       <c r="J92" s="73" t="inlineStr">
         <is>
-          <t>5.6 관련 / 세부 작업 미분해</t>
+          <t>2.5·2.6 (저장 기반)</t>
         </is>
       </c>
       <c r="K92" s="2" t="n"/>
@@ -6245,32 +6233,28 @@
       <c r="X92" s="2" t="n"/>
       <c r="Y92" s="2" t="n"/>
     </row>
-    <row r="93" ht="97" customHeight="1" s="109">
+    <row r="93" ht="64" customHeight="1" s="109">
       <c r="A93" s="112" t="n"/>
       <c r="B93" s="112" t="n"/>
       <c r="C93" s="64" t="inlineStr">
         <is>
-          <t>F-RPT-02</t>
+          <t>F-OPS-03</t>
         </is>
       </c>
       <c r="D93" s="73" t="inlineStr">
         <is>
-          <t>즉시 비공개·소명</t>
+          <t>AI 참조 자료 제공</t>
         </is>
       </c>
       <c r="E93" s="73" t="inlineStr">
         <is>
-          <t>권리 신고가 접수되면 운영자에게 바로 알리고, 운영자가 빠르게 검토해 비공개·관련 AI·Fork 기능 중지 등 필요한 조치를 한 뒤 작품 소유자에게 소명 절차를 안내해야 합니다. 운영자가 소명을 검토해 재공개 또는 비공개 유지를 결정합니다.</t>
-        </is>
-      </c>
-      <c r="F93" s="96" t="inlineStr">
-        <is>
-          <t>원작 작가임이 확인된 신고는 즉시 비공개(확정), 그 밖의 조치 기준은 상세 검토 예정. 원작 작가 확인 방법·허위 신고 대응·소명 기한 미정. 신고만으로 원고를 삭제하지 않습니다. 신고 대상이 세계관이면 관련 작품·세계관 Fork 목록을 운영자에게 보여 주고 자동 일괄 조치 없이 건별 판단하며, 관련 소유자에게 경고(신고자 정보 미노출).</t>
-        </is>
-      </c>
+          <t>Core API가 작업별 권한과 작품·회차·Fork 기준을 확인한 최소 문맥만 AI에 제공해야 합니다. AI는 제안만 반환하며 정본·승인·발행·크레딧을 최종 확정하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F93" s="96" t="n"/>
       <c r="G93" s="73" t="inlineStr">
         <is>
-          <t>UC-20</t>
+          <t>UC-04, UC-09, UC-11, UC-12, UC-15</t>
         </is>
       </c>
       <c r="H93" s="73" t="inlineStr">
@@ -6285,7 +6269,7 @@
       </c>
       <c r="J93" s="73" t="inlineStr">
         <is>
-          <t>5.6 관련 / 세부 작업 미분해</t>
+          <t>4.9·5.9 (연동)</t>
         </is>
       </c>
       <c r="K93" s="2" t="n"/>
@@ -6304,32 +6288,28 @@
       <c r="X93" s="2" t="n"/>
       <c r="Y93" s="2" t="n"/>
     </row>
-    <row r="94" ht="97" customHeight="1" s="109">
+    <row r="94" ht="64" customHeight="1" s="109">
       <c r="A94" s="112" t="n"/>
       <c r="B94" s="112" t="n"/>
       <c r="C94" s="64" t="inlineStr">
         <is>
-          <t>F-ALT-01</t>
+          <t>F-OPS-04</t>
         </is>
       </c>
       <c r="D94" s="73" t="inlineStr">
         <is>
-          <t>처리 실패 즉시 고지</t>
+          <t>원작·분기 데이터 격리</t>
         </is>
       </c>
       <c r="E94" s="73" t="inlineStr">
         <is>
-          <t>AI 처리가 실패하거나 기준 시간 안에 끝나지 않으면 대기 상태로 두지 않고 즉시 사용자에게 실패를 알려야 합니다.</t>
-        </is>
-      </c>
-      <c r="F94" s="96" t="inlineStr">
-        <is>
-          <t>지연 기준 시간 미정. 자동 재처리하지 않으며 사용자가 다시 요청합니다.</t>
-        </is>
-      </c>
+          <t>원작·각 Fork·편집 초안·시뮬레이션의 사건·설정·인물 상태를 분리해야 합니다. 폐기한 실행이나 다른 분기의 데이터가 정본·다른 실행에 섞이지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F94" s="96" t="n"/>
       <c r="G94" s="73" t="inlineStr">
         <is>
-          <t>UC-21, UC-14, UC-15</t>
+          <t>UC-08, UC-09</t>
         </is>
       </c>
       <c r="H94" s="73" t="inlineStr">
@@ -6344,7 +6324,7 @@
       </c>
       <c r="J94" s="73" t="inlineStr">
         <is>
-          <t>5.6 관련 / 세부 작업 미분해</t>
+          <t>2.5·2.6 (저장 기반)</t>
         </is>
       </c>
       <c r="K94" s="2" t="n"/>
@@ -6368,27 +6348,27 @@
       <c r="B95" s="112" t="n"/>
       <c r="C95" s="64" t="inlineStr">
         <is>
-          <t>F-ALT-02</t>
+          <t>F-OPS-05</t>
         </is>
       </c>
       <c r="D95" s="73" t="inlineStr">
         <is>
-          <t>운영자 경고·오류 로그</t>
+          <t>사용자 유형별 운영 흐름</t>
         </is>
       </c>
       <c r="E95" s="73" t="inlineStr">
         <is>
-          <t>실패·지연 시 오류 로그를 남기고 운영자에게 경고해야 하며, 로그에 비공개 원고 전문이나 비밀값을 남기지 않아야 합니다.</t>
+          <t>독자·신입 작가·연재 작가의 이용 흐름과 운영 업무를 구분해야 합니다. 운영자는 처리 실패·지연 경고와 오류 로그 확인, 권리 신고 검토를 맡으며 개별 피드백 응대·비공개 원고 무제한 열람·임의 수정 권한을 갖지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F95" s="96" t="inlineStr">
         <is>
-          <t>경고 채널·로그 보관 기간 미정.</t>
+          <t>운영자 단일 역할로 시작(확정). 사용자 AI 작업은 자동 재처리하지 않음. 외부 플랫폼 로그인·스크래핑·자동 게시·동기화는 제외.</t>
         </is>
       </c>
       <c r="G95" s="73" t="inlineStr">
         <is>
-          <t>UC-21</t>
+          <t>UC-21, UC-20</t>
         </is>
       </c>
       <c r="H95" s="73" t="inlineStr">
@@ -6403,7 +6383,7 @@
       </c>
       <c r="J95" s="73" t="inlineStr">
         <is>
-          <t>5.6 관련 / 세부 작업 미분해</t>
+          <t>운영 작업 미분해</t>
         </is>
       </c>
       <c r="K95" s="2" t="n"/>
@@ -6422,17 +6402,57 @@
       <c r="X95" s="2" t="n"/>
       <c r="Y95" s="2" t="n"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" s="109">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
-      <c r="J96" s="2" t="n"/>
+    <row r="96" ht="97" customHeight="1" s="109">
+      <c r="A96" s="50" t="inlineStr">
+        <is>
+          <t>REQ12</t>
+        </is>
+      </c>
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>작품 설정·변경 이력</t>
+        </is>
+      </c>
+      <c r="C96" s="64" t="inlineStr">
+        <is>
+          <t>F-SET-01</t>
+        </is>
+      </c>
+      <c r="D96" s="70" t="inlineStr">
+        <is>
+          <t>작품별 자동 처리 설정</t>
+        </is>
+      </c>
+      <c r="E96" s="70" t="inlineStr">
+        <is>
+          <t>작품 소유자는 작품 설정에서 세계관 업데이트(수동/자동), 표기 오류 수정안(작가 검토/자동 승인·발행), AI 자율 연재(끔/켬)를 선택할 수 있어야 합니다. 기본값은 수동·작가 검토·끔입니다.</t>
+        </is>
+      </c>
+      <c r="F96" s="68" t="inlineStr">
+        <is>
+          <t>크레딧이 드는 자동 처리는 켤 때 예상 비용과 부담 주체(작품 소유자)를 안내하고 동의를 받습니다.</t>
+        </is>
+      </c>
+      <c r="G96" s="73" t="inlineStr">
+        <is>
+          <t>UC-24, UC-04, UC-16, UC-18</t>
+        </is>
+      </c>
+      <c r="H96" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I96" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J96" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n"/>
@@ -6449,17 +6469,49 @@
       <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="n"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" s="109">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="2" t="n"/>
+    <row r="97" ht="97" customHeight="1" s="109">
+      <c r="A97" s="112" t="n"/>
+      <c r="B97" s="112" t="n"/>
+      <c r="C97" s="64" t="inlineStr">
+        <is>
+          <t>F-SET-02</t>
+        </is>
+      </c>
+      <c r="D97" s="73" t="inlineStr">
+        <is>
+          <t>세계관 변경 이력</t>
+        </is>
+      </c>
+      <c r="E97" s="73" t="inlineStr">
+        <is>
+          <t>세계관·인물관계도의 모든 변경을 현재 HEAD 위에 새 버전으로 쌓아 저장하고(덮어쓰기·삭제·머지 없음) 이전 상태를 조회·되돌릴 수 있어야 합니다. 자동 반영 결과도 이력에 남겨야 합니다. 자기 세계관을 고칠 때 함께 반영될 자기 작품 목록을 저장 전에 안내합니다.</t>
+        </is>
+      </c>
+      <c r="F97" s="96" t="inlineStr">
+        <is>
+          <t>저장소는 Gitea(확정). 변경 이력은 무기한 보관(확정). 영향 작품 안내는 조회만 하며 AI를 쓰지 않음.</t>
+        </is>
+      </c>
+      <c r="G97" s="73" t="inlineStr">
+        <is>
+          <t>UC-02, UC-04, UC-06</t>
+        </is>
+      </c>
+      <c r="H97" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I97" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J97" s="73" t="inlineStr">
+        <is>
+          <t>Gitea 구축 작업 WBS 없음</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
@@ -6476,17 +6528,49 @@
       <c r="X97" s="2" t="n"/>
       <c r="Y97" s="2" t="n"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" s="109">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
+    <row r="98" ht="97" customHeight="1" s="109">
+      <c r="A98" s="112" t="n"/>
+      <c r="B98" s="112" t="n"/>
+      <c r="C98" s="64" t="inlineStr">
+        <is>
+          <t>F-SET-03</t>
+        </is>
+      </c>
+      <c r="D98" s="73" t="inlineStr">
+        <is>
+          <t>비공개 설정 공개 전환</t>
+        </is>
+      </c>
+      <c r="E98" s="73" t="inlineStr">
+        <is>
+          <t>비공개 설정집·인물관계도 항목을 특정 회차부터 독자 공개로 전환하고 전환 회차를 기록해야 합니다. 세계관 자동 업데이트 실행 시에도 같은 방식으로 반영합니다.</t>
+        </is>
+      </c>
+      <c r="F98" s="96" t="inlineStr">
+        <is>
+          <t>세계관에서는 항목의 공개·비공개만 정하고, 공개 전환 회차는 연결된 작품에서 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G98" s="73" t="inlineStr">
+        <is>
+          <t>UC-02, UC-06, UC-04</t>
+        </is>
+      </c>
+      <c r="H98" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I98" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J98" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n"/>
@@ -6503,17 +6587,49 @@
       <c r="X98" s="2" t="n"/>
       <c r="Y98" s="2" t="n"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" s="109">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="2" t="n"/>
-      <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
-      <c r="J99" s="2" t="n"/>
+    <row r="99" ht="97" customHeight="1" s="109">
+      <c r="A99" s="112" t="n"/>
+      <c r="B99" s="112" t="n"/>
+      <c r="C99" s="64" t="inlineStr">
+        <is>
+          <t>F-SET-04</t>
+        </is>
+      </c>
+      <c r="D99" s="73" t="inlineStr">
+        <is>
+          <t>외부 2차 창작물 등록</t>
+        </is>
+      </c>
+      <c r="E99" s="73" t="inlineStr">
+        <is>
+          <t>다른 플랫폼에서 가져온 2차 창작물은 작품 유형으로 구분하고 무료 공개만 허용해야 합니다. 등록자에게 권리 책임과 권리 문제 시 운영자 조치·소명 절차를 고지하고 동의를 받아야 합니다. 외부 2차 창작물도 Fork 원작이 될 수 있으며 AI 기능 크레딧은 별도로 청구합니다.</t>
+        </is>
+      </c>
+      <c r="F99" s="96" t="inlineStr">
+        <is>
+          <t>같은 외부 IP는 먼저 올린 작품을 원본으로 인정하고 다른 작품도 허용(확정). 외부 IP의 2차 창작 허용 범위는 등록자가 따르며 플랫폼은 직접 확인하지 않음. 면책 범위는 이용약관·법률 검토 필요.</t>
+        </is>
+      </c>
+      <c r="G99" s="73" t="inlineStr">
+        <is>
+          <t>UC-24, UC-03, UC-13, UC-20</t>
+        </is>
+      </c>
+      <c r="H99" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I99" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J99" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n"/>
@@ -6530,17 +6646,57 @@
       <c r="X99" s="2" t="n"/>
       <c r="Y99" s="2" t="n"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" s="109">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="2" t="n"/>
+    <row r="100" ht="97" customHeight="1" s="109">
+      <c r="A100" s="50" t="inlineStr">
+        <is>
+          <t>REQ13</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="inlineStr">
+        <is>
+          <t>AI 크레딧·저장 관리</t>
+        </is>
+      </c>
+      <c r="C100" s="64" t="inlineStr">
+        <is>
+          <t>F-CRD-01</t>
+        </is>
+      </c>
+      <c r="D100" s="70" t="inlineStr">
+        <is>
+          <t>실행 전 비용 안내·동의</t>
+        </is>
+      </c>
+      <c r="E100" s="70" t="inlineStr">
+        <is>
+          <t>AI 작업 전에 예상 크레딧 범위(상한)·부담 주체·잔여량을 안내하고 동의를 받아야 하며, 실행 후 실제 토큰 사용량을 크레딧으로 환산해 동의한 상한 이내로 차감해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F100" s="68" t="inlineStr">
+        <is>
+          <t>후차감 방식(확정). 잔여가 예상 상한보다 적으면 실행하지 않음. 비용 확인 단계 취소는 '취소됨'·차감 없음. 가격·토큰 환산 비율은 미정.</t>
+        </is>
+      </c>
+      <c r="G100" s="73" t="inlineStr">
+        <is>
+          <t>UC-17</t>
+        </is>
+      </c>
+      <c r="H100" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I100" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J100" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
@@ -6557,17 +6713,49 @@
       <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="n"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" s="109">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="3" t="n"/>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
-      <c r="J101" s="2" t="n"/>
+    <row r="101" ht="97" customHeight="1" s="109">
+      <c r="A101" s="112" t="n"/>
+      <c r="B101" s="112" t="n"/>
+      <c r="C101" s="64" t="inlineStr">
+        <is>
+          <t>F-CRD-02</t>
+        </is>
+      </c>
+      <c r="D101" s="73" t="inlineStr">
+        <is>
+          <t>크레딧 부담 주체</t>
+        </is>
+      </c>
+      <c r="E101" s="73" t="inlineStr">
+        <is>
+          <t>AI 크레딧은 요청하거나 자동 실행을 설정한 사용자에게 청구해야 합니다. 피드백 등록은 무료이며, 단순 오류·질문 응대와 유해 콘텐츠 필터는 플랫폼이, 독자가 고른 스토리 오류 검증 시뮬레이션은 독자가, 자율 연재·세계관 자동 업데이트는 작품 소유자가 부담합니다. 작품 Fork·세계관 Fork 생성, 직접 집필은 무료입니다.</t>
+        </is>
+      </c>
+      <c r="F101" s="96" t="inlineStr">
+        <is>
+          <t>팀 결정으로 확정.</t>
+        </is>
+      </c>
+      <c r="G101" s="73" t="inlineStr">
+        <is>
+          <t>UC-17, UC-14, UC-09, UC-04, UC-18</t>
+        </is>
+      </c>
+      <c r="H101" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I101" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J101" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
@@ -6584,17 +6772,49 @@
       <c r="X101" s="2" t="n"/>
       <c r="Y101" s="2" t="n"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" s="109">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
-      <c r="I102" s="2" t="n"/>
-      <c r="J102" s="2" t="n"/>
+    <row r="102" ht="97" customHeight="1" s="109">
+      <c r="A102" s="112" t="n"/>
+      <c r="B102" s="112" t="n"/>
+      <c r="C102" s="64" t="inlineStr">
+        <is>
+          <t>F-CRD-03</t>
+        </is>
+      </c>
+      <c r="D102" s="73" t="inlineStr">
+        <is>
+          <t>사용 내역·오류 복구</t>
+        </is>
+      </c>
+      <c r="E102" s="73" t="inlineStr">
+        <is>
+          <t>실제 사용량과 결과 상태를 기록하고, 서비스 오류로 완료되지 않은 작업은 성공과 구분해 복구 기준에 따라 처리해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F102" s="96" t="inlineStr">
+        <is>
+          <t>실패·시간 초과는 차감 없음(토큰 비용 플랫폼 부담), 긴 작업 실행 중 중단은 사용분만 차감(확정). 동의 없는 재차감 금지.</t>
+        </is>
+      </c>
+      <c r="G102" s="73" t="inlineStr">
+        <is>
+          <t>UC-17, UC-21</t>
+        </is>
+      </c>
+      <c r="H102" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I102" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J102" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n"/>
@@ -6611,17 +6831,49 @@
       <c r="X102" s="2" t="n"/>
       <c r="Y102" s="2" t="n"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" s="109">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
-      <c r="J103" s="2" t="n"/>
+    <row r="103" ht="80" customHeight="1" s="109">
+      <c r="A103" s="112" t="n"/>
+      <c r="B103" s="112" t="n"/>
+      <c r="C103" s="64" t="inlineStr">
+        <is>
+          <t>F-CRD-04</t>
+        </is>
+      </c>
+      <c r="D103" s="73" t="inlineStr">
+        <is>
+          <t>크레딧 종류·소멸</t>
+        </is>
+      </c>
+      <c r="E103" s="73" t="inlineStr">
+        <is>
+          <t>크레딧을 무료(가입 체험·보상·이벤트)와 유료(구독·추가 구매)로 구분하고, 종류별 소멸 기준과 차감 순서를 적용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F103" s="96" t="inlineStr">
+        <is>
+          <t>가입 체험 30일, 보상·이벤트 월 소멸, 구독 매달 초기화(이월 없음), 추가 구매는 구독 회원만·12개월, 소멸이 빠른 것부터 차감(확정). 현재는 실결제 없이 테스트 크레딧. 플랜·가격 미정.</t>
+        </is>
+      </c>
+      <c r="G103" s="73" t="inlineStr">
+        <is>
+          <t>UC-17</t>
+        </is>
+      </c>
+      <c r="H103" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I103" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J103" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-11)</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="2" t="n"/>
@@ -6638,17 +6890,49 @@
       <c r="X103" s="2" t="n"/>
       <c r="Y103" s="2" t="n"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" s="109">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="3" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="3" t="n"/>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
-      <c r="J104" s="2" t="n"/>
+    <row r="104" ht="80" customHeight="1" s="109">
+      <c r="A104" s="112" t="n"/>
+      <c r="B104" s="112" t="n"/>
+      <c r="C104" s="64" t="inlineStr">
+        <is>
+          <t>F-CRD-05</t>
+        </is>
+      </c>
+      <c r="D104" s="73" t="inlineStr">
+        <is>
+          <t>AI 요청 속도 제한</t>
+        </is>
+      </c>
+      <c r="E104" s="73" t="inlineStr">
+        <is>
+          <t>Core API는 사용자별 분당 요청 수·토큰 수와 플랫폼 전체 한도를 토큰 버킷 방식으로 제한하고, 초과 시 차감 없이 다시 시도할 시점을 안내해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F104" s="96" t="inlineStr">
+        <is>
+          <t>플랜별 한도(확정 방식). 한도 값·상태 저장 방식은 구현 시 결정.</t>
+        </is>
+      </c>
+      <c r="G104" s="73" t="inlineStr">
+        <is>
+          <t>UC-17</t>
+        </is>
+      </c>
+      <c r="H104" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I104" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J104" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-11)</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
@@ -6665,17 +6949,49 @@
       <c r="X104" s="2" t="n"/>
       <c r="Y104" s="2" t="n"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" s="109">
-      <c r="A105" s="2" t="n"/>
-      <c r="B105" s="3" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2" t="n"/>
-      <c r="I105" s="2" t="n"/>
-      <c r="J105" s="2" t="n"/>
+    <row r="105" ht="97" customHeight="1" s="109">
+      <c r="A105" s="112" t="n"/>
+      <c r="B105" s="112" t="n"/>
+      <c r="C105" s="64" t="inlineStr">
+        <is>
+          <t>F-STO-01</t>
+        </is>
+      </c>
+      <c r="D105" s="73" t="inlineStr">
+        <is>
+          <t>저장 사용량 확인·정리</t>
+        </is>
+      </c>
+      <c r="E105" s="73" t="inlineStr">
+        <is>
+          <t>사용자는 저장 사용량을 확인하고 정리·확장을 선택할 수 있어야 하며, 한도 초과로 기존 작품을 자동 삭제하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F105" s="96" t="inlineStr">
+        <is>
+          <t>용량·요금·삭제 복원 정책 미정.</t>
+        </is>
+      </c>
+      <c r="G105" s="73" t="inlineStr">
+        <is>
+          <t>UC-19</t>
+        </is>
+      </c>
+      <c r="H105" s="73" t="inlineStr">
+        <is>
+          <t>조건부 기획 / 정책 미정</t>
+        </is>
+      </c>
+      <c r="I105" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J105" s="73" t="inlineStr">
+        <is>
+          <t>조건부 / 작업 미분해</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
@@ -6692,17 +7008,57 @@
       <c r="X105" s="2" t="n"/>
       <c r="Y105" s="2" t="n"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" s="109">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="3" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="3" t="n"/>
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
-      <c r="J106" s="2" t="n"/>
+    <row r="106" ht="97" customHeight="1" s="109">
+      <c r="A106" s="50" t="inlineStr">
+        <is>
+          <t>REQ14</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>권리 신고·운영 알림</t>
+        </is>
+      </c>
+      <c r="C106" s="64" t="inlineStr">
+        <is>
+          <t>F-RPT-01</t>
+        </is>
+      </c>
+      <c r="D106" s="70" t="inlineStr">
+        <is>
+          <t>권리 침해 신고 접수</t>
+        </is>
+      </c>
+      <c r="E106" s="70" t="inlineStr">
+        <is>
+          <t>신고자는 대상 작품·회차, 근거, 연락처를 제출할 수 있어야 하며, 대상·근거가 빠진 신고는 보완을 요청해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F106" s="68" t="inlineStr">
+        <is>
+          <t>로그인한 회원만 접수(확정). 증빙 기준은 다른 플랫폼 사례 조사 후 반영.</t>
+        </is>
+      </c>
+      <c r="G106" s="73" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+      <c r="H106" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I106" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J106" s="73" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
@@ -6719,17 +7075,49 @@
       <c r="X106" s="2" t="n"/>
       <c r="Y106" s="2" t="n"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" s="109">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="3" t="n"/>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="2" t="n"/>
+    <row r="107" ht="97" customHeight="1" s="109">
+      <c r="A107" s="112" t="n"/>
+      <c r="B107" s="112" t="n"/>
+      <c r="C107" s="64" t="inlineStr">
+        <is>
+          <t>F-RPT-02</t>
+        </is>
+      </c>
+      <c r="D107" s="73" t="inlineStr">
+        <is>
+          <t>즉시 비공개·소명</t>
+        </is>
+      </c>
+      <c r="E107" s="73" t="inlineStr">
+        <is>
+          <t>권리 신고가 접수되면 운영자에게 바로 알리고, 운영자가 빠르게 검토해 비공개·관련 AI·Fork 기능 중지 등 필요한 조치를 한 뒤 작품 소유자에게 소명 절차를 안내해야 합니다. 운영자가 소명을 검토해 재공개 또는 비공개 유지를 결정합니다.</t>
+        </is>
+      </c>
+      <c r="F107" s="96" t="inlineStr">
+        <is>
+          <t>원작 작가 확인(운영자 교차 확인) 시 즉시 비공개, 그 밖은 접수 후 24시간 내 1차 조치·미조치 시 지연 경고, 소명 7일(1회 7일 연장), 허위 신고 3회 시 30일 신고 제한, 신고·조치·소명 기록 1년 보관(확정, 법률 검토 후 조정). 원작 작품 조치는 Fork에도 적용. 신고만으로 원고를 삭제하지 않음. 세계관 신고는 관련 작품을 건별 판단하고 관련 소유자에게 경고(신고자 정보 미노출).</t>
+        </is>
+      </c>
+      <c r="G107" s="73" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+      <c r="H107" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I107" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J107" s="73" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
@@ -6746,17 +7134,49 @@
       <c r="X107" s="2" t="n"/>
       <c r="Y107" s="2" t="n"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" s="109">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="2" t="n"/>
-      <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="n"/>
-      <c r="J108" s="2" t="n"/>
+    <row r="108" ht="80" customHeight="1" s="109">
+      <c r="A108" s="112" t="n"/>
+      <c r="B108" s="112" t="n"/>
+      <c r="C108" s="64" t="inlineStr">
+        <is>
+          <t>F-RPT-03</t>
+        </is>
+      </c>
+      <c r="D108" s="73" t="inlineStr">
+        <is>
+          <t>유해 콘텐츠 신고(회차)</t>
+        </is>
+      </c>
+      <c r="E108" s="73" t="inlineStr">
+        <is>
+          <t>회원은 회차 본문의 유해 콘텐츠(인격권 침해 포함)를 신고할 수 있어야 하며, 시스템은 판정 모델 재검사 결과를 붙여 운영자 확인 목록에 올려야 합니다.</t>
+        </is>
+      </c>
+      <c r="F108" s="96" t="inlineStr">
+        <is>
+          <t>회차는 오판 위험으로 자동 숨김 없이 운영자가 UC-20 절차로 조치(확정). 신고 유형은 권리 침해·유해 콘텐츠 두 가지.</t>
+        </is>
+      </c>
+      <c r="G108" s="73" t="inlineStr">
+        <is>
+          <t>UC-20, UC-14</t>
+        </is>
+      </c>
+      <c r="H108" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I108" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J108" s="73" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
@@ -6773,17 +7193,49 @@
       <c r="X108" s="2" t="n"/>
       <c r="Y108" s="2" t="n"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" s="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="3" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="3" t="n"/>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="n"/>
+    <row r="109" ht="97" customHeight="1" s="109">
+      <c r="A109" s="112" t="n"/>
+      <c r="B109" s="112" t="n"/>
+      <c r="C109" s="64" t="inlineStr">
+        <is>
+          <t>F-ALT-01</t>
+        </is>
+      </c>
+      <c r="D109" s="73" t="inlineStr">
+        <is>
+          <t>처리 실패 즉시 고지</t>
+        </is>
+      </c>
+      <c r="E109" s="73" t="inlineStr">
+        <is>
+          <t>AI 처리가 실패하거나 기준 시간 안에 끝나지 않으면 대기 상태로 두지 않고 즉시 사용자에게 실패를 알려야 합니다.</t>
+        </is>
+      </c>
+      <c r="F109" s="96" t="inlineStr">
+        <is>
+          <t>시간 초과 기준: 질문·단순 오류 응대 2분, 집필 지원 3분, 시뮬레이션·자율 연재 회차 생성 10분(확정, 구현 시 조정). 자동 재처리하지 않으며 사용자가 다시 요청합니다.</t>
+        </is>
+      </c>
+      <c r="G109" s="73" t="inlineStr">
+        <is>
+          <t>UC-21, UC-14, UC-15</t>
+        </is>
+      </c>
+      <c r="H109" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I109" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J109" s="73" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
@@ -6800,17 +7252,49 @@
       <c r="X109" s="2" t="n"/>
       <c r="Y109" s="2" t="n"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" s="109">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="3" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="3" t="n"/>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
-      <c r="J110" s="2" t="n"/>
+    <row r="110" ht="97" customHeight="1" s="109">
+      <c r="A110" s="112" t="n"/>
+      <c r="B110" s="112" t="n"/>
+      <c r="C110" s="64" t="inlineStr">
+        <is>
+          <t>F-ALT-02</t>
+        </is>
+      </c>
+      <c r="D110" s="73" t="inlineStr">
+        <is>
+          <t>운영자 경고·오류 로그</t>
+        </is>
+      </c>
+      <c r="E110" s="73" t="inlineStr">
+        <is>
+          <t>실패·지연 시 오류 로그를 남기고 운영자에게 경고해야 하며, 로그에 비공개 원고 전문이나 비밀값을 남기지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F110" s="96" t="inlineStr">
+        <is>
+          <t>경고는 운영 화면 경고 목록·사이트 안 알림만, 오류 로그 90일 보관(확정). 정기 작업 실패(UC-28)·AI 지표 이상(UC-26)도 같은 경고 목록.</t>
+        </is>
+      </c>
+      <c r="G110" s="73" t="inlineStr">
+        <is>
+          <t>UC-21</t>
+        </is>
+      </c>
+      <c r="H110" s="73" t="inlineStr">
+        <is>
+          <t>기획 초안 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I110" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J110" s="73" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
@@ -6827,17 +7311,57 @@
       <c r="X110" s="2" t="n"/>
       <c r="Y110" s="2" t="n"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" s="109">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-      <c r="J111" s="2" t="n"/>
+    <row r="111" ht="80" customHeight="1" s="109">
+      <c r="A111" s="50" t="inlineStr">
+        <is>
+          <t>REQ15</t>
+        </is>
+      </c>
+      <c r="B111" s="51" t="inlineStr">
+        <is>
+          <t>알림·정기 작업</t>
+        </is>
+      </c>
+      <c r="C111" s="64" t="inlineStr">
+        <is>
+          <t>F-NTF-01</t>
+        </is>
+      </c>
+      <c r="D111" s="70" t="inlineStr">
+        <is>
+          <t>알림함</t>
+        </is>
+      </c>
+      <c r="E111" s="70" t="inlineStr">
+        <is>
+          <t>회원은 자신과 관련된 처리 결과·상태 변화를 사이트 안 알림함에서 확인하고 읽음 처리할 수 있어야 합니다. 같은 종류가 몰리면 묶어 표시합니다.</t>
+        </is>
+      </c>
+      <c r="F111" s="68" t="inlineStr">
+        <is>
+          <t>사이트 안 알림만, 이메일은 인증·보안 메일만, 90일 보관(확정). 웹 푸시는 추후.</t>
+        </is>
+      </c>
+      <c r="G111" s="73" t="inlineStr">
+        <is>
+          <t>UC-27</t>
+        </is>
+      </c>
+      <c r="H111" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I111" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J111" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-12)</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
@@ -6854,17 +7378,49 @@
       <c r="X111" s="2" t="n"/>
       <c r="Y111" s="2" t="n"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" s="109">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
-      <c r="J112" s="2" t="n"/>
+    <row r="112" ht="80" customHeight="1" s="109">
+      <c r="A112" s="112" t="n"/>
+      <c r="B112" s="112" t="n"/>
+      <c r="C112" s="64" t="inlineStr">
+        <is>
+          <t>F-NTF-02</t>
+        </is>
+      </c>
+      <c r="D112" s="73" t="inlineStr">
+        <is>
+          <t>알림 설정</t>
+        </is>
+      </c>
+      <c r="E112" s="73" t="inlineStr">
+        <is>
+          <t>회원은 끌 수 있는 알림 종류(관심 소설 새 회차·새 댓글·자율 연재 결과·세계관 변경 등)를 켜고 끌 수 있어야 합니다. 권리·처리 실패·크레딧·보안 알림은 끌 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="F112" s="96" t="inlineStr">
+        <is>
+          <t>기본값 모두 켜짐(확정).</t>
+        </is>
+      </c>
+      <c r="G112" s="73" t="inlineStr">
+        <is>
+          <t>UC-27</t>
+        </is>
+      </c>
+      <c r="H112" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I112" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J112" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-12)</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
@@ -6881,17 +7437,49 @@
       <c r="X112" s="2" t="n"/>
       <c r="Y112" s="2" t="n"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" s="109">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="2" t="n"/>
-      <c r="G113" s="2" t="n"/>
-      <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
-      <c r="J113" s="2" t="n"/>
+    <row r="113" ht="80" customHeight="1" s="109">
+      <c r="A113" s="112" t="n"/>
+      <c r="B113" s="112" t="n"/>
+      <c r="C113" s="64" t="inlineStr">
+        <is>
+          <t>F-JOB-01</t>
+        </is>
+      </c>
+      <c r="D113" s="73" t="inlineStr">
+        <is>
+          <t>정기 작업 실행·기록</t>
+        </is>
+      </c>
+      <c r="E113" s="73" t="inlineStr">
+        <is>
+          <t>시스템은 기한·주기 규칙(자율 연재, 필터 재검사, 크레딧 초기화·소멸, 탈퇴 처리, 소명 기한, 로그·알림 정리, 검색 색인 동기화, 비용 집계)을 정해진 시점에 실행하고 결과를 기록해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F113" s="96" t="inlineStr">
+        <is>
+          <t>Core API 내장 스케줄러 하나, worker·큐 없음, 같은 대상 중복 처리 금지(확정). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
+        </is>
+      </c>
+      <c r="G113" s="73" t="inlineStr">
+        <is>
+          <t>UC-28</t>
+        </is>
+      </c>
+      <c r="H113" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I113" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J113" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-12)</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
@@ -6908,17 +7496,49 @@
       <c r="X113" s="2" t="n"/>
       <c r="Y113" s="2" t="n"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" s="109">
-      <c r="A114" s="2" t="n"/>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
-      <c r="J114" s="2" t="n"/>
+    <row r="114" ht="80" customHeight="1" s="109">
+      <c r="A114" s="112" t="n"/>
+      <c r="B114" s="112" t="n"/>
+      <c r="C114" s="64" t="inlineStr">
+        <is>
+          <t>F-JOB-02</t>
+        </is>
+      </c>
+      <c r="D114" s="73" t="inlineStr">
+        <is>
+          <t>정기 작업 감시·재실행</t>
+        </is>
+      </c>
+      <c r="E114" s="73" t="inlineStr">
+        <is>
+          <t>운영자는 정기 작업별 마지막 실행 시각과 결과를 확인하고, 실패한 작업을 수동으로 다시 실행할 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F114" s="96" t="inlineStr">
+        <is>
+          <t>실패·지연은 UC-21 경고(확정). 사용자 AI 작업은 자동 재처리하지 않음.</t>
+        </is>
+      </c>
+      <c r="G114" s="73" t="inlineStr">
+        <is>
+          <t>UC-28, UC-21</t>
+        </is>
+      </c>
+      <c r="H114" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I114" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J114" s="73" t="inlineStr">
+        <is>
+          <t>작업 미분해 (개발현황 GAP-12)</t>
+        </is>
+      </c>
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
@@ -6935,17 +7555,57 @@
       <c r="X114" s="2" t="n"/>
       <c r="Y114" s="2" t="n"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" s="109">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-      <c r="J115" s="2" t="n"/>
+    <row r="115" ht="80" customHeight="1" s="109">
+      <c r="A115" s="50" t="inlineStr">
+        <is>
+          <t>REQ16</t>
+        </is>
+      </c>
+      <c r="B115" s="51" t="inlineStr">
+        <is>
+          <t>AI 운영(LLMOps)</t>
+        </is>
+      </c>
+      <c r="C115" s="64" t="inlineStr">
+        <is>
+          <t>F-LLM-01</t>
+        </is>
+      </c>
+      <c r="D115" s="70" t="inlineStr">
+        <is>
+          <t>AI 호출 추적</t>
+        </is>
+      </c>
+      <c r="E115" s="70" t="inlineStr">
+        <is>
+          <t>AI Service는 작업마다 요청 ID·작업 유형·LangGraph 단계·모델·프롬프트 버전·토큰·지연·비용·결과 상태를 Langfuse에 기록해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F115" s="68" t="inlineStr">
+        <is>
+          <t>Langfuse는 Docker로 직접 설치, 메타데이터만 전송(원고 원문·비공개 설정·개인정보 제외)(확정). 기록 보관 기간 미정.</t>
+        </is>
+      </c>
+      <c r="G115" s="73" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="H115" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I115" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J115" s="73" t="inlineStr">
+        <is>
+          <t>WBS 없음 (개발현황 GAP-13)</t>
+        </is>
+      </c>
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="2" t="n"/>
@@ -6962,17 +7622,49 @@
       <c r="X115" s="2" t="n"/>
       <c r="Y115" s="2" t="n"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" s="109">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
-      <c r="J116" s="2" t="n"/>
+    <row r="116" ht="80" customHeight="1" s="109">
+      <c r="A116" s="112" t="n"/>
+      <c r="B116" s="112" t="n"/>
+      <c r="C116" s="64" t="inlineStr">
+        <is>
+          <t>F-LLM-02</t>
+        </is>
+      </c>
+      <c r="D116" s="73" t="inlineStr">
+        <is>
+          <t>프롬프트·모델 버전 관리</t>
+        </is>
+      </c>
+      <c r="E116" s="73" t="inlineStr">
+        <is>
+          <t>프롬프트를 버전으로 관리하고 AI 결과마다 사용한 버전을 기록하며, 문제가 생기면 이전 버전으로 되돌릴 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="F116" s="96" t="inlineStr">
+        <is>
+          <t>되돌려도 이미 생성된 결과는 바꾸지 않음(확정).</t>
+        </is>
+      </c>
+      <c r="G116" s="73" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="H116" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I116" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J116" s="73" t="inlineStr">
+        <is>
+          <t>WBS 없음 (개발현황 GAP-13)</t>
+        </is>
+      </c>
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="2" t="n"/>
@@ -6989,17 +7681,49 @@
       <c r="X116" s="2" t="n"/>
       <c r="Y116" s="2" t="n"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" s="109">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="2" t="n"/>
-      <c r="G117" s="2" t="n"/>
-      <c r="H117" s="2" t="n"/>
-      <c r="I117" s="2" t="n"/>
-      <c r="J117" s="2" t="n"/>
+    <row r="117" ht="80" customHeight="1" s="109">
+      <c r="A117" s="112" t="n"/>
+      <c r="B117" s="112" t="n"/>
+      <c r="C117" s="64" t="inlineStr">
+        <is>
+          <t>F-LLM-03</t>
+        </is>
+      </c>
+      <c r="D117" s="73" t="inlineStr">
+        <is>
+          <t>변경 전 회귀 평가</t>
+        </is>
+      </c>
+      <c r="E117" s="73" t="inlineStr">
+        <is>
+          <t>프롬프트·모델을 바꾸기 전에 고정 평가 세트(설정 충돌 탐지, 근거 인용 정확도, 단순 오류 수정 정확도, 인물 지식·스포일러 누설)로 기존 버전과 비교해 나빠지면 배포하지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F117" s="96" t="inlineStr">
+        <is>
+          <t>평가 세트는 이용 조건을 확인한 저작권 만료 작품으로 구성(확정). 구성·통과 기준 미정.</t>
+        </is>
+      </c>
+      <c r="G117" s="73" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="H117" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I117" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J117" s="73" t="inlineStr">
+        <is>
+          <t>4.10·4.11 관련 / 세부 작업 미분해</t>
+        </is>
+      </c>
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n"/>
@@ -7016,17 +7740,49 @@
       <c r="X117" s="2" t="n"/>
       <c r="Y117" s="2" t="n"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" s="109">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-      <c r="J118" s="2" t="n"/>
+    <row r="118" ht="80" customHeight="1" s="109">
+      <c r="A118" s="112" t="n"/>
+      <c r="B118" s="112" t="n"/>
+      <c r="C118" s="64" t="inlineStr">
+        <is>
+          <t>F-LLM-04</t>
+        </is>
+      </c>
+      <c r="D118" s="73" t="inlineStr">
+        <is>
+          <t>AI 품질·비용 지표와 경고</t>
+        </is>
+      </c>
+      <c r="E118" s="73" t="inlineStr">
+        <is>
+          <t>운영자는 실패율·시간 초과율·지연·토큰·비용(사용자·플랫폼 부담 구분)과 제안 채택률·수정안 승인률·필터 복원률을 확인하고, 기준 초과 시 경고를 받아야 합니다.</t>
+        </is>
+      </c>
+      <c r="F118" s="96" t="inlineStr">
+        <is>
+          <t>UI 프로토타입 A05를 운영 화면으로 확정. 경고 기준 값 미정.</t>
+        </is>
+      </c>
+      <c r="G118" s="73" t="inlineStr">
+        <is>
+          <t>UC-26, UC-21, UC-28</t>
+        </is>
+      </c>
+      <c r="H118" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I118" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J118" s="73" t="inlineStr">
+        <is>
+          <t>WBS 없음 (개발현황 GAP-13)</t>
+        </is>
+      </c>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="2" t="n"/>
@@ -7043,17 +7799,49 @@
       <c r="X118" s="2" t="n"/>
       <c r="Y118" s="2" t="n"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" s="109">
-      <c r="A119" s="2" t="n"/>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
-      <c r="J119" s="2" t="n"/>
+    <row r="119" ht="80" customHeight="1" s="109">
+      <c r="A119" s="112" t="n"/>
+      <c r="B119" s="112" t="n"/>
+      <c r="C119" s="64" t="inlineStr">
+        <is>
+          <t>F-LLM-05</t>
+        </is>
+      </c>
+      <c r="D119" s="73" t="inlineStr">
+        <is>
+          <t>정보 누설 표본 검사</t>
+        </is>
+      </c>
+      <c r="E119" s="73" t="inlineStr">
+        <is>
+          <t>시스템은 AI 응답 표본에 작가 비공개 설정이나 독자가 보지 않은 회차 내용이 섞였는지 자동 검사하고 의심 건을 경고해야 합니다.</t>
+        </is>
+      </c>
+      <c r="F119" s="96" t="inlineStr">
+        <is>
+          <t>BR-02 운영 확인 장치(확정). 표본 비율 미정.</t>
+        </is>
+      </c>
+      <c r="G119" s="73" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="H119" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정 / 개발 계약 미확정</t>
+        </is>
+      </c>
+      <c r="I119" s="73" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="J119" s="73" t="inlineStr">
+        <is>
+          <t>WBS 없음 (개발현황 GAP-13)</t>
+        </is>
+      </c>
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
@@ -13401,37 +14189,41 @@
       <c r="E989" s="49" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A4:A11"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A58:A69"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="B12:B19"/>
-    <mergeCell ref="B88:B91"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="B30:B36"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A47:A57"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="B58:B69"/>
-    <mergeCell ref="A37:A46"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="A70:A74"/>
+  <mergeCells count="34">
+    <mergeCell ref="B53:B66"/>
+    <mergeCell ref="B42:B52"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B100:B105"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="B111:B114"/>
+    <mergeCell ref="A115:A119"/>
+    <mergeCell ref="A53:A66"/>
+    <mergeCell ref="B67:B81"/>
+    <mergeCell ref="A106:A110"/>
+    <mergeCell ref="A91:A95"/>
+    <mergeCell ref="A4:A12"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="B35:B41"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="A42:A52"/>
+    <mergeCell ref="B106:B110"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A67:A81"/>
+    <mergeCell ref="A96:A99"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B47:B57"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B37:B46"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A111:A114"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13443,7 +14235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="19" customWidth="1" style="109" min="1" max="1"/>
@@ -13520,7 +14312,7 @@
       </c>
       <c r="D4" s="73" t="inlineStr">
         <is>
-          <t>원본 11개 요구사항 그룹·80개 기능 ID 유지. 문구 정합성 보완과 G:J 추적 열 추가. 새 기능 ID·담당자·일정은 임의 부여하지 않음. 유스케이스 v3 반영으로 3개 그룹·12개 ID(F-SET·F-CRD·F-STO·F-RPT·F-ALT) 추가.</t>
+          <t>원본 11개 요구사항 그룹·80개 기능 ID 유지. 문구 정합성 보완과 G:J 추적 열 추가. 새 기능 ID·담당자·일정은 임의 부여하지 않음. 유스케이스 v3 반영으로 3개 그룹·12개 ID(F-SET·F-CRD·F-STO·F-RPT·F-ALT) 추가. 유스케이스 v6 반영으로 2개 그룹(REQ15 알림·정기 작업, REQ16 AI 운영)과 24개 ID 추가, F-FBK-02·03은 독자 유형 선택 기준으로 재정의(총 116개).</t>
         </is>
       </c>
       <c r="E4" s="73" t="inlineStr">
@@ -13731,12 +14523,12 @@
       </c>
       <c r="C12" s="73" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>v6 확정 / 일부 미정</t>
         </is>
       </c>
       <c r="D12" s="73" t="inlineStr">
         <is>
-          <t>가입 필수 항목·인증 방식·세션·복구·탈퇴 데이터·비회원·공동 집필·운영 역할은 합의 필요. 기존 계정 지원 요구는 삭제하지 않음.</t>
+          <t>이메일 인증, 접근 토큰 30분·갱신 토큰 14일, 로그아웃 시 갱신 토큰 폐기, 다중 기기, 30일 유예 탈퇴, 비회원 열람만(v6 확정). 약관·선택 동의·로그인 잠금 기준은 미정.</t>
         </is>
       </c>
       <c r="E12" s="73" t="inlineStr">
@@ -13758,12 +14550,12 @@
       </c>
       <c r="C13" s="73" t="inlineStr">
         <is>
-          <t>미정</t>
+          <t>v6 확정 / 일부 미정</t>
         </is>
       </c>
       <c r="D13" s="73" t="inlineStr">
         <is>
-          <t>입력 형식·크기·중복·회차 구분, 세계관 업데이트 수용, 자동 저장·동시 수정·버전 보관·발행본 변경을 구현 전에 정할 것.</t>
+          <t>.txt·.epub 가져오기·내보내기, 이미지 삽입, 회차 자동 구분, 재등록은 새 초안 버전, 자동 저장·충돌 재확인·버전 무기한 보관(v6 확정). 이미지 저장 위치·자동 저장 간격은 미정.</t>
         </is>
       </c>
       <c r="E13" s="73" t="inlineStr">
@@ -13785,12 +14577,12 @@
       </c>
       <c r="C14" s="73" t="inlineStr">
         <is>
-          <t>일부 정책 미정</t>
+          <t>v6 확정 / 일부 미정</t>
         </is>
       </c>
       <c r="D14" s="73" t="inlineStr">
         <is>
-          <t>해석·선호를 오류로 단정하지 않음. 응대는 허용 공개 근거만 사용. 스포일러 범위·답변 공개 수준·알림 채널·승인 후 공개 반영 시점 미정.</t>
+          <t>독자가 유형 선택(AI 분류 없음, BR-15), 단순 오류와 스토리 오류 분리, 제보 무료, 검증 시뮬레이션은 독자 선택·반영 시 보상, 유해 콘텐츠 1차 필터, 스포일러는 독자가 본 회차까지(v6 확정). 보상 상한 값·재검사 주기는 미정.</t>
         </is>
       </c>
       <c r="E14" s="73" t="inlineStr">
@@ -13817,7 +14609,7 @@
       </c>
       <c r="D15" s="73" t="inlineStr">
         <is>
-          <t>생성·발행을 구분. 실행·중단·재개·검토·예산·반응 반영 정책 합의 전 개발 범위를 확정하지 않음. 투표·좋아요·스케줄러가 승인된 것은 아님.</t>
+          <t>자동 발행, 소유자 지정 요일·시각 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단, 발행 전 확인 옵션(기본 꺼짐), Core API 내장 스케줄러(v6 확정). 다중 서버 중복 실행 방지는 미정.</t>
         </is>
       </c>
       <c r="E15" s="73" t="inlineStr">
@@ -13844,7 +14636,7 @@
       </c>
       <c r="D16" s="73" t="inlineStr">
         <is>
-          <t>크레딧은 요청·설정한 사용자 부담(피드백 분석은 제보자)으로 확정. 가격·무료 제공량·차감 시점·복구는 미정.</t>
+          <t>실행 후 실제 토큰 사용량 환산 차감(상한 이내), 실패 시 차감 없음, 무료(가입 체험·보상·이벤트)·유료(구독·추가 구매) 크레딧, 토큰 버킷 속도 제한(v6 확정). 플랜·가격·환산 비율은 미정.</t>
         </is>
       </c>
       <c r="E16" s="73" t="inlineStr">
@@ -13898,7 +14690,7 @@
       </c>
       <c r="D18" s="73" t="inlineStr">
         <is>
-          <t>신고 접수 시 운영자가 빠르게 검토·조치(비공개 등)하고 소명 절차를 엶. 즉시 비공개 여부 등 상세 절차는 검토 예정. 증빙·소명 기한·허위 신고 대응·기존 Fork 영향은 미정.</t>
+          <t>회원만 접수, 24시간 내 1차 조치, 소명 7일(1회 연장), 허위 신고 3회 시 30일 제한, 회차 유해 콘텐츠 신고 추가(v6 확정). 증빙 기준은 다른 플랫폼 사례 조사 후 반영.</t>
         </is>
       </c>
       <c r="E18" s="73" t="inlineStr">
@@ -13925,7 +14717,7 @@
       </c>
       <c r="D19" s="73" t="inlineStr">
         <is>
-          <t>실패·지연 즉시 고지(대기 없음), 운영자 경고·오류 로그 확정. 지연 기준·경고 채널·로그 보관은 미정.</t>
+          <t>작업별 시간 초과(응대 2분·집필 3분·시뮬레이션·자율 연재 10분), 운영 화면·사이트 안 알림 경고, 오류 로그 90일(v6 확정).</t>
         </is>
       </c>
       <c r="E19" s="73" t="inlineStr">
@@ -14006,7 +14798,7 @@
       </c>
       <c r="D22" s="73" t="inlineStr">
         <is>
-          <t>자율 연재 자동 발행(원작·Fork, 작품 소유자 부담), JWT 이메일·비밀번호 로그인(소셜 추후), .txt·에디터 입력.</t>
+          <t>자율 연재 자동 발행(원작·Fork, 작품 소유자 부담), JWT 이메일·비밀번호 로그인(소셜 추후), .txt·.epub·에디터 입력(v6에서 .epub 추가).</t>
         </is>
       </c>
       <c r="E22" s="73" t="inlineStr">
@@ -14136,17 +14928,179 @@
       </c>
       <c r="C27" s="73" t="inlineStr">
         <is>
-          <t>기능 ID 미부여</t>
+          <t>채택·MVP 제외 / F-PUB-07</t>
         </is>
       </c>
       <c r="D27" s="73" t="inlineStr">
         <is>
-          <t>UI 프로토타입에서 제안된 캐릭터 챗을 후보 유스케이스로 추가. 채택 시 기능 ID 부여.</t>
+          <t>UI 프로토타입에서 제안된 캐릭터 챗을 v6에서 채택하되 첫 출시(MVP) 범위에서 제외. 기능 ID F-PUB-07 부여.</t>
         </is>
       </c>
       <c r="E27" s="73" t="inlineStr">
         <is>
           <t>usecase.md §3.1; usecase-spec/UC-25.md; prototype-alignment.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1" s="109">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="inlineStr">
+        <is>
+          <t>AI 이용 권한</t>
+        </is>
+      </c>
+      <c r="C28" s="73" t="inlineStr">
+        <is>
+          <t>확정 / F-RGT-01·03</t>
+        </is>
+      </c>
+      <c r="D28" s="73" t="inlineStr">
+        <is>
+          <t>AI 처리 허용 설정을 제거. Fork·세계관 이용 허용 범위에서 AI 사용 가능, 권리 제한만 차단. 원작 조건 철회·비공개 전환·공개 중단은 기존 Fork 유지·새 행위만 차단.</t>
+        </is>
+      </c>
+      <c r="E28" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-04; UC-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1" s="109">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B29" s="73" t="inlineStr">
+        <is>
+          <t>탐색·읽기</t>
+        </is>
+      </c>
+      <c r="C29" s="73" t="inlineStr">
+        <is>
+          <t>확정 / F-PUB-05·06</t>
+        </is>
+      </c>
+      <c r="D29" s="73" t="inlineStr">
+        <is>
+          <t>제목·작가·해시태그·장르 검색(Elasticsearch 예정, 본문 제외), 최신 발행·좋아요·조회순 정렬, 좋아요 수 공개, 관심 소설·이어 읽기 본인만, 감정 반응 없음.</t>
+        </is>
+      </c>
+      <c r="E29" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/UC-01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1" s="109">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B30" s="73" t="inlineStr">
+        <is>
+          <t>AI 스택·LLMOps</t>
+        </is>
+      </c>
+      <c r="C30" s="73" t="inlineStr">
+        <is>
+          <t>확정 / REQ16 F-LLM-01~05</t>
+        </is>
+      </c>
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>AI Service는 LangChain·LangGraph로 구현하고 Langfuse(Docker 직접 설치)로 추적·평가·프롬프트 버전 관리. 기존 openai-agents 의존성은 첫 AI 기능 구현 시 교체.</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/UC-26.md; ../backend/ai-service/AGENTS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1" s="109">
+      <c r="A31" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B31" s="73" t="inlineStr">
+        <is>
+          <t>알림·정기 작업</t>
+        </is>
+      </c>
+      <c r="C31" s="73" t="inlineStr">
+        <is>
+          <t>확정 / REQ15 F-NTF·F-JOB</t>
+        </is>
+      </c>
+      <c r="D31" s="73" t="inlineStr">
+        <is>
+          <t>사이트 안 알림함과 끌 수 있는/없는 알림 종류, 기한·주기 규칙을 Core API 내장 스케줄러로 실행·기록·감시.</t>
+        </is>
+      </c>
+      <c r="E31" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/UC-27.md, UC-28.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1" s="109">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>추적 규칙</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>v6 신규 기능 ID</t>
+        </is>
+      </c>
+      <c r="C32" s="73" t="inlineStr">
+        <is>
+          <t>24개 추가</t>
+        </is>
+      </c>
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>F-ACT-09, F-WLD-09, F-PUB-05~07, F-SIM-11, F-WRT-12~14, F-FBK-13~15, F-CRD-04·05, F-RPT-03, F-NTF-01·02, F-JOB-01·02, F-LLM-01~05. 담당·일정은 부여하지 않음.</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>usecase.md §3.1·§7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1" s="109">
+      <c r="A33" s="73" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="B33" s="73" t="inlineStr">
+        <is>
+          <t>자체 분류 모델(WBS 3.2~3.7)</t>
+        </is>
+      </c>
+      <c r="C33" s="73" t="inlineStr">
+        <is>
+          <t>재검토 / F-FBK-02</t>
+        </is>
+      </c>
+      <c r="D33" s="73" t="inlineStr">
+        <is>
+          <t>BR-15로 런타임 피드백 분류가 필요 없어짐. 과정 산출물(ML/DL 학습결과서) 요구 여부를 확인한 뒤 용도를 재정의하거나 정리. 라벨링 데이터는 UC-26 평가 세트로 활용 가능.</t>
+        </is>
+      </c>
+      <c r="E33" s="73" t="inlineStr">
+        <is>
+          <t>SKN34-final-4Team_WBS.xlsx 개발현황 CHECK-07</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정리 기준" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="시트1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정리 기준" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'정리 기준'!$A$3:$E$20</definedName>
@@ -939,7 +939,7 @@
     <row r="2" ht="30" customHeight="1" s="109">
       <c r="A2" s="73" t="inlineStr">
         <is>
-          <t>기획서 v1.4 · 유스케이스 v6·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 116개 미구현 · 미정 정책 유지 · 상세: 정리 기준 시트</t>
+          <t>기획서 v1.4 · 유스케이스 v7·UC별 명세(docs/usecase-spec) 기준 · 업무 기능 116개 미구현 · 미정 정책 유지 · MVP 제외는 H열 표기 · 상세: 정리 기준 시트</t>
         </is>
       </c>
       <c r="B2" s="110" t="n"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F4" s="68" t="inlineStr">
         <is>
-          <t>필수 항목은 이메일·비밀번호·닉네임, 이메일 인증 후 계정 생성(확정). 약관·선택 동의 항목은 미정.</t>
+          <t>필수 항목은 이메일·비밀번호·닉네임, 이메일 인증 후 계정 생성(확정). 약관·선택 동의 항목은 미정. 인증 메일은 Core API가 SMTP로 발송, 개발 환경은 로컬 Mailpit으로 확인(v7 확정).</t>
         </is>
       </c>
       <c r="G4" s="73" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F10" s="96" t="inlineStr">
         <is>
-          <t>가입 이메일로 재설정 링크 발송, 재설정 시 모든 갱신 토큰 폐기(확정).</t>
+          <t>가입 이메일로 재설정 링크 발송, 재설정 시 모든 갱신 토큰 폐기(확정). 재설정 메일도 같은 SMTP 경로(v7).</t>
         </is>
       </c>
       <c r="G10" s="73" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="F11" s="96" t="inlineStr">
         <is>
-          <t>30일 유예 후 작품·세계관·Fork 삭제, 다른 회원의 Fork가 참조하는 고정본은 유지('탈퇴한 회원' 표시), 댓글·피드백은 익명화(확정). 남은 크레딧 처리는 미정.</t>
+          <t>30일 유예 후 작품·세계관·Fork 삭제, 다른 회원의 Fork가 참조하는 고정본은 유지('탈퇴한 회원' 표시), 댓글·피드백은 익명화(확정). 남은 크레딧 처리는 미정. 탈퇴한 원작자의 분기 전 회차 본문은 Fork 독자에게 숨김(v7 확정).</t>
         </is>
       </c>
       <c r="G11" s="73" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F14" s="96" t="inlineStr">
         <is>
-          <t>세계관·인물관계도는 Gitea로 변경 이력 관리(확정)</t>
+          <t>세계관 설정 값·인물관계도·인물 기본 정보는 세계관마다 하나의 Gitea 저장소로 변경 이력 관리(확정). 항목마다 이용자 노출 여부(기본 노출)를 지정하며, 독자 공개는 작품 단위로 정함(v7 확정).</t>
         </is>
       </c>
       <c r="G14" s="73" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F15" s="96" t="inlineStr">
         <is>
-          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 단, 연결한 다른 사용자 세계관을 자기 세계관 Fork로 교체하는 것은 발행 후에도 허용(연결 수 유지). 세계관 Fork를 허용하지 않은 세계관만 연결하면 작가 소유 세계관도 함께 연결하도록 안내. 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다.</t>
+          <t>연결 목록은 첫 회차 발행 전까지만 변경 가능(확정). 단, 연결한 다른 사용자 세계관을 자기 세계관 Fork로 교체하는 것은 발행 후에도 허용(연결 수 유지). 세계관 Fork를 허용하지 않은 세계관만 연결하면 작가 소유 세계관도 함께 연결하도록 안내. 세계관 간 충돌은 설정 검토(UC-12)로 해결. 생성·저장이 자동 공개를 뜻하지 않습니다. Fork 작품은 원작에서 받은 고정 세계관도 5개에 포함하고, Fork 전용 세계관은 분기 이후 첫 회차 발행 뒤에도 5개 안에서 추가 가능(v7 확정).</t>
         </is>
       </c>
       <c r="G15" s="73" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F16" s="96" t="inlineStr">
         <is>
-          <t>회차(에피소드) 원고는 DB에 저장(확정)</t>
+          <t>회차 원고와 작품별 회차 기록(설정 유효·독자 공개·인물별 인지 회차, 작품별 인물 상태, @ 연결)은 DB에 저장하고 세계관 항목 ID·커밋 ID를 참조(v7 확정).</t>
         </is>
       </c>
       <c r="G16" s="73" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F20" s="96" t="inlineStr">
         <is>
-          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 공개 항목만, 비공개 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경 알림·골라 가져오기는 미확정. 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
+          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 이용자 노출 항목만, 비노출 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경은 알림만 받고 가져오지 않음(확정). 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
         </is>
       </c>
       <c r="G20" s="73" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F21" s="96" t="inlineStr">
         <is>
-          <t>DRM 파일·지원하지 않는 이미지는 실패로 구분(확정). 이미지 저장 위치 미정.</t>
+          <t>DRM 파일·지원하지 않는 이미지는 실패로 구분(확정). 이미지 파일은 MinIO에 저장하고 DB에는 위치·메타데이터만(v7 확정).</t>
         </is>
       </c>
       <c r="G21" s="73" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F24" s="96" t="inlineStr">
         <is>
-          <t>인물 기본 정보는 세계관과 함께 Gitea에 저장(확정). 회차 시점(설정 유효·독자 공개·인물별 인지 회차)은 세계관이 아니라 작품별로 기록(확정).</t>
+          <t>인물 기본 정보는 세계관과 함께 Gitea에 저장(확정). 회차 시점(설정 유효·독자 공개·인물별 인지 회차)은 세계관이 아니라 작품별로 기록(확정). 작품별 기록은 DB에 저장(v7 확정).</t>
         </is>
       </c>
       <c r="G24" s="73" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F29" s="96" t="inlineStr">
         <is>
-          <t>발행 후 수정·공개 철회·버전 노출·유료 열람 정책 미정. 등록 원고의 공개를 강제하지 않습니다.</t>
+          <t>회차 공개 중단은 기존 Fork 유지·새 분기 기준 불가(확정). 유료 열람은 MVP 제외(v7). 발행 후 수정 이력 노출·예약 발행은 미정. 등록 원고의 공개를 강제하지 않습니다.</t>
         </is>
       </c>
       <c r="G29" s="73" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F32" s="96" t="inlineStr">
         <is>
-          <t>Elasticsearch 예정, 공개 정보만 색인, 본문 검색 제외(확정). 한국어 분석 방식은 구현 시 결정.</t>
+          <t>Elasticsearch 예정, 공개 정보만 색인, 본문 검색 제외(확정). 한국어 분석 방식은 구현 시 결정. MVP는 Elasticsearch 없이 DB 검색으로 제공(v7 확정).</t>
         </is>
       </c>
       <c r="G32" s="73" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="E36" s="73" t="inlineStr">
         <is>
-          <t>Core API는 Fork 생성 전에 요청자의 접근 권한, 원작의 이용 조건, 원작 세계관의 공개 상태와 선택 회차의 Fork 허용 여부를 확인해야 합니다. 등록·허용 설정만으로 외부 IP의 적법한 이용권을 가정하지 않아야 합니다.</t>
+          <t>Core API는 Fork 생성 전에 요청자의 접근 권한, 원작의 이용 조건, 선택 회차의 Fork 허용 여부를 확인해야 합니다. 등록·허용 설정만으로 외부 IP의 적법한 이용권을 가정하지 않아야 합니다.</t>
         </is>
       </c>
       <c r="F36" s="96" t="inlineStr">
         <is>
-          <t>원작에서만 Fork 가능, 한 독자는 한 원작에서 1번만, Fork 작품의 Fork 불가(확정, 관리 단순화). 권리 확인 절차·증빙 기준 정의 필요</t>
+          <t>원작에서만 Fork 가능, 한 독자는 한 원작에서 1번만, Fork 작품의 Fork 불가(확정, 관리 단순화). 권리 확인 절차·증빙 기준 정의 필요 원작 세계관의 세계관 공개는 요구하지 않음(v7 확정).</t>
         </is>
       </c>
       <c r="G36" s="73" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F38" s="96" t="inlineStr">
         <is>
-          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 분기 시점 버전을 참조하는 원칙은 확정, Gitea 브랜치·커밋 참조 등 구현 수단은 미정. 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
+          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 세계관은 분기 시점 Gitea 커밋 ID, 작품별 회차 기록은 DB 사본으로 고정(v7 확정), 브랜치 운용은 미정. 원작 삭제·원작 작가 탈퇴 시 Fork 독자에게 분기 전 회차 본문 숨김, 고정본은 Fork 소유자 참고·AI 문맥으로만 사용(v7 확정). 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G38" s="73" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="F61" s="96" t="inlineStr">
         <is>
-          <t>자동 발행 확정. 소유자가 정한 요일·시각(주 1~7회, 하루 최대 1회)에 Core API 내장 스케줄러로 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단됨, 생성 회차도 1차 필터, 발행 전 확인 옵션(기본 꺼짐)(확정). 다중 서버 중복 실행 방지 미정.</t>
+          <t>자동 발행 확정. 소유자가 정한 요일·시각(주 1~7회, 하루 최대 1회)에 Core API 내장 스케줄러로 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단됨, 생성 회차도 1차 필터, 발행 전 확인 옵션(기본 꺼짐)(확정). 다중 서버 중복 실행 방지 미정. 일정은 KST, 예정 시각에서 1시간 넘게 지연된 실행은 건너뛰고 알림·연속 실패에 미포함(v7 확정).</t>
         </is>
       </c>
       <c r="G61" s="73" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="F64" s="96" t="inlineStr">
         <is>
-          <t>JPG·PNG·WebP 장당 10MB, 이용 권한 확인, 저장 사용량 포함, AI에 전달하지 않음(확정). 저장 위치·대체 텍스트 입력 방식 미정.</t>
+          <t>JPG·PNG·WebP 장당 10MB, 이용 권한 확인, 저장 사용량 포함, AI에 전달하지 않음(확정). MinIO에 저장(v7 확정). 대체 텍스트 입력 방식 미정.</t>
         </is>
       </c>
       <c r="G64" s="73" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F66" s="96" t="inlineStr">
         <is>
-          <t>지정 장면과 작가가 정리한 인물 외형만 이미지 생성 모델에 전달, 안전 정책 거부는 실패로 고지(확정). 비용·권리 귀속·AI 생성 표시 미정. 기획서 근거 없음(팀 결정).</t>
+          <t>지정 장면과 작가가 정리한 인물 외형만 이미지 생성 모델에 전달, 안전 정책 거부는 실패로 고지(확정). 비용·권리 귀속·AI 생성 표시 미정. 기획서 근거 없음(팀 결정). MVP 제외(v7).</t>
         </is>
       </c>
       <c r="G66" s="73" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="H66" s="73" t="inlineStr">
         <is>
-          <t>팀 결정 / 개발 계약 미확정</t>
+          <t>팀 결정 · MVP 제외</t>
         </is>
       </c>
       <c r="I66" s="73" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J66" s="73" t="inlineStr">
         <is>
-          <t>작업 미분해 (개발현황 GAP-09)</t>
+          <t>MVP 범위 밖 (개발현황 GAP-09)</t>
         </is>
       </c>
       <c r="K66" s="2" t="n"/>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E69" s="73" t="inlineStr">
         <is>
-          <t>단순 오류(오탈자·맞춤법·명백한 숫자·표기)와 스토리 오류(설정 충돌·인물 행동·지식 모순·개연성)를 분리해야 합니다. 단순 오류만 수정안·자동 승인 경로로 처리하고, 스토리 오류는 언제나 작가가 판단합니다.</t>
+          <t>단순 오류(오탈자·맞춤법·띄어쓰기·문장부호·명백한 숫자·표기)와 스토리 오류(설정 충돌·인물 행동·지식 모순·개연성)를 분리해야 합니다. 단순 오류만 수정안 경로로 처리하고(자동 승인은 오탈자·맞춤법·띄어쓰기·문장부호 수정만), 스토리 오류는 언제나 작가가 판단합니다.</t>
         </is>
       </c>
       <c r="F69" s="96" t="n"/>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E73" s="73" t="inlineStr">
         <is>
-          <t>작품 소유자가 수정안을 검토·승인하면 권한과 기준 버전을 다시 확인해 승인 범위만 초안에 반영하고 발행 절차로 공개해야 합니다. 작품 설정이 '표기 오류 자동 승인·발행'이면 오타·맞춤법·명백한 숫자 표기 오류에 한해 시스템이 자동 승인·발행합니다.</t>
+          <t>작품 소유자가 수정안을 검토·승인하면 권한과 기준 버전을 다시 확인해 승인 범위만 초안에 반영하고 발행 절차로 공개해야 합니다. 작품 설정이 '표기 오류 자동 승인·발행'이면 오탈자·맞춤법·띄어쓰기·문장부호만 고치는 수정안에 한해 시스템이 자동 승인·발행합니다.</t>
         </is>
       </c>
       <c r="F73" s="96" t="inlineStr">
         <is>
-          <t>Fork 소유자는 자신의 Fork만 승인. 기준 버전이 바뀌거나 자동 발행이 실패하면 자동 처리를 멈추고 작가 검토로 전환.</t>
+          <t>Fork 소유자는 자신의 Fork만 승인. 기준 버전이 바뀌거나 자동 발행이 실패하면 자동 처리를 멈추고 작가 검토로 전환. 숫자·고유명사·단어 교체가 들어간 수정안은 작가 검토, 작업 초안이 발행본과 다르면 자동 처리하지 않고 작가 검토로 전환, 자동 처리 대상은 AI가 아닌 Core API가 변경 차이로 판정(v7 확정).</t>
         </is>
       </c>
       <c r="G73" s="73" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F82" s="68" t="inlineStr">
         <is>
-          <t>'일부 공개'는 삭제(확정). 세계관 자체의 판매는 범위 밖. 공개 세계관을 비공개로 바꾸면 이용 허가 철회와 같이 처리.</t>
+          <t>'일부 공개'는 삭제(확정). 세계관 자체의 판매는 범위 밖. 공개 세계관을 비공개로 바꾸면 이용 허가 철회와 같이 처리. 세계관 공개·항목 이용자 노출·독자 공개는 별개 개념(v7). 유료 공개 허용 항목은 MVP 제외.</t>
         </is>
       </c>
       <c r="G82" s="73" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F84" s="96" t="inlineStr">
         <is>
-          <t>AI 처리 허용 항목 제거(확정). 허용 철회·작품 비공개 전환('비공개 원작' 표시)·회차 공개 중단은 기존 Fork와 공개 상태를 유지하고 새 행위만 차단(확정). 권리 증빙·유료 공개 조건은 미정.</t>
+          <t>AI 처리 허용 항목 제거(확정). 허용 철회·작품 비공개 전환('비공개 원작' 표시)·회차 공개 중단은 기존 Fork와 공개 상태를 유지하고 새 행위만 차단(확정). 권리 증빙·유료 공개 조건은 미정. 유료 공개 항목은 MVP 화면에 표시하지 않음(v7).</t>
         </is>
       </c>
       <c r="G84" s="73" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="E98" s="73" t="inlineStr">
         <is>
-          <t>비공개 설정집·인물관계도 항목을 특정 회차부터 독자 공개로 전환하고 전환 회차를 기록해야 합니다. 세계관 자동 업데이트 실행 시에도 같은 방식으로 반영합니다.</t>
+          <t>독자 비공개인 설정집·인물관계도 항목을 특정 회차부터 독자 공개로 전환하고 전환 회차를 기록해야 합니다. 세계관 자동 업데이트 실행 시에도 같은 방식으로 반영합니다.</t>
         </is>
       </c>
       <c r="F98" s="96" t="inlineStr">
         <is>
-          <t>세계관에서는 항목의 공개·비공개만 정하고, 공개 전환 회차는 연결된 작품에서 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
+          <t>세계관에서는 항목의 이용자 노출 여부만 정하고 독자 공개는 언제나 작품 단위이며(v7), 공개 전환 회차는 연결된 작품에서 작품별로 기록(확정). 다른 작품에서 공개된 항목도 이용 작품에는 비공개로 들어와 그 작품 회차 기준으로 공개. 기존 Fork에는 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G98" s="73" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F100" s="68" t="inlineStr">
         <is>
-          <t>후차감 방식(확정). 잔여가 예상 상한보다 적으면 실행하지 않음. 비용 확인 단계 취소는 '취소됨'·차감 없음. 가격·토큰 환산 비율은 미정.</t>
+          <t>후차감 방식(확정). 실행 전 동의한 상한만큼 예약하고 정산 후 남은 예약을 해제하며, 사용 가능 잔액(잔여−예약)이 상한보다 적으면 실행하지 않음(v7 확정). 비용 확인 단계 취소는 '취소됨'·차감 없음. 가격 미정. 토큰 환산 비율은 모델별 Core API 설정값(값 미정).</t>
         </is>
       </c>
       <c r="G100" s="73" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F103" s="96" t="inlineStr">
         <is>
-          <t>가입 체험 30일, 보상·이벤트 월 소멸, 구독 매달 초기화(이월 없음), 추가 구매는 구독 회원만·12개월, 소멸이 빠른 것부터 차감(확정). 현재는 실결제 없이 테스트 크레딧. 플랜·가격 미정.</t>
+          <t>가입 체험 30일, 보상·이벤트 월 소멸, 구독 매달 초기화(이월 없음), 추가 구매는 구독 회원만·12개월, 소멸 시각이 빠른 것부터 차감·같으면 무료 먼저, 예약분은 정산 전 소멸 제외, 월간 초기화는 매월 1일 00:00 KST(v7 확정). 구독·추가 구매는 MVP 제외, 테스트 크레딧만 사용. 플랜·가격 미정.</t>
         </is>
       </c>
       <c r="G103" s="73" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="F105" s="96" t="inlineStr">
         <is>
-          <t>용량·요금·삭제 복원 정책 미정.</t>
+          <t>용량·요금·삭제 복원 정책 미정. MVP 제외(v7).</t>
         </is>
       </c>
       <c r="G105" s="73" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="H105" s="73" t="inlineStr">
         <is>
-          <t>조건부 기획 / 정책 미정</t>
+          <t>조건부 · MVP 제외</t>
         </is>
       </c>
       <c r="I105" s="73" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="J105" s="73" t="inlineStr">
         <is>
-          <t>조건부 / 작업 미분해</t>
+          <t>MVP 범위 밖</t>
         </is>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="F113" s="96" t="inlineStr">
         <is>
-          <t>Core API 내장 스케줄러 하나, worker·큐 없음, 같은 대상 중복 처리 금지(확정). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
+          <t>Core API 내장 스케줄러 하나, worker·큐 없음, 같은 대상 중복 처리 금지(확정). KST 기준, 서버 중단 후 밀린 작업은 기동 시 실행·지연 경고(자율 연재는 1시간 초과 시 건너뜀)(v7 확정). 검색 색인 동기화는 Elasticsearch 도입 후(MVP 제외). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
         </is>
       </c>
       <c r="G113" s="73" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="F117" s="96" t="inlineStr">
         <is>
-          <t>평가 세트는 이용 조건을 확인한 저작권 만료 작품으로 구성(확정). 구성·통과 기준 미정.</t>
+          <t>평가 세트는 이용 조건을 확인한 저작권 만료 작품으로 구성(확정). 구성·통과 기준 미정. MVP 제외(v7, MVP는 Langfuse 추적만).</t>
         </is>
       </c>
       <c r="G117" s="73" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="H117" s="73" t="inlineStr">
         <is>
-          <t>팀 결정 / 개발 계약 미확정</t>
+          <t>팀 결정 · MVP 제외</t>
         </is>
       </c>
       <c r="I117" s="73" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="J117" s="73" t="inlineStr">
         <is>
-          <t>4.10·4.11 관련 / 세부 작업 미분해</t>
+          <t>MVP 범위 밖</t>
         </is>
       </c>
       <c r="K117" s="2" t="n"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="F119" s="96" t="inlineStr">
         <is>
-          <t>BR-02 운영 확인 장치(확정). 표본 비율 미정.</t>
+          <t>BR-02 운영 확인 장치(확정). 표본 비율 미정. MVP 제외(v7, MVP는 Langfuse 추적만).</t>
         </is>
       </c>
       <c r="G119" s="73" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="H119" s="73" t="inlineStr">
         <is>
-          <t>팀 결정 / 개발 계약 미확정</t>
+          <t>팀 결정 · MVP 제외</t>
         </is>
       </c>
       <c r="I119" s="73" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="J119" s="73" t="inlineStr">
         <is>
-          <t>WBS 없음 (개발현황 GAP-13)</t>
+          <t>MVP 범위 밖</t>
         </is>
       </c>
       <c r="K119" s="2" t="n"/>
@@ -14235,7 +14235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="19" customWidth="1" style="109" min="1" max="1"/>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="D4" s="73" t="inlineStr">
         <is>
-          <t>원본 11개 요구사항 그룹·80개 기능 ID 유지. 문구 정합성 보완과 G:J 추적 열 추가. 새 기능 ID·담당자·일정은 임의 부여하지 않음. 유스케이스 v3 반영으로 3개 그룹·12개 ID(F-SET·F-CRD·F-STO·F-RPT·F-ALT) 추가. 유스케이스 v6 반영으로 2개 그룹(REQ15 알림·정기 작업, REQ16 AI 운영)과 24개 ID 추가, F-FBK-02·03은 독자 유형 선택 기준으로 재정의(총 116개).</t>
+          <t>원본 11개 요구사항 그룹·80개 기능 ID 유지. 문구 정합성 보완과 G:J 추적 열 추가. 새 기능 ID·담당자·일정은 임의 부여하지 않음. 유스케이스 v3 반영으로 3개 그룹·12개 ID(F-SET·F-CRD·F-STO·F-RPT·F-ALT) 추가. 유스케이스 v6 반영으로 2개 그룹(REQ15 알림·정기 작업, REQ16 AI 운영)과 24개 ID 추가, F-FBK-02·03은 독자 유형 선택 기준으로 재정의(총 116개). 유스케이스 v7(2026-10-28) 반영으로 MVP 범위·공개 용어·저장 경계 등 결정 11건과 문서 불일치 8건 정리(ID 추가 없음, 총 116개).</t>
         </is>
       </c>
       <c r="E4" s="73" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="D10" s="73" t="inlineStr">
         <is>
-          <t>기준 회차의 정확한 버전과 당시 허용된 공개 정보만 고정. 비공개·이후 내용 제외. 원작 후속 변경 자동 유입 금지. 분기 시점 버전 참조 원칙은 확정(구현 수단 미정). 작품 운영 설정·공개 조건은 넘기지 않음. 철회 영향은 미정.</t>
+          <t>기준 회차의 정확한 버전과 당시 허용된 공개 정보만 고정. 비공개·이후 내용 제외. 원작 후속 변경 자동 유입 금지. 분기 시점 고정은 세계관 Gitea 커밋 ID·작품별 회차 기록 DB 사본(v7 확정, 브랜치 운용 미정). 작품 운영 설정·공개 조건은 넘기지 않음. 철회·비공개 전환·공개 중단은 기존 Fork 유지·새 행위만 차단(v6 확정). 세계관 공개 불요·원작 삭제 시 분기 전 본문 숨김(v7 확정).</t>
         </is>
       </c>
       <c r="E10" s="73" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="D13" s="73" t="inlineStr">
         <is>
-          <t>.txt·.epub 가져오기·내보내기, 이미지 삽입, 회차 자동 구분, 재등록은 새 초안 버전, 자동 저장·충돌 재확인·버전 무기한 보관(v6 확정). 이미지 저장 위치·자동 저장 간격은 미정.</t>
+          <t>.txt·.epub 가져오기·내보내기, 이미지 삽입, 회차 자동 구분, 재등록은 새 초안 버전, 자동 저장·충돌 재확인·버전 무기한 보관(v6 확정). 이미지는 MinIO(v7 확정). 자동 저장 간격은 미정.</t>
         </is>
       </c>
       <c r="E13" s="73" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="D15" s="73" t="inlineStr">
         <is>
-          <t>자동 발행, 소유자 지정 요일·시각 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단, 발행 전 확인 옵션(기본 꺼짐), Core API 내장 스케줄러(v6 확정). 다중 서버 중복 실행 방지는 미정.</t>
+          <t>자동 발행, 소유자 지정 요일·시각 실행, 연속 3회 실패·월 한도·크레딧 부족 시 중단, 발행 전 확인 옵션(기본 꺼짐), Core API 내장 스케줄러(v6 확정). KST 기준·1시간 넘게 지연된 실행 건너뜀(v7 확정). 다중 서버 중복 실행 방지는 미정.</t>
         </is>
       </c>
       <c r="E15" s="73" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="D16" s="73" t="inlineStr">
         <is>
-          <t>실행 후 실제 토큰 사용량 환산 차감(상한 이내), 실패 시 차감 없음, 무료(가입 체험·보상·이벤트)·유료(구독·추가 구매) 크레딧, 토큰 버킷 속도 제한(v6 확정). 플랜·가격·환산 비율은 미정.</t>
+          <t>실행 후 실제 토큰 사용량 환산 차감(상한 이내), 실패 시 차감 없음, 무료(가입 체험·보상·이벤트)·유료(구독·추가 구매) 크레딧, 토큰 버킷 속도 제한(v6 확정). 예약 후 정산·소멸 임박 순 차감·매월 1일 KST 초기화·환산 비율 설정값(v7 확정). 플랜·가격·환산 비율 값은 미정.</t>
         </is>
       </c>
       <c r="E16" s="73" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="D25" s="73" t="inlineStr">
         <is>
-          <t>다른 사용자 세계관 수정 시 공개 항목만 세계관 Fork로 복사·연결 교체·원본 업데이트 없음·출처 기록. 플랫폼 장르 기본 세계관 복사는 원본 관계 없음. 이용과 세계관 Fork는 따로 허용.</t>
+          <t>다른 사용자 세계관 수정 시 이용자 노출 항목만 세계관 Fork로 복사·연결 교체·원본 업데이트 없음·출처 기록. 플랫폼 장르 기본 세계관 복사는 원본 관계 없음. 이용과 세계관 Fork는 따로 허용.</t>
         </is>
       </c>
       <c r="E25" s="73" t="inlineStr">
@@ -15101,6 +15101,114 @@
       <c r="E33" s="73" t="inlineStr">
         <is>
           <t>SKN34-final-4Team_WBS.xlsx 개발현황 CHECK-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1" s="109">
+      <c r="A34" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
+        <is>
+          <t>MVP 범위</t>
+        </is>
+      </c>
+      <c r="C34" s="73" t="inlineStr">
+        <is>
+          <t>v7 확정 / F-PUB-05·07, F-WRT-14, F-CRD-04, F-STO-01, F-LLM-03·05</t>
+        </is>
+      </c>
+      <c r="D34" s="73" t="inlineStr">
+        <is>
+          <t>첫 출시 제외: 유료 공개·열람(설정 숨김), UC-19 저장 공간, 구독·추가 구매(테스트 크레딧만), 일러스트 생성, Elasticsearch(DB 검색 대체), LLMOps 평가 세트·표본 검사(Langfuse 추적만), 캐릭터 챗. 전부 제외되는 기능 ID는 H열에 MVP 제외 표기.</t>
+        </is>
+      </c>
+      <c r="E34" s="73" t="inlineStr">
+        <is>
+          <t>usecase.md §6.2 MVP 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1" s="109">
+      <c r="A35" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B35" s="73" t="inlineStr">
+        <is>
+          <t>공개 용어·저장 경계</t>
+        </is>
+      </c>
+      <c r="C35" s="73" t="inlineStr">
+        <is>
+          <t>v7 확정 / F-WLD-02·04·08, F-CHR-03, F-SET-03</t>
+        </is>
+      </c>
+      <c r="D35" s="73" t="inlineStr">
+        <is>
+          <t>세계관 공개(UC-07)·항목 이용자 노출(UC-02)·독자 공개(작품 단위) 분리. 세계관 설정 값·인물 기본 정보는 세계관별 Gitea 저장소, 작품별 회차 기록은 DB, 이미지는 MinIO.</t>
+        </is>
+      </c>
+      <c r="E35" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-10·BR-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1" s="109">
+      <c r="A36" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>Fork·표기 오류·크레딧</t>
+        </is>
+      </c>
+      <c r="C36" s="73" t="inlineStr">
+        <is>
+          <t>v7 확정 / F-FRK-02·04, F-FBK-03·07, F-CRD-01·04</t>
+        </is>
+      </c>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>작품 Fork에 세계관 공개 불요, 원작 삭제·작가 탈퇴 시 분기 전 본문 숨김, 고정 세계관도 연결 5개에 포함. 자동 승인은 오탈자·맞춤법·띄어쓰기·문장부호만, 작업 초안이 발행본과 다르면 작가 검토. 크레딧 예약 후 정산, 소멸 임박 순 차감, 매월 1일 KST 초기화.</t>
+        </is>
+      </c>
+      <c r="E36" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/README.md BR-04·BR-15; UC-16.md, UC-17.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1" s="109">
+      <c r="A37" s="73" t="inlineStr">
+        <is>
+          <t>팀 결정</t>
+        </is>
+      </c>
+      <c r="B37" s="73" t="inlineStr">
+        <is>
+          <t>일정·인증 메일</t>
+        </is>
+      </c>
+      <c r="C37" s="73" t="inlineStr">
+        <is>
+          <t>v7 확정 / F-WRT-09, F-JOB-01, F-ACT-01·07</t>
+        </is>
+      </c>
+      <c r="D37" s="73" t="inlineStr">
+        <is>
+          <t>모든 일정 KST. 서버 중단 후 자율 연재는 1시간 초과 시 건너뛰고 다른 정기 작업은 기동 시 실행. 인증 메일은 SMTP(개발: 로컬 Mailpit). MinIO·Mailpit은 새 구성요소로 구현 전 팀 공유.</t>
+        </is>
+      </c>
+      <c r="E37" s="73" t="inlineStr">
+        <is>
+          <t>usecase-spec/UC-18.md, UC-22.md, UC-28.md</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_요구사항정의서.xlsx
+++ b/docs/SKN34-final-4Team_요구사항정의서.xlsx
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F16" s="96" t="inlineStr">
         <is>
-          <t>회차 원고와 작품별 회차 기록(설정 유효·독자 공개·인물별 인지 회차, 작품별 인물 상태, @ 연결)은 DB에 저장하고 세계관 항목 ID·커밋 ID를 참조(v7 확정).</t>
+          <t>회차 원고와 작품별 회차 기록(설정 유효·독자 공개·인물별 인지 회차, 작품별 인물 상태, @ 연결)은 DB에 저장하고 세계관 항목 ID를 참조, 커밋 ID 고정은 Fork·이용 허가 철회 시점에만(v7 확정).</t>
         </is>
       </c>
       <c r="G16" s="73" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F20" s="96" t="inlineStr">
         <is>
-          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관 전체를 세계관 Fork로 복사(그 시점 이용자 노출 항목만, 비노출 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경은 알림만 받고 가져오지 않음(확정). 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
+          <t>다른 사용자 세계관은 고치지 않으면 원본 참조(최신 공개본 반영). 고치려면 세계관을 세계관 Fork로 복사(그 시점 이용자 노출 항목만, 비노출 항목·원작 작품 회차 기록 제외)하고 연결 교체. 세계관 Fork는 원본 업데이트를 받지 않고 출처 기록, 원본 소유자가 허용한 경우만 가능(확정). 원본 변경은 알림만 받고 가져오지 않음(확정). 빌려 쓰는 세계관에 자기 작품 설정을 추가하는 것은 항상 가능. 이용 허가 철회·비공개 전환 시 철회 시점 상태로 고정.</t>
         </is>
       </c>
       <c r="G20" s="73" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F38" s="96" t="inlineStr">
         <is>
-          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 세계관은 분기 시점 Gitea 커밋 ID, 작품별 회차 기록은 DB 사본으로 고정(v7 확정), 브랜치 운용은 미정. 원작 삭제·원작 작가 탈퇴 시 Fork 독자에게 분기 전 회차 본문 숨김, 고정본은 Fork 소유자 참고·AI 문맥으로만 사용(v7 확정). 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
+          <t>회차별 설정 이력이 없는 원작(일괄 등록)은 현재 공개 상태로 고정하고 독자에게 경고(확정). 세계관은 분기 시점 Gitea 커밋 ID, 작품별 회차 기록은 DB 사본으로 고정(v7 확정), 브랜치 운용은 미정. 원작 삭제·원작 작가 탈퇴 시 Fork 독자에게 분기 전 회차 본문 숨김, 고정본은 Fork 소유자 참고·AI 문맥으로만 사용하고 AI 출력은 숨긴 본문을 길게 그대로 옮기지 않음(v7 확정). 원작의 후속 변경은 기존 Fork에 반영하지 않습니다.</t>
         </is>
       </c>
       <c r="G38" s="73" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F100" s="68" t="inlineStr">
         <is>
-          <t>후차감 방식(확정). 실행 전 동의한 상한만큼 예약하고 정산 후 남은 예약을 해제하며, 사용 가능 잔액(잔여−예약)이 상한보다 적으면 실행하지 않음(v7 확정). 비용 확인 단계 취소는 '취소됨'·차감 없음. 가격 미정. 토큰 환산 비율은 모델별 Core API 설정값(값 미정).</t>
+          <t>후차감 방식(확정). 실행 전 동의한 상한만큼 예약하고 정산 후 남은 예약을 해제하며, 사용 가능 잔액(잔여−예약)이 상한보다 적으면 실행하지 않음(v7 확정). 자동 실행은 설정 시가 아니라 매 실행 직전에 1회분만 예약하고, 상한·범위 변경 시 재동의. 비용 확인 단계 취소는 '취소됨'·차감 없음. 가격 미정. 토큰 환산 비율은 모델별 Core API 설정값(값 미정).</t>
         </is>
       </c>
       <c r="G100" s="73" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F103" s="96" t="inlineStr">
         <is>
-          <t>가입 체험 30일, 보상·이벤트 월 소멸, 구독 매달 초기화(이월 없음), 추가 구매는 구독 회원만·12개월, 소멸 시각이 빠른 것부터 차감·같으면 무료 먼저, 예약분은 정산 전 소멸 제외, 월간 초기화는 매월 1일 00:00 KST(v7 확정). 구독·추가 구매는 MVP 제외, 테스트 크레딧만 사용. 플랜·가격 미정.</t>
+          <t>가입 체험 30일, 보상·이벤트 월 소멸, 구독 매달 초기화(이월 없음), 추가 구매는 구독 회원만·12개월, 소멸 시각이 빠른 것부터 차감·같으면 무료 먼저, 예약분은 정산 전 소멸 제외, 월간 초기화는 매월 1일 00:00 KST(v7 확정). 구독·추가 구매는 MVP 제외, MVP는 가입 체험·보상·이벤트 크레딧만 사용, 추가 지급은 이벤트 크레딧(v7). 플랜·가격 미정.</t>
         </is>
       </c>
       <c r="G103" s="73" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="D34" s="73" t="inlineStr">
         <is>
-          <t>첫 출시 제외: 유료 공개·열람(설정 숨김), UC-19 저장 공간, 구독·추가 구매(테스트 크레딧만), 일러스트 생성, Elasticsearch(DB 검색 대체), LLMOps 평가 세트·표본 검사(Langfuse 추적만), 캐릭터 챗. 전부 제외되는 기능 ID는 H열에 MVP 제외 표기.</t>
+          <t>첫 출시 제외: 유료 공개·열람(설정 숨김), UC-19 저장 공간, 구독·추가 구매(가입 체험·보상·이벤트 크레딧만), 일러스트 생성, Elasticsearch(DB 검색 대체), LLMOps 평가 세트·표본 검사(Langfuse 추적만), 캐릭터 챗. 전부 제외되는 기능 ID는 H열에 MVP 제외 표기.</t>
         </is>
       </c>
       <c r="E34" s="73" t="inlineStr">
